--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -1319,7 +1319,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2771,7 +2771,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="221">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="8" type="noConversion"/>
@@ -72,636 +72,739 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>!bool</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pen_Physical</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pen_Magic</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate</t>
+  </si>
+  <si>
+    <t>SuperCritRate_Add</t>
+  </si>
+  <si>
+    <t>SuperCritDam</t>
+  </si>
+  <si>
+    <t>SuperCritDam_Add</t>
+  </si>
+  <si>
+    <t>SuperCritDam_Ratio</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>HP_Base</t>
+  </si>
+  <si>
+    <t>HP_Add</t>
+  </si>
+  <si>
+    <t>HP_Ratio</t>
+  </si>
+  <si>
+    <t>HP_Amp</t>
+  </si>
+  <si>
+    <t>DEF</t>
+  </si>
+  <si>
+    <t>DEF_Base</t>
+  </si>
+  <si>
+    <t>DEF_Add</t>
+  </si>
+  <si>
+    <t>DEF_Ratio</t>
+  </si>
+  <si>
+    <t>MDEF</t>
+  </si>
+  <si>
+    <t>MDEF_Base</t>
+  </si>
+  <si>
+    <t>MDEF_Add</t>
+  </si>
+  <si>
+    <t>MDEF_Ratio</t>
+  </si>
+  <si>
+    <t>HP_Regen</t>
+  </si>
+  <si>
+    <t>HP_Regen_Base</t>
+  </si>
+  <si>
+    <t>HP_Regen_Add</t>
+  </si>
+  <si>
+    <t>HP_Regen_Ratio</t>
+  </si>
+  <si>
+    <t>LifeSteal_Ratio</t>
+  </si>
+  <si>
+    <t>SpellVamp_Ratio</t>
+  </si>
+  <si>
+    <t>DamReduce_Ratio</t>
+  </si>
+  <si>
+    <t>AtkSpeed</t>
+  </si>
+  <si>
+    <t>AtkSpeed_Base</t>
+  </si>
+  <si>
+    <t>AtkSpeed_Add</t>
+  </si>
+  <si>
+    <t>AtkSpeed_Ratio</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Base</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Ratio</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Accuracy_Base</t>
+  </si>
+  <si>
+    <t>Accuracy_Add</t>
+  </si>
+  <si>
+    <t>Evasion</t>
+  </si>
+  <si>
+    <t>Evasion_Base</t>
+  </si>
+  <si>
+    <t>Evasion_Add</t>
+  </si>
+  <si>
+    <t>DamBoss_Ratio</t>
+  </si>
+  <si>
+    <t>DamNormal_Ratio</t>
+  </si>
+  <si>
+    <t>SkillDam_Ratio</t>
+  </si>
+  <si>
+    <t>NormalDam_Ratio</t>
+  </si>
+  <si>
+    <t>Cooldown_Reduce</t>
+  </si>
+  <si>
+    <t>GoldBonus_Ratio</t>
+  </si>
+  <si>
+    <t>ExpBonus_Ratio</t>
+  </si>
+  <si>
+    <t>ItemDrop_Ratio</t>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 물리 공격력</t>
+  </si>
+  <si>
+    <t>추가 물리 공격력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 최종 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어구 관통 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 마법 공격력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 마법 공격력</t>
+  </si>
+  <si>
+    <t>마법 공격력 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 저항 관통 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 체력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 최대 체력</t>
+  </si>
+  <si>
+    <t>추가 최대 체력</t>
+  </si>
+  <si>
+    <t>최대 체력 최종 증폭 (%)</t>
+  </si>
+  <si>
+    <t>물리 방어력</t>
+  </si>
+  <si>
+    <t>기본 물리 방어력</t>
+  </si>
+  <si>
+    <t>추가 물리 방어력</t>
+  </si>
+  <si>
+    <t>물리 방어력 증가 (%)</t>
+  </si>
+  <si>
+    <t>마법 방어력</t>
+  </si>
+  <si>
+    <t>기본 마법 방어력</t>
+  </si>
+  <si>
+    <t>추가 마법 방어력</t>
+  </si>
+  <si>
+    <t>마법 방어력 증가 (%)</t>
+  </si>
+  <si>
+    <t>초당 체력 회복량</t>
+  </si>
+  <si>
+    <t>기본 초당 체력 회복</t>
+  </si>
+  <si>
+    <t>추가 초당 체력 회복</t>
+  </si>
+  <si>
+    <t>초당 체력 회복 증가 (%)</t>
+  </si>
+  <si>
+    <t>물리 피해 흡혈률 (%)</t>
+  </si>
+  <si>
+    <t>마법 피해 흡혈률 (%)</t>
+  </si>
+  <si>
+    <t>받는 피해 감소 (%)</t>
+  </si>
+  <si>
+    <t>공격 속도</t>
+  </si>
+  <si>
+    <t>기본 공격 속도</t>
+  </si>
+  <si>
+    <t>이동 속도</t>
+  </si>
+  <si>
+    <t>기본 이동 속도</t>
+  </si>
+  <si>
+    <t>명중치</t>
+  </si>
+  <si>
+    <t>기본 명중치</t>
+  </si>
+  <si>
+    <t>추가 명중치</t>
+  </si>
+  <si>
+    <t>보스 몬스터 추가 피해 (%)</t>
+  </si>
+  <si>
+    <t>일반 몬스터 추가 피해 (%)</t>
+  </si>
+  <si>
+    <t>스킬 피해량 증가 (%)</t>
+  </si>
+  <si>
+    <t>일반 공격 피해량 증가 (%)</t>
+  </si>
+  <si>
+    <t>스킬 쿨타임 감소 (%)</t>
+  </si>
+  <si>
+    <t>골드 획득량 증가 (%)</t>
+  </si>
+  <si>
+    <t>경험치 획득량 증가 (%)</t>
+  </si>
+  <si>
+    <t>아이템 드랍률 증가 (%)</t>
+  </si>
+  <si>
+    <t>추가 공격 속도</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 체력 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!EnumTable</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseStat</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 데미지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 데미지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!StatInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 최종 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>IsRatio</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>!bool</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pen_Physical</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pen_Magic</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate</t>
-  </si>
-  <si>
-    <t>SuperCritRate_Add</t>
-  </si>
-  <si>
-    <t>SuperCritDam</t>
-  </si>
-  <si>
-    <t>SuperCritDam_Add</t>
-  </si>
-  <si>
-    <t>SuperCritDam_Ratio</t>
-  </si>
-  <si>
-    <t>HP</t>
-  </si>
-  <si>
-    <t>HP_Base</t>
-  </si>
-  <si>
-    <t>HP_Add</t>
-  </si>
-  <si>
-    <t>HP_Ratio</t>
-  </si>
-  <si>
-    <t>HP_Amp</t>
-  </si>
-  <si>
-    <t>DEF</t>
-  </si>
-  <si>
-    <t>DEF_Base</t>
-  </si>
-  <si>
-    <t>DEF_Add</t>
-  </si>
-  <si>
-    <t>DEF_Ratio</t>
-  </si>
-  <si>
-    <t>MDEF</t>
-  </si>
-  <si>
-    <t>MDEF_Base</t>
-  </si>
-  <si>
-    <t>MDEF_Add</t>
-  </si>
-  <si>
-    <t>MDEF_Ratio</t>
-  </si>
-  <si>
-    <t>HP_Regen</t>
-  </si>
-  <si>
-    <t>HP_Regen_Base</t>
-  </si>
-  <si>
-    <t>HP_Regen_Add</t>
-  </si>
-  <si>
-    <t>HP_Regen_Ratio</t>
-  </si>
-  <si>
-    <t>LifeSteal_Ratio</t>
-  </si>
-  <si>
-    <t>SpellVamp_Ratio</t>
-  </si>
-  <si>
-    <t>DamReduce_Ratio</t>
-  </si>
-  <si>
-    <t>AtkSpeed</t>
-  </si>
-  <si>
-    <t>AtkSpeed_Base</t>
-  </si>
-  <si>
-    <t>AtkSpeed_Add</t>
-  </si>
-  <si>
-    <t>AtkSpeed_Ratio</t>
-  </si>
-  <si>
-    <t>MoveSpeed_Base</t>
-  </si>
-  <si>
-    <t>MoveSpeed_Ratio</t>
-  </si>
-  <si>
-    <t>Accuracy</t>
-  </si>
-  <si>
-    <t>Accuracy_Base</t>
+    <t>이동 속도 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 속도 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Accuracy_Add</t>
-  </si>
-  <si>
-    <t>Evasion</t>
-  </si>
-  <si>
-    <t>Evasion_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>명중치 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Evasion_Add</t>
-  </si>
-  <si>
-    <t>DamBoss_Ratio</t>
-  </si>
-  <si>
-    <t>DamNormal_Ratio</t>
-  </si>
-  <si>
-    <t>SkillDam_Ratio</t>
-  </si>
-  <si>
-    <t>NormalDam_Ratio</t>
-  </si>
-  <si>
-    <t>Cooldown_Reduce</t>
-  </si>
-  <si>
-    <t>GoldBonus_Ratio</t>
-  </si>
-  <si>
-    <t>ExpBonus_Ratio</t>
-  </si>
-  <si>
-    <t>ItemDrop_Ratio</t>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 물리 공격력</t>
-  </si>
-  <si>
-    <t>추가 물리 공격력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 최종 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 방어구 관통 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 마법 공격력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 마법 공격력</t>
-  </si>
-  <si>
-    <t>마법 공격력 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력 최종 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 저항 관통 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 확률</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 확률</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 피해량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 피해량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 피해량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 피해량 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 확률</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 확률 (%)</t>
-  </si>
-  <si>
-    <t>초치명타 피해량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 피해량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 피해량 증가 (%)</t>
-  </si>
-  <si>
-    <t>최대 체력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 최대 체력</t>
-  </si>
-  <si>
-    <t>추가 최대 체력</t>
-  </si>
-  <si>
-    <t>최대 체력 최종 증폭 (%)</t>
-  </si>
-  <si>
-    <t>물리 방어력</t>
-  </si>
-  <si>
-    <t>기본 물리 방어력</t>
-  </si>
-  <si>
-    <t>추가 물리 방어력</t>
-  </si>
-  <si>
-    <t>물리 방어력 증가 (%)</t>
-  </si>
-  <si>
-    <t>마법 방어력</t>
-  </si>
-  <si>
-    <t>기본 마법 방어력</t>
-  </si>
-  <si>
-    <t>추가 마법 방어력</t>
-  </si>
-  <si>
-    <t>마법 방어력 증가 (%)</t>
-  </si>
-  <si>
-    <t>초당 체력 회복량</t>
-  </si>
-  <si>
-    <t>기본 초당 체력 회복</t>
-  </si>
-  <si>
-    <t>추가 초당 체력 회복</t>
-  </si>
-  <si>
-    <t>초당 체력 회복 증가 (%)</t>
-  </si>
-  <si>
-    <t>물리 피해 흡혈률 (%)</t>
-  </si>
-  <si>
-    <t>마법 피해 흡혈률 (%)</t>
-  </si>
-  <si>
-    <t>받는 피해 감소 (%)</t>
-  </si>
-  <si>
-    <t>공격 속도</t>
-  </si>
-  <si>
-    <t>기본 공격 속도</t>
-  </si>
-  <si>
-    <t>이동 속도</t>
-  </si>
-  <si>
-    <t>기본 이동 속도</t>
-  </si>
-  <si>
-    <t>이동 속도 증가 (%)</t>
-  </si>
-  <si>
-    <t>명중치</t>
-  </si>
-  <si>
-    <t>기본 명중치</t>
-  </si>
-  <si>
-    <t>추가 명중치</t>
-  </si>
-  <si>
-    <t>보스 몬스터 추가 피해 (%)</t>
-  </si>
-  <si>
-    <t>일반 몬스터 추가 피해 (%)</t>
-  </si>
-  <si>
-    <t>스킬 피해량 증가 (%)</t>
-  </si>
-  <si>
-    <t>일반 공격 피해량 증가 (%)</t>
-  </si>
-  <si>
-    <t>스킬 쿨타임 감소 (%)</t>
-  </si>
-  <si>
-    <t>골드 획득량 증가 (%)</t>
-  </si>
-  <si>
-    <t>경험치 획득량 증가 (%)</t>
-  </si>
-  <si>
-    <t>아이템 드랍률 증가 (%)</t>
-  </si>
-  <si>
-    <t>추가 공격 속도</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 속도 증가</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 체력 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>회피</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 회피</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 회피</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>방어</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 방어</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 방어</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!ID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!EnumTable</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseStat</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량 증가 (%)</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -709,95 +812,27 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>HpRecovery</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!StatInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF</t>
+    <t>회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 방어 (%)</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1319,7 +1354,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1348,68 +1383,68 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>4</v>
@@ -1417,172 +1452,172 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B44" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B45" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B46" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B47" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B48" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.3">
@@ -1592,157 +1627,157 @@
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B53" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B54" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B55" s="2" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B56" s="2" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B57" s="2" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B58" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B59" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B60" s="2" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B61" s="2" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B62" s="2" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B63" s="2" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B64" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B65" s="2" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B66" s="2" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B67" s="2" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B68" s="2" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B69" s="2" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B70" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B71" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B72" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B73" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B74" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B75" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B76" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B77" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B78" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B79" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B80" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +1788,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
@@ -1774,23 +1809,23 @@
   <sheetData>
     <row r="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C1" s="11"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="9" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>8</v>
@@ -1799,7 +1834,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="H2" s="13"/>
       <c r="I2" s="9"/>
@@ -1810,7 +1845,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="9" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>6</v>
@@ -1819,13 +1854,13 @@
         <v>6</v>
       </c>
       <c r="E3" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="G3" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
@@ -1836,7 +1871,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
       <c r="B4" s="2" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>7</v>
@@ -1850,30 +1885,30 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I5" s="12"/>
       <c r="J5" s="5"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I6" s="12"/>
       <c r="J6" s="5"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G7" s="2" t="b">
         <v>1</v>
@@ -1882,10 +1917,10 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G8" s="2" t="b">
         <v>1</v>
@@ -1893,43 +1928,43 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G13" s="2" t="b">
         <v>1</v>
@@ -1937,10 +1972,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>88</v>
+        <v>193</v>
       </c>
       <c r="G14" s="2" t="b">
         <v>1</v>
@@ -1948,21 +1983,18 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" s="2">
-        <v>5</v>
+        <v>194</v>
       </c>
       <c r="F16" s="2">
         <v>100</v>
@@ -1973,10 +2005,10 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="G17" s="2" t="b">
         <v>1</v>
@@ -1984,10 +2016,10 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>92</v>
+        <v>196</v>
       </c>
       <c r="G18" s="2" t="b">
         <v>1</v>
@@ -1995,34 +2027,46 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>93</v>
+        <v>197</v>
+      </c>
+      <c r="G19" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>94</v>
+        <v>198</v>
+      </c>
+      <c r="G20" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>95</v>
+        <v>199</v>
+      </c>
+      <c r="G21" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="2" t="s">
-        <v>31</v>
+        <v>190</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>96</v>
+        <v>200</v>
+      </c>
+      <c r="F22" s="2">
+        <v>100</v>
       </c>
       <c r="G22" s="2" t="b">
         <v>1</v>
@@ -2030,24 +2074,18 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F23" s="2">
-        <v>100</v>
-      </c>
-      <c r="G23" s="2" t="b">
-        <v>1</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>202</v>
       </c>
       <c r="G24" s="2" t="b">
         <v>1</v>
@@ -2055,26 +2093,32 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="2" t="s">
-        <v>34</v>
+        <v>191</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>99</v>
+        <v>203</v>
+      </c>
+      <c r="G25" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>100</v>
+        <v>206</v>
+      </c>
+      <c r="G26" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" t="s">
-        <v>101</v>
+        <v>34</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="G27" s="2" t="b">
         <v>1</v>
@@ -2082,34 +2126,34 @@
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="2" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="2" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="2" t="s">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="C31" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="G31" s="2" t="b">
         <v>1</v>
@@ -2117,10 +2161,10 @@
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="2" t="s">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="G32" s="2" t="b">
         <v>1</v>
@@ -2128,10 +2172,10 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="2" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="C33" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="F33" s="2">
         <v>95</v>
@@ -2142,26 +2186,26 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="2" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="G36" s="2" t="b">
         <v>1</v>
@@ -2169,10 +2213,10 @@
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="F37" s="2">
         <v>95</v>
@@ -2183,26 +2227,26 @@
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B39" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G40" s="2" t="b">
         <v>1</v>
@@ -2210,34 +2254,34 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="2" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="C42" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="C43" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="2" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="C44" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="G44" s="2" t="b">
         <v>1</v>
@@ -2245,10 +2289,10 @@
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="G45" s="2" t="b">
         <v>1</v>
@@ -2256,10 +2300,10 @@
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="G46" s="2" t="b">
         <v>1</v>
@@ -2267,10 +2311,10 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G47" s="2" t="b">
         <v>1</v>
@@ -2278,34 +2322,37 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="2" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="2" t="s">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="C50" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="C51" t="s">
-        <v>138</v>
+        <v>209</v>
+      </c>
+      <c r="G51" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
@@ -2313,23 +2360,23 @@
         <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C53" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" s="2" t="s">
-        <v>205</v>
+        <v>180</v>
       </c>
       <c r="C54" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="G54" s="2" t="b">
         <v>1</v>
@@ -2337,202 +2384,238 @@
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C55" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C56" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B57" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C57" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B58" s="2" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="C58" t="s">
-        <v>175</v>
+        <v>212</v>
+      </c>
+      <c r="G58" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C59" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B60" s="2" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="C60" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B61" s="2" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="C61" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B62" s="2" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="C62" t="s">
-        <v>179</v>
+        <v>155</v>
+      </c>
+      <c r="G62" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B63" s="2" t="s">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="C63" t="s">
-        <v>180</v>
+        <v>156</v>
+      </c>
+      <c r="G63" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B64" s="2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C64" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B65" s="2" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="C65" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B66" s="2" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="C66" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B67" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C67" t="s">
-        <v>184</v>
+        <v>160</v>
+      </c>
+      <c r="G67" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B68" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C68" t="s">
         <v>161</v>
       </c>
-      <c r="C68" t="s">
-        <v>185</v>
+      <c r="G68" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B69" s="2" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="C69" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B70" s="2" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="C70" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B71" s="2" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C71" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B72" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C72" t="s">
-        <v>189</v>
+        <v>165</v>
+      </c>
+      <c r="G72" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B73" s="2" t="s">
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="C73" t="s">
-        <v>144</v>
+        <v>214</v>
+      </c>
+      <c r="G73" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B74" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C74" t="s">
-        <v>145</v>
+        <v>215</v>
+      </c>
+      <c r="G74" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B75" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C75" t="s">
-        <v>146</v>
+        <v>216</v>
+      </c>
+      <c r="G75" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B76" s="2" t="s">
-        <v>141</v>
+        <v>213</v>
       </c>
       <c r="C76" t="s">
-        <v>147</v>
+        <v>217</v>
+      </c>
+      <c r="G76" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B77" s="2" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="C77" t="s">
-        <v>148</v>
+        <v>218</v>
+      </c>
+      <c r="G77" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B78" s="2" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="C78" t="s">
-        <v>149</v>
+        <v>219</v>
+      </c>
+      <c r="G78" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B79" s="2" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="C79" t="s">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="G79" s="2" t="b">
         <v>1</v>
@@ -2540,10 +2623,10 @@
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B80" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C80" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="G80" s="2" t="b">
         <v>1</v>
@@ -2551,10 +2634,10 @@
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B81" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C81" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G81" s="2" t="b">
         <v>1</v>
@@ -2562,10 +2645,10 @@
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B82" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C82" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="G82" s="2" t="b">
         <v>1</v>
@@ -2573,10 +2656,10 @@
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C83" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G83" s="2" t="b">
         <v>1</v>
@@ -2584,10 +2667,10 @@
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B84" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C84" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="G84" s="2" t="b">
         <v>1</v>
@@ -2595,10 +2678,10 @@
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B85" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C85" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="G85" s="2" t="b">
         <v>1</v>
@@ -2606,12 +2689,23 @@
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B86" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C86" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="G86" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B87" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C87" t="s">
+        <v>121</v>
+      </c>
+      <c r="G87" s="2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2650,10 +2744,10 @@
   <sheetData>
     <row r="1" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="C1" s="11"/>
     </row>
@@ -2663,106 +2757,106 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="9" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="N3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="O3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="P3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="222">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="8" type="noConversion"/>
@@ -833,6 +833,10 @@
   </si>
   <si>
     <t>추가 방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1354,7 +1358,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2796,7 +2800,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>148</v>
+        <v>221</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>66</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
@@ -1358,7 +1358,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="5">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="H5" s="5">
         <v>10</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="5">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="H6" s="5">
         <v>10</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="220">
   <si>
     <t>!ID</t>
   </si>
@@ -145,9 +145,6 @@
     <t>SpellVamp_Ratio</t>
   </si>
   <si>
-    <t>DamReduce_Ratio</t>
-  </si>
-  <si>
     <t>AtkSpeed</t>
   </si>
   <si>
@@ -730,83 +727,127 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>KnockBack_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 파워 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 저항 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는 피해 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는 피해 감소</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는 피해 감소</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는 피해 증가</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는 피해 증가</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>KnockBack_Add</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>KnockBack_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>KnockBackResist_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 파워 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1289,11 +1330,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.75" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.75" style="1" bestFit="1" customWidth="1"/>
@@ -1310,17 +1351,17 @@
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>2</v>
@@ -1335,7 +1376,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="6"/>
@@ -1346,7 +1387,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
@@ -1355,10 +1396,10 @@
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>7</v>
@@ -1372,7 +1413,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1389,17 +1430,17 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="2"/>
@@ -1409,7 +1450,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -1421,7 +1462,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -1432,7 +1473,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1440,7 +1481,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1448,7 +1489,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1457,7 +1498,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1465,7 +1506,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G13" s="1" t="b">
         <v>1</v>
@@ -1476,7 +1517,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G14" s="1" t="b">
         <v>1</v>
@@ -1487,15 +1528,15 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -1509,7 +1550,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G17" s="1" t="b">
         <v>1</v>
@@ -1517,10 +1558,10 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G18" s="1" t="b">
         <v>1</v>
@@ -1528,10 +1569,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G19" s="1" t="b">
         <v>1</v>
@@ -1542,7 +1583,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G20" s="1" t="b">
         <v>1</v>
@@ -1550,10 +1591,10 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G21" s="1" t="b">
         <v>1</v>
@@ -1561,10 +1602,10 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F22" s="1">
         <v>100</v>
@@ -1575,10 +1616,10 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
@@ -1586,7 +1627,7 @@
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G24" s="1" t="b">
         <v>1</v>
@@ -1594,10 +1635,10 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G25" s="1" t="b">
         <v>1</v>
@@ -1605,10 +1646,10 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="G26" s="1" t="b">
         <v>1</v>
@@ -1619,7 +1660,7 @@
         <v>22</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G27" s="1" t="b">
         <v>1</v>
@@ -1627,34 +1668,34 @@
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G31" s="1" t="b">
         <v>1</v>
@@ -1662,10 +1703,10 @@
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G32" s="1" t="b">
         <v>1</v>
@@ -1673,10 +1714,10 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F33" s="1">
         <v>95</v>
@@ -1690,15 +1731,15 @@
         <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
@@ -1706,7 +1747,7 @@
         <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G36" s="1" t="b">
         <v>1</v>
@@ -1717,7 +1758,7 @@
         <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F37" s="1">
         <v>95</v>
@@ -1731,7 +1772,7 @@
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
@@ -1739,7 +1780,7 @@
         <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
@@ -1747,7 +1788,7 @@
         <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G40" s="1" t="b">
         <v>1</v>
@@ -1755,34 +1796,34 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G44" s="1" t="b">
         <v>1</v>
@@ -1793,7 +1834,7 @@
         <v>29</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G45" s="1" t="b">
         <v>1</v>
@@ -1804,7 +1845,7 @@
         <v>30</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G46" s="1" t="b">
         <v>1</v>
@@ -1812,10 +1853,10 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>31</v>
+        <v>208</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G47" s="1" t="b">
         <v>1</v>
@@ -1823,34 +1864,43 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>32</v>
+        <v>209</v>
       </c>
       <c r="C48" t="s">
-        <v>78</v>
+        <v>213</v>
+      </c>
+      <c r="G48" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>147</v>
+        <v>210</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>214</v>
+      </c>
+      <c r="G49" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="C50" t="s">
-        <v>93</v>
+        <v>205</v>
+      </c>
+      <c r="G50" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>151</v>
+        <v>211</v>
       </c>
       <c r="C51" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="G51" s="1" t="b">
         <v>1</v>
@@ -1858,107 +1908,107 @@
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>1</v>
+        <v>212</v>
       </c>
       <c r="C52" t="s">
-        <v>80</v>
+        <v>216</v>
+      </c>
+      <c r="G52" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C53" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C54" t="s">
-        <v>176</v>
-      </c>
-      <c r="G54" s="1" t="b">
-        <v>1</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="C55" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="C56" t="s">
-        <v>83</v>
+        <v>176</v>
+      </c>
+      <c r="G56" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
-        <v>178</v>
+        <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>179</v>
+        <v>33</v>
       </c>
       <c r="C58" t="s">
-        <v>180</v>
-      </c>
-      <c r="G58" s="1" t="b">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>175</v>
+      </c>
+      <c r="G59" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="C60" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>111</v>
+        <v>177</v>
       </c>
       <c r="C62" t="s">
-        <v>124</v>
-      </c>
-      <c r="G62" s="1" t="b">
-        <v>1</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="C63" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="G63" s="1" t="b">
         <v>1</v>
@@ -1966,34 +2016,34 @@
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C64" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C65" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C66" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C67" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G67" s="1" t="b">
         <v>1</v>
@@ -2001,10 +2051,10 @@
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C68" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="G68" s="1" t="b">
         <v>1</v>
@@ -2012,34 +2062,34 @@
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="C69" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C70" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C71" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C72" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G72" s="1" t="b">
         <v>1</v>
@@ -2047,10 +2097,10 @@
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C73" t="s">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="G73" s="1" t="b">
         <v>1</v>
@@ -2058,34 +2108,34 @@
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>203</v>
+        <v>107</v>
       </c>
       <c r="C74" t="s">
-        <v>194</v>
+        <v>130</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
       <c r="C75" t="s">
-        <v>195</v>
+        <v>131</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="C76" t="s">
-        <v>196</v>
+        <v>132</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>191</v>
+        <v>118</v>
       </c>
       <c r="C77" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="G77" s="1" t="b">
         <v>1</v>
@@ -2093,45 +2143,45 @@
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="C78" t="s">
-        <v>201</v>
+        <v>181</v>
+      </c>
+      <c r="G78" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C79" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C80" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C81" t="s">
-        <v>200</v>
-      </c>
-      <c r="G81" s="1" t="b">
-        <v>1</v>
+        <v>192</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="C82" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G82" s="1" t="b">
         <v>1</v>
@@ -2139,43 +2189,34 @@
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>38</v>
+        <v>207</v>
       </c>
       <c r="C83" t="s">
-        <v>184</v>
-      </c>
-      <c r="G83" s="1" t="b">
-        <v>1</v>
+        <v>197</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C84" t="s">
-        <v>185</v>
-      </c>
-      <c r="G84" s="1" t="b">
-        <v>1</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>95</v>
+        <v>219</v>
       </c>
       <c r="C85" t="s">
-        <v>186</v>
-      </c>
-      <c r="G85" s="1" t="b">
-        <v>1</v>
+        <v>195</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>96</v>
+        <v>206</v>
       </c>
       <c r="C86" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="G86" s="1" t="b">
         <v>1</v>
@@ -2183,10 +2224,10 @@
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="C87" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G87" s="1" t="b">
         <v>1</v>
@@ -2194,10 +2235,10 @@
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C88" t="s">
-        <v>85</v>
+        <v>183</v>
       </c>
       <c r="G88" s="1" t="b">
         <v>1</v>
@@ -2205,10 +2246,10 @@
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="C89" t="s">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="G89" s="1" t="b">
         <v>1</v>
@@ -2216,10 +2257,10 @@
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>87</v>
+        <v>185</v>
       </c>
       <c r="G90" s="1" t="b">
         <v>1</v>
@@ -2227,10 +2268,10 @@
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>88</v>
+        <v>186</v>
       </c>
       <c r="G91" s="1" t="b">
         <v>1</v>
@@ -2238,10 +2279,10 @@
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="G92" s="1" t="b">
         <v>1</v>
@@ -2249,10 +2290,10 @@
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C93" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G93" s="1" t="b">
         <v>1</v>
@@ -2260,10 +2301,10 @@
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C94" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G94" s="1" t="b">
         <v>1</v>
@@ -2271,12 +2312,67 @@
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C95" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G95" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B96" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C96" t="s">
+        <v>87</v>
+      </c>
+      <c r="G96" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B97" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C97" t="s">
+        <v>88</v>
+      </c>
+      <c r="G97" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B98" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C98" t="s">
+        <v>89</v>
+      </c>
+      <c r="G98" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B99" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C99" t="s">
+        <v>90</v>
+      </c>
+      <c r="G99" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B100" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C100" t="s">
+        <v>91</v>
+      </c>
+      <c r="G100" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2316,10 +2412,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C1" s="7"/>
     </row>
@@ -2329,10 +2425,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>19</v>
@@ -2341,7 +2437,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>23</v>
@@ -2350,97 +2446,97 @@
         <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
@@ -2458,7 +2554,7 @@
         <v>5</v>
       </c>
       <c r="F4" s="1">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G4" s="2">
         <v>500</v>
@@ -2485,10 +2581,10 @@
         <v>100</v>
       </c>
       <c r="O4" s="1">
+        <v>20</v>
+      </c>
+      <c r="P4" s="1">
         <v>10</v>
-      </c>
-      <c r="P4" s="1">
-        <v>0</v>
       </c>
       <c r="Q4" s="1">
         <v>30</v>
@@ -2518,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G5" s="2">
         <v>200</v>
@@ -2548,7 +2644,7 @@
         <v>5</v>
       </c>
       <c r="P5" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q5" s="1">
         <v>10</v>
@@ -2578,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G6" s="2">
         <v>500</v>
@@ -2608,7 +2704,7 @@
         <v>5</v>
       </c>
       <c r="P6" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q6" s="1">
         <v>20</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -1322,7 +1322,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2385,7 +2385,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T38"/>
+  <dimension ref="A1:T40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
@@ -2569,7 +2569,7 @@
         <v>10</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L4" s="1">
         <v>10</v>
@@ -2587,10 +2587,10 @@
         <v>10</v>
       </c>
       <c r="Q4" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="R4" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S4" s="1">
         <v>0</v>
@@ -2601,56 +2601,56 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
-      <c r="B5">
-        <v>1001</v>
+      <c r="B5" s="2">
+        <v>102</v>
       </c>
       <c r="C5" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
-      <c r="E5" s="1">
-        <v>0</v>
+      <c r="E5" s="13">
+        <v>5</v>
       </c>
       <c r="F5" s="1">
         <v>150</v>
       </c>
       <c r="G5" s="2">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H5" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L5" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="M5" s="1">
         <v>50</v>
       </c>
       <c r="N5" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O5" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P5" s="1">
         <v>10</v>
       </c>
       <c r="Q5" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R5" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S5" s="1">
         <v>0</v>
@@ -2661,17 +2661,17 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
-      <c r="B6">
-        <v>10001</v>
+      <c r="B6" s="2">
+        <v>103</v>
       </c>
       <c r="C6" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D6" s="1">
-        <v>50</v>
-      </c>
-      <c r="E6" s="1">
         <v>0</v>
+      </c>
+      <c r="E6" s="13">
+        <v>5</v>
       </c>
       <c r="F6" s="1">
         <v>150</v>
@@ -2680,7 +2680,7 @@
         <v>500</v>
       </c>
       <c r="H6" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -2689,28 +2689,28 @@
         <v>10</v>
       </c>
       <c r="K6" s="1">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="L6" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="M6" s="1">
         <v>50</v>
       </c>
       <c r="N6" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="O6" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P6" s="1">
         <v>10</v>
       </c>
       <c r="Q6" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="R6" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="S6" s="1">
         <v>0</v>
@@ -2721,27 +2721,141 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="B7">
+        <v>1001</v>
+      </c>
+      <c r="C7" s="1">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>150</v>
+      </c>
+      <c r="G7" s="2">
+        <v>200</v>
+      </c>
+      <c r="H7" s="2">
+        <v>10</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="L7" s="1">
+        <v>50</v>
+      </c>
+      <c r="M7" s="1">
+        <v>50</v>
+      </c>
+      <c r="N7" s="1">
+        <v>50</v>
+      </c>
+      <c r="O7" s="1">
+        <v>5</v>
+      </c>
+      <c r="P7" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>10</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="B8">
+        <v>10001</v>
+      </c>
+      <c r="C8" s="1">
+        <v>50</v>
+      </c>
+      <c r="D8" s="1">
+        <v>50</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>150</v>
+      </c>
+      <c r="G8" s="2">
+        <v>500</v>
+      </c>
+      <c r="H8" s="2">
+        <v>10</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>10</v>
+      </c>
+      <c r="K8" s="1">
+        <v>50</v>
+      </c>
+      <c r="L8" s="1">
+        <v>50</v>
+      </c>
+      <c r="M8" s="1">
+        <v>50</v>
+      </c>
+      <c r="N8" s="1">
+        <v>80</v>
+      </c>
+      <c r="O8" s="1">
+        <v>5</v>
+      </c>
+      <c r="P8" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>20</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E9" s="2"/>
+      <c r="A9" s="4"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
       <c r="E10" s="2"/>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D18"/>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D19"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="E12" s="2"/>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D20"/>
@@ -2799,6 +2913,12 @@
     </row>
     <row r="38" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D38"/>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -1035,9 +1035,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1045,6 +1042,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1322,7 +1322,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1353,7 +1353,7 @@
       <c r="A1" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>198</v>
       </c>
       <c r="C1" s="7"/>
@@ -2411,10 +2411,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>105</v>
       </c>
       <c r="C1" s="7"/>
@@ -2550,14 +2550,14 @@
       <c r="D4" s="1">
         <v>0</v>
       </c>
-      <c r="E4" s="13">
-        <v>5</v>
+      <c r="E4" s="12">
+        <v>20</v>
       </c>
       <c r="F4" s="1">
         <v>150</v>
       </c>
       <c r="G4" s="2">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="H4" s="2">
         <v>20</v>
@@ -2587,7 +2587,7 @@
         <v>10</v>
       </c>
       <c r="Q4" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R4" s="1">
         <v>0</v>
@@ -2610,14 +2610,14 @@
       <c r="D5" s="1">
         <v>0</v>
       </c>
-      <c r="E5" s="13">
-        <v>5</v>
+      <c r="E5" s="12">
+        <v>20</v>
       </c>
       <c r="F5" s="1">
         <v>150</v>
       </c>
       <c r="G5" s="2">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="H5" s="2">
         <v>20</v>
@@ -2670,14 +2670,14 @@
       <c r="D6" s="1">
         <v>0</v>
       </c>
-      <c r="E6" s="13">
-        <v>5</v>
+      <c r="E6" s="12">
+        <v>20</v>
       </c>
       <c r="F6" s="1">
         <v>150</v>
       </c>
       <c r="G6" s="2">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="H6" s="2">
         <v>20</v>
@@ -2707,7 +2707,7 @@
         <v>10</v>
       </c>
       <c r="Q6" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R6" s="1">
         <v>0</v>
@@ -2785,10 +2785,10 @@
         <v>10001</v>
       </c>
       <c r="C8" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>50</v>
       </c>
       <c r="L8" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="M8" s="1">
         <v>50</v>
@@ -2841,15 +2841,123 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="B9">
+        <v>10002</v>
+      </c>
+      <c r="C9" s="1">
+        <v>20</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>150</v>
+      </c>
+      <c r="G9" s="2">
+        <v>500</v>
+      </c>
+      <c r="H9" s="2">
+        <v>10</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>10</v>
+      </c>
+      <c r="K9" s="1">
+        <v>50</v>
+      </c>
+      <c r="L9" s="1">
+        <v>5</v>
+      </c>
+      <c r="M9" s="1">
+        <v>50</v>
+      </c>
+      <c r="N9" s="1">
+        <v>80</v>
+      </c>
+      <c r="O9" s="1">
+        <v>5</v>
+      </c>
+      <c r="P9" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>20</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="B10">
+        <v>10003</v>
+      </c>
+      <c r="C10" s="1">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>150</v>
+      </c>
+      <c r="G10" s="2">
+        <v>500</v>
+      </c>
+      <c r="H10" s="2">
+        <v>10</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>10</v>
+      </c>
+      <c r="K10" s="1">
+        <v>50</v>
+      </c>
+      <c r="L10" s="1">
+        <v>5</v>
+      </c>
+      <c r="M10" s="1">
+        <v>50</v>
+      </c>
+      <c r="N10" s="1">
+        <v>80</v>
+      </c>
+      <c r="O10" s="1">
+        <v>5</v>
+      </c>
+      <c r="P10" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>20</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E11" s="2"/>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -145,709 +145,710 @@
     <t>SpellVamp_Ratio</t>
   </si>
   <si>
+    <t>AtkSpeed_Base</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Base</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Accuracy_Base</t>
+  </si>
+  <si>
+    <t>Evasion</t>
+  </si>
+  <si>
+    <t>Evasion_Base</t>
+  </si>
+  <si>
+    <t>DamBoss_Ratio</t>
+  </si>
+  <si>
+    <t>DamNormal_Ratio</t>
+  </si>
+  <si>
+    <t>SkillDam_Ratio</t>
+  </si>
+  <si>
+    <t>NormalDam_Ratio</t>
+  </si>
+  <si>
+    <t>Cooldown_Reduce</t>
+  </si>
+  <si>
+    <t>GoldBonus_Ratio</t>
+  </si>
+  <si>
+    <t>ExpBonus_Ratio</t>
+  </si>
+  <si>
+    <t>ItemDrop_Ratio</t>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 물리 공격력</t>
+  </si>
+  <si>
+    <t>추가 물리 공격력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 최종 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어구 관통 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 마법 공격력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 마법 공격력</t>
+  </si>
+  <si>
+    <t>마법 공격력 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 저항 관통 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 체력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 최대 체력</t>
+  </si>
+  <si>
+    <t>추가 최대 체력</t>
+  </si>
+  <si>
+    <t>최대 체력 최종 증폭 (%)</t>
+  </si>
+  <si>
+    <t>물리 방어력</t>
+  </si>
+  <si>
+    <t>기본 물리 방어력</t>
+  </si>
+  <si>
+    <t>추가 물리 방어력</t>
+  </si>
+  <si>
+    <t>물리 방어력 증가 (%)</t>
+  </si>
+  <si>
+    <t>마법 방어력</t>
+  </si>
+  <si>
+    <t>기본 마법 방어력</t>
+  </si>
+  <si>
+    <t>추가 마법 방어력</t>
+  </si>
+  <si>
+    <t>마법 방어력 증가 (%)</t>
+  </si>
+  <si>
+    <t>초당 체력 회복량</t>
+  </si>
+  <si>
+    <t>기본 초당 체력 회복</t>
+  </si>
+  <si>
+    <t>추가 초당 체력 회복</t>
+  </si>
+  <si>
+    <t>초당 체력 회복 증가 (%)</t>
+  </si>
+  <si>
+    <t>물리 피해 흡혈률 (%)</t>
+  </si>
+  <si>
+    <t>마법 피해 흡혈률 (%)</t>
+  </si>
+  <si>
+    <t>받는 피해 감소 (%)</t>
+  </si>
+  <si>
+    <t>공격 속도</t>
+  </si>
+  <si>
+    <t>기본 공격 속도</t>
+  </si>
+  <si>
+    <t>이동 속도</t>
+  </si>
+  <si>
+    <t>기본 이동 속도</t>
+  </si>
+  <si>
+    <t>명중치</t>
+  </si>
+  <si>
+    <t>기본 명중치</t>
+  </si>
+  <si>
+    <t>추가 명중치</t>
+  </si>
+  <si>
+    <t>보스 몬스터 추가 피해 (%)</t>
+  </si>
+  <si>
+    <t>일반 몬스터 추가 피해 (%)</t>
+  </si>
+  <si>
+    <t>스킬 피해량 증가 (%)</t>
+  </si>
+  <si>
+    <t>일반 공격 피해량 증가 (%)</t>
+  </si>
+  <si>
+    <t>스킬 쿨타임 감소 (%)</t>
+  </si>
+  <si>
+    <t>골드 획득량 증가 (%)</t>
+  </si>
+  <si>
+    <t>경험치 획득량 증가 (%)</t>
+  </si>
+  <si>
+    <t>아이템 드랍률 증가 (%)</t>
+  </si>
+  <si>
+    <t>추가 공격 속도</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 체력 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!EnumTable</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseStat</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 데미지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 데미지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!StatInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 최종 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsRatio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동 속도 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 속도 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>명중치 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 파워 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 저항 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는 피해 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는 피해 감소</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는 피해 감소</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는 피해 증가</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는 피해 증가</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>AtkSpeed</t>
-  </si>
-  <si>
-    <t>AtkSpeed_Base</t>
-  </si>
-  <si>
-    <t>MoveSpeed_Base</t>
-  </si>
-  <si>
-    <t>Accuracy</t>
-  </si>
-  <si>
-    <t>Accuracy_Base</t>
-  </si>
-  <si>
-    <t>Evasion</t>
-  </si>
-  <si>
-    <t>Evasion_Base</t>
-  </si>
-  <si>
-    <t>DamBoss_Ratio</t>
-  </si>
-  <si>
-    <t>DamNormal_Ratio</t>
-  </si>
-  <si>
-    <t>SkillDam_Ratio</t>
-  </si>
-  <si>
-    <t>NormalDam_Ratio</t>
-  </si>
-  <si>
-    <t>Cooldown_Reduce</t>
-  </si>
-  <si>
-    <t>GoldBonus_Ratio</t>
-  </si>
-  <si>
-    <t>ExpBonus_Ratio</t>
-  </si>
-  <si>
-    <t>ItemDrop_Ratio</t>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 물리 공격력</t>
-  </si>
-  <si>
-    <t>추가 물리 공격력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 최종 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 방어구 관통 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 마법 공격력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 마법 공격력</t>
-  </si>
-  <si>
-    <t>마법 공격력 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 저항 관통 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 체력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 최대 체력</t>
-  </si>
-  <si>
-    <t>추가 최대 체력</t>
-  </si>
-  <si>
-    <t>최대 체력 최종 증폭 (%)</t>
-  </si>
-  <si>
-    <t>물리 방어력</t>
-  </si>
-  <si>
-    <t>기본 물리 방어력</t>
-  </si>
-  <si>
-    <t>추가 물리 방어력</t>
-  </si>
-  <si>
-    <t>물리 방어력 증가 (%)</t>
-  </si>
-  <si>
-    <t>마법 방어력</t>
-  </si>
-  <si>
-    <t>기본 마법 방어력</t>
-  </si>
-  <si>
-    <t>추가 마법 방어력</t>
-  </si>
-  <si>
-    <t>마법 방어력 증가 (%)</t>
-  </si>
-  <si>
-    <t>초당 체력 회복량</t>
-  </si>
-  <si>
-    <t>기본 초당 체력 회복</t>
-  </si>
-  <si>
-    <t>추가 초당 체력 회복</t>
-  </si>
-  <si>
-    <t>초당 체력 회복 증가 (%)</t>
-  </si>
-  <si>
-    <t>물리 피해 흡혈률 (%)</t>
-  </si>
-  <si>
-    <t>마법 피해 흡혈률 (%)</t>
-  </si>
-  <si>
-    <t>받는 피해 감소 (%)</t>
-  </si>
-  <si>
-    <t>공격 속도</t>
-  </si>
-  <si>
-    <t>기본 공격 속도</t>
-  </si>
-  <si>
-    <t>이동 속도</t>
-  </si>
-  <si>
-    <t>기본 이동 속도</t>
-  </si>
-  <si>
-    <t>명중치</t>
-  </si>
-  <si>
-    <t>기본 명중치</t>
-  </si>
-  <si>
-    <t>추가 명중치</t>
-  </si>
-  <si>
-    <t>보스 몬스터 추가 피해 (%)</t>
-  </si>
-  <si>
-    <t>일반 몬스터 추가 피해 (%)</t>
-  </si>
-  <si>
-    <t>스킬 피해량 증가 (%)</t>
-  </si>
-  <si>
-    <t>일반 공격 피해량 증가 (%)</t>
-  </si>
-  <si>
-    <t>스킬 쿨타임 감소 (%)</t>
-  </si>
-  <si>
-    <t>골드 획득량 증가 (%)</t>
-  </si>
-  <si>
-    <t>경험치 획득량 증가 (%)</t>
-  </si>
-  <si>
-    <t>아이템 드랍률 증가 (%)</t>
-  </si>
-  <si>
-    <t>추가 공격 속도</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 체력 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!ID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!EnumTable</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseStat</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!StatInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력 최종 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsRatio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동 속도 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 속도 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>명중치 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evasion_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 파워 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는 피해 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는 피해 감소</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는 피해 감소</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는 피해 증가</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는 피해 증가</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Add</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1322,7 +1323,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1351,17 +1352,17 @@
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>2</v>
@@ -1376,7 +1377,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="6"/>
@@ -1387,7 +1388,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
@@ -1396,10 +1397,10 @@
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>7</v>
@@ -1413,7 +1414,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1430,17 +1431,17 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="2"/>
@@ -1450,7 +1451,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -1462,7 +1463,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -1473,7 +1474,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1481,7 +1482,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1489,7 +1490,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1498,7 +1499,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1506,7 +1507,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13" s="1" t="b">
         <v>1</v>
@@ -1517,7 +1518,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G14" s="1" t="b">
         <v>1</v>
@@ -1528,15 +1529,15 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -1550,7 +1551,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G17" s="1" t="b">
         <v>1</v>
@@ -1558,10 +1559,10 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G18" s="1" t="b">
         <v>1</v>
@@ -1569,10 +1570,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G19" s="1" t="b">
         <v>1</v>
@@ -1583,7 +1584,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G20" s="1" t="b">
         <v>1</v>
@@ -1591,10 +1592,10 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G21" s="1" t="b">
         <v>1</v>
@@ -1602,10 +1603,10 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F22" s="1">
         <v>100</v>
@@ -1616,10 +1617,10 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
@@ -1627,7 +1628,7 @@
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G24" s="1" t="b">
         <v>1</v>
@@ -1635,10 +1636,10 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G25" s="1" t="b">
         <v>1</v>
@@ -1646,10 +1647,10 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="G26" s="1" t="b">
         <v>1</v>
@@ -1660,7 +1661,7 @@
         <v>22</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G27" s="1" t="b">
         <v>1</v>
@@ -1668,34 +1669,34 @@
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G31" s="1" t="b">
         <v>1</v>
@@ -1703,10 +1704,10 @@
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G32" s="1" t="b">
         <v>1</v>
@@ -1714,10 +1715,10 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F33" s="1">
         <v>95</v>
@@ -1731,15 +1732,15 @@
         <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
@@ -1747,7 +1748,7 @@
         <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G36" s="1" t="b">
         <v>1</v>
@@ -1758,7 +1759,7 @@
         <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F37" s="1">
         <v>95</v>
@@ -1772,7 +1773,7 @@
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
@@ -1780,7 +1781,7 @@
         <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
@@ -1788,7 +1789,7 @@
         <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G40" s="1" t="b">
         <v>1</v>
@@ -1796,34 +1797,34 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G44" s="1" t="b">
         <v>1</v>
@@ -1834,7 +1835,7 @@
         <v>29</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G45" s="1" t="b">
         <v>1</v>
@@ -1845,7 +1846,7 @@
         <v>30</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G46" s="1" t="b">
         <v>1</v>
@@ -1853,10 +1854,10 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G47" s="1" t="b">
         <v>1</v>
@@ -1864,10 +1865,10 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C48" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G48" s="1" t="b">
         <v>1</v>
@@ -1875,10 +1876,10 @@
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C49" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G49" s="1" t="b">
         <v>1</v>
@@ -1886,10 +1887,10 @@
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G50" s="1" t="b">
         <v>1</v>
@@ -1897,10 +1898,10 @@
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C51" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G51" s="1" t="b">
         <v>1</v>
@@ -1908,10 +1909,10 @@
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C52" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G52" s="1" t="b">
         <v>1</v>
@@ -1919,34 +1920,43 @@
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>31</v>
+        <v>219</v>
       </c>
       <c r="C53" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="G53" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="G54" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C55" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="G55" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G56" s="1" t="b">
         <v>1</v>
@@ -1957,23 +1967,23 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C58" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C59" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G59" s="1" t="b">
         <v>1</v>
@@ -1981,34 +1991,34 @@
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C62" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C63" t="s">
         <v>178</v>
-      </c>
-      <c r="C63" t="s">
-        <v>179</v>
       </c>
       <c r="G63" s="1" t="b">
         <v>1</v>
@@ -2016,34 +2026,34 @@
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C64" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C65" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C66" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C67" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G67" s="1" t="b">
         <v>1</v>
@@ -2051,10 +2061,10 @@
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C68" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G68" s="1" t="b">
         <v>1</v>
@@ -2062,34 +2072,34 @@
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C70" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C71" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C72" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G72" s="1" t="b">
         <v>1</v>
@@ -2097,10 +2107,10 @@
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C73" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G73" s="1" t="b">
         <v>1</v>
@@ -2108,34 +2118,34 @@
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C74" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C75" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C76" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C77" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G77" s="1" t="b">
         <v>1</v>
@@ -2143,10 +2153,10 @@
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C78" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G78" s="1" t="b">
         <v>1</v>
@@ -2154,34 +2164,34 @@
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C79" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C80" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C81" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G82" s="1" t="b">
         <v>1</v>
@@ -2189,34 +2199,34 @@
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C83" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C84" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C85" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C86" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G86" s="1" t="b">
         <v>1</v>
@@ -2224,10 +2234,10 @@
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G87" s="1" t="b">
         <v>1</v>
@@ -2235,10 +2245,10 @@
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C88" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G88" s="1" t="b">
         <v>1</v>
@@ -2246,10 +2256,10 @@
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C89" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G89" s="1" t="b">
         <v>1</v>
@@ -2257,10 +2267,10 @@
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C90" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G90" s="1" t="b">
         <v>1</v>
@@ -2268,10 +2278,10 @@
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C91" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G91" s="1" t="b">
         <v>1</v>
@@ -2279,10 +2289,10 @@
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C92" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G92" s="1" t="b">
         <v>1</v>
@@ -2290,10 +2300,10 @@
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C93" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G93" s="1" t="b">
         <v>1</v>
@@ -2301,10 +2311,10 @@
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C94" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G94" s="1" t="b">
         <v>1</v>
@@ -2312,10 +2322,10 @@
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C95" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G95" s="1" t="b">
         <v>1</v>
@@ -2323,10 +2333,10 @@
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C96" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G96" s="1" t="b">
         <v>1</v>
@@ -2334,10 +2344,10 @@
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C97" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G97" s="1" t="b">
         <v>1</v>
@@ -2345,10 +2355,10 @@
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C98" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G98" s="1" t="b">
         <v>1</v>
@@ -2356,10 +2366,10 @@
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C99" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G99" s="1" t="b">
         <v>1</v>
@@ -2367,10 +2377,10 @@
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C100" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G100" s="1" t="b">
         <v>1</v>
@@ -2412,10 +2422,10 @@
   <sheetData>
     <row r="1" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C1" s="7"/>
     </row>
@@ -2425,10 +2435,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>19</v>
@@ -2437,7 +2447,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>23</v>
@@ -2446,97 +2456,97 @@
         <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
@@ -2569,7 +2579,7 @@
         <v>10</v>
       </c>
       <c r="K4" s="1">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="L4" s="1">
         <v>10</v>
@@ -2629,7 +2639,7 @@
         <v>10</v>
       </c>
       <c r="K5" s="1">
-        <v>400</v>
+        <v>2</v>
       </c>
       <c r="L5" s="1">
         <v>10</v>
@@ -2689,7 +2699,7 @@
         <v>10</v>
       </c>
       <c r="K6" s="1">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="L6" s="1">
         <v>10</v>
@@ -2749,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L7" s="1">
         <v>50</v>
@@ -2809,7 +2819,7 @@
         <v>10</v>
       </c>
       <c r="K8" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L8" s="1">
         <v>5</v>
@@ -2869,7 +2879,7 @@
         <v>10</v>
       </c>
       <c r="K9" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L9" s="1">
         <v>5</v>
@@ -2929,7 +2939,7 @@
         <v>10</v>
       </c>
       <c r="K10" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L10" s="1">
         <v>5</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -396,459 +396,459 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>BreakGage_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 데미지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 데미지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!StatInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 최종 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsRatio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동 속도 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 속도 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>명중치 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 파워 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 저항 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는 피해 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는 피해 감소</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는 피해 감소</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는 피해 증가</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는 피해 증가</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>BreakRecovery</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!StatInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력 최종 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsRatio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동 속도 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 속도 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>명중치 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evasion_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 파워 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는 피해 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는 피해 감소</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는 피해 감소</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는 피해 증가</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는 피해 증가</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1323,7 +1323,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1355,7 +1355,7 @@
         <v>97</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C1" s="7"/>
     </row>
@@ -1377,7 +1377,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="6"/>
@@ -1388,7 +1388,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
@@ -1414,7 +1414,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>48</v>
@@ -1518,7 +1518,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G14" s="1" t="b">
         <v>1</v>
@@ -1534,10 +1534,10 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -1551,7 +1551,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G17" s="1" t="b">
         <v>1</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G18" s="1" t="b">
         <v>1</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G19" s="1" t="b">
         <v>1</v>
@@ -1584,7 +1584,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G20" s="1" t="b">
         <v>1</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G21" s="1" t="b">
         <v>1</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F22" s="1">
         <v>100</v>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
@@ -1628,7 +1628,7 @@
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G24" s="1" t="b">
         <v>1</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G25" s="1" t="b">
         <v>1</v>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="G26" s="1" t="b">
         <v>1</v>
@@ -1661,7 +1661,7 @@
         <v>22</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G27" s="1" t="b">
         <v>1</v>
@@ -1685,7 +1685,7 @@
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C30" t="s">
         <v>59</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s">
         <v>61</v>
@@ -1737,7 +1737,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C35" t="s">
         <v>63</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C41" t="s">
         <v>69</v>
@@ -1805,7 +1805,7 @@
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
         <v>70</v>
@@ -1813,7 +1813,7 @@
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C43" t="s">
         <v>71</v>
@@ -1821,7 +1821,7 @@
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C44" t="s">
         <v>72</v>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C47" t="s">
         <v>75</v>
@@ -1865,10 +1865,10 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C48" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G48" s="1" t="b">
         <v>1</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C49" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G49" s="1" t="b">
         <v>1</v>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C50" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G50" s="1" t="b">
         <v>1</v>
@@ -1898,10 +1898,10 @@
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C51" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G51" s="1" t="b">
         <v>1</v>
@@ -1909,10 +1909,10 @@
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C52" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G52" s="1" t="b">
         <v>1</v>
@@ -1920,7 +1920,7 @@
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C53" t="s">
         <v>76</v>
@@ -1931,7 +1931,7 @@
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C54" t="s">
         <v>77</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C55" t="s">
         <v>91</v>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C56" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G56" s="1" t="b">
         <v>1</v>
@@ -1980,10 +1980,10 @@
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C59" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G59" s="1" t="b">
         <v>1</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C62" t="s">
         <v>82</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C63" t="s">
         <v>177</v>
-      </c>
-      <c r="C63" t="s">
-        <v>178</v>
       </c>
       <c r="G63" s="1" t="b">
         <v>1</v>
@@ -2026,34 +2026,34 @@
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C64" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C65" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C66" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C67" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G67" s="1" t="b">
         <v>1</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C68" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G68" s="1" t="b">
         <v>1</v>
@@ -2072,34 +2072,34 @@
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C69" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C70" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C72" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G72" s="1" t="b">
         <v>1</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G73" s="1" t="b">
         <v>1</v>
@@ -2118,34 +2118,34 @@
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>106</v>
+        <v>219</v>
       </c>
       <c r="C74" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C75" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C76" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C77" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G77" s="1" t="b">
         <v>1</v>
@@ -2153,10 +2153,10 @@
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C78" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G78" s="1" t="b">
         <v>1</v>
@@ -2164,34 +2164,34 @@
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C79" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C81" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G82" s="1" t="b">
         <v>1</v>
@@ -2199,34 +2199,34 @@
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C83" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C84" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C85" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C86" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G86" s="1" t="b">
         <v>1</v>
@@ -2237,7 +2237,7 @@
         <v>35</v>
       </c>
       <c r="C87" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G87" s="1" t="b">
         <v>1</v>
@@ -2248,7 +2248,7 @@
         <v>36</v>
       </c>
       <c r="C88" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G88" s="1" t="b">
         <v>1</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C89" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G89" s="1" t="b">
         <v>1</v>
@@ -2270,7 +2270,7 @@
         <v>93</v>
       </c>
       <c r="C90" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G90" s="1" t="b">
         <v>1</v>
@@ -2281,7 +2281,7 @@
         <v>94</v>
       </c>
       <c r="C91" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G91" s="1" t="b">
         <v>1</v>
@@ -2292,7 +2292,7 @@
         <v>95</v>
       </c>
       <c r="C92" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G92" s="1" t="b">
         <v>1</v>
@@ -2435,10 +2435,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>19</v>
@@ -2456,7 +2456,7 @@
         <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>31</v>
@@ -2468,19 +2468,19 @@
         <v>34</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>36</v>
@@ -2537,10 +2537,10 @@
         <v>105</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="S3" s="6" t="s">
         <v>105</v>
@@ -2827,14 +2827,8 @@
       <c r="M8" s="1">
         <v>50</v>
       </c>
-      <c r="N8" s="1">
-        <v>80</v>
-      </c>
       <c r="O8" s="1">
         <v>5</v>
-      </c>
-      <c r="P8" s="1">
-        <v>10</v>
       </c>
       <c r="Q8" s="1">
         <v>20</v>
@@ -2970,7 +2964,63 @@
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E11" s="2"/>
+      <c r="B11">
+        <v>20001</v>
+      </c>
+      <c r="C11" s="1">
+        <v>50</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>150</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H11" s="2">
+        <v>10</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>10</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2</v>
+      </c>
+      <c r="L11" s="1">
+        <v>5</v>
+      </c>
+      <c r="M11" s="1">
+        <v>50</v>
+      </c>
+      <c r="N11" s="1">
+        <v>100</v>
+      </c>
+      <c r="O11" s="1">
+        <v>5</v>
+      </c>
+      <c r="P11" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>20</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="E12" s="2"/>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -1323,7 +1323,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2579,7 +2579,7 @@
         <v>10</v>
       </c>
       <c r="K4" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L4" s="1">
         <v>10</v>
@@ -2639,7 +2639,7 @@
         <v>10</v>
       </c>
       <c r="K5" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L5" s="1">
         <v>10</v>
@@ -2699,7 +2699,7 @@
         <v>10</v>
       </c>
       <c r="K6" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L6" s="1">
         <v>10</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -1323,7 +1323,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2579,7 +2579,7 @@
         <v>10</v>
       </c>
       <c r="K4" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L4" s="1">
         <v>10</v>
@@ -2639,7 +2639,7 @@
         <v>10</v>
       </c>
       <c r="K5" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L5" s="1">
         <v>10</v>
@@ -2699,7 +2699,7 @@
         <v>10</v>
       </c>
       <c r="K6" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6" s="1">
         <v>10</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -3001,7 +3001,7 @@
         <v>50</v>
       </c>
       <c r="N11" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O11" s="1">
         <v>5</v>
@@ -3023,7 +3023,66 @@
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="E12" s="2"/>
+      <c r="B12">
+        <v>30001</v>
+      </c>
+      <c r="C12" s="1">
+        <v>100</v>
+      </c>
+      <c r="D12" s="1">
+        <v>100</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>150</v>
+      </c>
+      <c r="G12" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H12" s="1">
+        <v>20</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>20</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>5</v>
+      </c>
+      <c r="M12" s="1">
+        <v>50</v>
+      </c>
+      <c r="N12" s="1">
+        <v>200</v>
+      </c>
+      <c r="O12" s="1">
+        <v>20</v>
+      </c>
+      <c r="P12" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>20</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B14"/>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D20"/>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -1323,7 +1323,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2615,13 +2615,13 @@
         <v>102</v>
       </c>
       <c r="C5" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="12">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F5" s="1">
         <v>150</v>
@@ -2639,7 +2639,7 @@
         <v>10</v>
       </c>
       <c r="K5" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" s="1">
         <v>10</v>
@@ -2657,7 +2657,7 @@
         <v>10</v>
       </c>
       <c r="Q5" s="1">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="R5" s="1">
         <v>0</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -1323,7 +1323,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2555,7 +2555,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -2732,7 +2732,7 @@
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7">
-        <v>1001</v>
+        <v>10001</v>
       </c>
       <c r="C7" s="1">
         <v>20</v>
@@ -2762,37 +2762,22 @@
         <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="M7" s="1">
         <v>50</v>
       </c>
-      <c r="N7" s="1">
-        <v>50</v>
-      </c>
       <c r="O7" s="1">
         <v>5</v>
       </c>
-      <c r="P7" s="1">
-        <v>10</v>
-      </c>
       <c r="Q7" s="1">
         <v>10</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-      <c r="T7" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8">
-        <v>10001</v>
+        <v>10002</v>
       </c>
       <c r="C8" s="1">
         <v>20</v>
@@ -2829,24 +2814,12 @@
       </c>
       <c r="O8" s="1">
         <v>5</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>20</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0</v>
-      </c>
-      <c r="T8" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="C9" s="1">
         <v>20</v>
@@ -2881,32 +2854,14 @@
       <c r="M9" s="1">
         <v>50</v>
       </c>
-      <c r="N9" s="1">
-        <v>80</v>
-      </c>
       <c r="O9" s="1">
         <v>5</v>
-      </c>
-      <c r="P9" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>20</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
-      <c r="T9" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10">
-        <v>10003</v>
+        <v>20001</v>
       </c>
       <c r="C10" s="1">
         <v>20</v>
@@ -2965,7 +2920,7 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B11">
-        <v>20001</v>
+        <v>30001</v>
       </c>
       <c r="C11" s="1">
         <v>50</v>
@@ -3024,7 +2979,7 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="B12">
-        <v>30001</v>
+        <v>100001</v>
       </c>
       <c r="C12" s="1">
         <v>100</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
     <sheet name="#StatInfo" sheetId="7" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="252">
   <si>
     <t>!ID</t>
   </si>
@@ -206,10 +206,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>물리 공격력 최종 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>물리 방어구 관통 (%)</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -604,10 +600,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>마법 공격력 최종 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>치명타 확률 (%)</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -849,6 +841,141 @@
   </si>
   <si>
     <t>BreakRecovery</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Base</t>
+  </si>
+  <si>
+    <t>StaminaSteal_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 스테미나</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스테미나 체력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스테미나 체력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 스테미나 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 스테미나 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초당 스테미너 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초당 스테미너 회복</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초당 스테미너 회복</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초당 스테미너 회복 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초당 스테미너 회복 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테미너 흡수 수치</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테미너 흡수 수치 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테미너 흡수 수치 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스테미너 흡수 수치</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스테미너 흡수 수치</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Ratio</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1331,7 +1458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M115"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
@@ -1352,17 +1479,17 @@
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>2</v>
@@ -1377,7 +1504,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="6"/>
@@ -1388,7 +1515,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
@@ -1414,7 +1541,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1438,7 +1565,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>48</v>
@@ -1463,7 +1590,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>50</v>
+        <v>238</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -1474,7 +1601,7 @@
         <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1482,7 +1609,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1490,7 +1617,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1499,7 +1626,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1507,7 +1634,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G13" s="1" t="b">
         <v>1</v>
@@ -1518,7 +1645,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>158</v>
+        <v>237</v>
       </c>
       <c r="G14" s="1" t="b">
         <v>1</v>
@@ -1529,15 +1656,15 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -1551,7 +1678,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G17" s="1" t="b">
         <v>1</v>
@@ -1559,10 +1686,10 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G18" s="1" t="b">
         <v>1</v>
@@ -1570,10 +1697,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G19" s="1" t="b">
         <v>1</v>
@@ -1584,7 +1711,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G20" s="1" t="b">
         <v>1</v>
@@ -1592,10 +1719,10 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G21" s="1" t="b">
         <v>1</v>
@@ -1603,10 +1730,10 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F22" s="1">
         <v>100</v>
@@ -1617,10 +1744,10 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
@@ -1628,7 +1755,7 @@
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G24" s="1" t="b">
         <v>1</v>
@@ -1636,10 +1763,10 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G25" s="1" t="b">
         <v>1</v>
@@ -1647,10 +1774,10 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G26" s="1" t="b">
         <v>1</v>
@@ -1661,7 +1788,7 @@
         <v>22</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G27" s="1" t="b">
         <v>1</v>
@@ -1669,34 +1796,34 @@
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G31" s="1" t="b">
         <v>1</v>
@@ -1704,10 +1831,10 @@
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G32" s="1" t="b">
         <v>1</v>
@@ -1715,10 +1842,10 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F33" s="1">
         <v>95</v>
@@ -1732,15 +1859,15 @@
         <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
@@ -1748,7 +1875,7 @@
         <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G36" s="1" t="b">
         <v>1</v>
@@ -1759,7 +1886,7 @@
         <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F37" s="1">
         <v>95</v>
@@ -1773,7 +1900,7 @@
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
@@ -1781,7 +1908,7 @@
         <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
@@ -1789,7 +1916,7 @@
         <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G40" s="1" t="b">
         <v>1</v>
@@ -1797,34 +1924,34 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G44" s="1" t="b">
         <v>1</v>
@@ -1835,7 +1962,7 @@
         <v>29</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G45" s="1" t="b">
         <v>1</v>
@@ -1846,7 +1973,7 @@
         <v>30</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G46" s="1" t="b">
         <v>1</v>
@@ -1854,10 +1981,10 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G47" s="1" t="b">
         <v>1</v>
@@ -1865,10 +1992,10 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C48" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G48" s="1" t="b">
         <v>1</v>
@@ -1876,10 +2003,10 @@
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G49" s="1" t="b">
         <v>1</v>
@@ -1887,10 +2014,10 @@
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C50" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G50" s="1" t="b">
         <v>1</v>
@@ -1898,10 +2025,10 @@
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C51" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G51" s="1" t="b">
         <v>1</v>
@@ -1909,10 +2036,10 @@
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C52" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G52" s="1" t="b">
         <v>1</v>
@@ -1920,10 +2047,10 @@
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G53" s="1" t="b">
         <v>1</v>
@@ -1931,10 +2058,10 @@
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C54" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G54" s="1" t="b">
         <v>1</v>
@@ -1942,10 +2069,10 @@
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G55" s="1" t="b">
         <v>1</v>
@@ -1953,10 +2080,10 @@
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C56" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G56" s="1" t="b">
         <v>1</v>
@@ -1967,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.3">
@@ -1975,15 +2102,15 @@
         <v>32</v>
       </c>
       <c r="C58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C59" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G59" s="1" t="b">
         <v>1</v>
@@ -1994,7 +2121,7 @@
         <v>33</v>
       </c>
       <c r="C60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
@@ -2002,23 +2129,23 @@
         <v>34</v>
       </c>
       <c r="C61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C62" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C63" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G63" s="1" t="b">
         <v>1</v>
@@ -2026,34 +2153,34 @@
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C64" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C65" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C66" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C67" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G67" s="1" t="b">
         <v>1</v>
@@ -2061,10 +2188,10 @@
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C68" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G68" s="1" t="b">
         <v>1</v>
@@ -2072,34 +2199,34 @@
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C69" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C70" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C71" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C72" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G72" s="1" t="b">
         <v>1</v>
@@ -2107,10 +2234,10 @@
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G73" s="1" t="b">
         <v>1</v>
@@ -2118,34 +2245,34 @@
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C74" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C75" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C76" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C77" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G77" s="1" t="b">
         <v>1</v>
@@ -2153,10 +2280,10 @@
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C78" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G78" s="1" t="b">
         <v>1</v>
@@ -2164,34 +2291,34 @@
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C79" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C80" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C81" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C82" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G82" s="1" t="b">
         <v>1</v>
@@ -2199,34 +2326,34 @@
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C83" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C84" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C85" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C86" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G86" s="1" t="b">
         <v>1</v>
@@ -2234,43 +2361,34 @@
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>35</v>
+        <v>229</v>
       </c>
       <c r="C87" t="s">
-        <v>180</v>
-      </c>
-      <c r="G87" s="1" t="b">
-        <v>1</v>
+        <v>228</v>
       </c>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C88" t="s">
-        <v>181</v>
-      </c>
-      <c r="G88" s="1" t="b">
-        <v>1</v>
+        <v>230</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>178</v>
+        <v>231</v>
       </c>
       <c r="C89" t="s">
-        <v>182</v>
-      </c>
-      <c r="G89" s="1" t="b">
-        <v>1</v>
+        <v>234</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>93</v>
+        <v>250</v>
       </c>
       <c r="C90" t="s">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="G90" s="1" t="b">
         <v>1</v>
@@ -2278,10 +2396,10 @@
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>94</v>
+        <v>232</v>
       </c>
       <c r="C91" t="s">
-        <v>184</v>
+        <v>236</v>
       </c>
       <c r="G91" s="1" t="b">
         <v>1</v>
@@ -2289,43 +2407,34 @@
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>95</v>
+        <v>218</v>
       </c>
       <c r="C92" t="s">
-        <v>185</v>
-      </c>
-      <c r="G92" s="1" t="b">
-        <v>1</v>
+        <v>239</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>37</v>
+        <v>220</v>
       </c>
       <c r="C93" t="s">
-        <v>83</v>
-      </c>
-      <c r="G93" s="1" t="b">
-        <v>1</v>
+        <v>240</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>38</v>
+        <v>219</v>
       </c>
       <c r="C94" t="s">
-        <v>84</v>
-      </c>
-      <c r="G94" s="1" t="b">
-        <v>1</v>
+        <v>241</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>39</v>
+        <v>251</v>
       </c>
       <c r="C95" t="s">
-        <v>85</v>
+        <v>242</v>
       </c>
       <c r="G95" s="1" t="b">
         <v>1</v>
@@ -2333,10 +2442,10 @@
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>40</v>
+        <v>221</v>
       </c>
       <c r="C96" t="s">
-        <v>86</v>
+        <v>243</v>
       </c>
       <c r="G96" s="1" t="b">
         <v>1</v>
@@ -2344,45 +2453,201 @@
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>41</v>
+        <v>222</v>
       </c>
       <c r="C97" t="s">
-        <v>87</v>
-      </c>
-      <c r="G97" s="1" t="b">
-        <v>1</v>
+        <v>244</v>
       </c>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>42</v>
+        <v>224</v>
       </c>
       <c r="C98" t="s">
-        <v>88</v>
-      </c>
-      <c r="G98" s="1" t="b">
-        <v>1</v>
+        <v>247</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>43</v>
+        <v>225</v>
       </c>
       <c r="C99" t="s">
-        <v>89</v>
-      </c>
-      <c r="G99" s="1" t="b">
-        <v>1</v>
+        <v>248</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C100" t="s">
+        <v>246</v>
+      </c>
+      <c r="G100" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B101" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C101" t="s">
+        <v>245</v>
+      </c>
+      <c r="G101" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B102" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C102" t="s">
+        <v>178</v>
+      </c>
+      <c r="G102" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B103" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C103" t="s">
+        <v>179</v>
+      </c>
+      <c r="G103" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B104" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C104" t="s">
+        <v>180</v>
+      </c>
+      <c r="G104" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B105" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C105" t="s">
+        <v>181</v>
+      </c>
+      <c r="G105" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B106" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C106" t="s">
+        <v>182</v>
+      </c>
+      <c r="G106" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B107" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C107" t="s">
+        <v>183</v>
+      </c>
+      <c r="G107" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B108" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C108" t="s">
+        <v>82</v>
+      </c>
+      <c r="G108" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B109" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C109" t="s">
+        <v>83</v>
+      </c>
+      <c r="G109" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B110" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C110" t="s">
+        <v>84</v>
+      </c>
+      <c r="G110" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B111" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C111" t="s">
+        <v>85</v>
+      </c>
+      <c r="G111" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B112" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C112" t="s">
+        <v>86</v>
+      </c>
+      <c r="G112" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B113" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C113" t="s">
+        <v>87</v>
+      </c>
+      <c r="G113" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B114" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C114" t="s">
+        <v>88</v>
+      </c>
+      <c r="G114" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B115" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C100" t="s">
-        <v>90</v>
-      </c>
-      <c r="G100" s="1" t="b">
+      <c r="C115" t="s">
+        <v>89</v>
+      </c>
+      <c r="G115" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2395,7 +2660,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
@@ -2414,31 +2679,31 @@
     <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18.875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="19.25" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="1"/>
+    <col min="17" max="21" width="19.25" style="1" customWidth="1"/>
+    <col min="22" max="22" width="12.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" s="7"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>19</v>
@@ -2447,7 +2712,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>23</v>
@@ -2456,7 +2721,7 @@
         <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>31</v>
@@ -2468,88 +2733,106 @@
         <v>34</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="S2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="W2" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>105</v>
+        <v>249</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="2">
         <v>101</v>
@@ -2603,13 +2886,13 @@
         <v>0</v>
       </c>
       <c r="S4" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="2">
         <v>102</v>
@@ -2663,13 +2946,13 @@
         <v>0</v>
       </c>
       <c r="S5" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="2">
         <v>103</v>
@@ -2723,13 +3006,13 @@
         <v>0</v>
       </c>
       <c r="S6" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7">
         <v>10001</v>
@@ -2774,7 +3057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8">
         <v>10002</v>
@@ -2816,7 +3099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9">
         <v>10003</v>
@@ -2858,7 +3141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10">
         <v>20001</v>
@@ -2911,14 +3194,8 @@
       <c r="R10" s="1">
         <v>0</v>
       </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-      <c r="T10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>30001</v>
       </c>
@@ -2970,14 +3247,8 @@
       <c r="R11" s="1">
         <v>0</v>
       </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-      <c r="T11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>100001</v>
       </c>
@@ -3029,14 +3300,8 @@
       <c r="R12" s="1">
         <v>0</v>
       </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
-      <c r="T12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B14"/>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#StatInfo" sheetId="7" r:id="rId1"/>
@@ -1450,7 +1450,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2865,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="L4" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M4" s="1">
         <v>50</v>
@@ -2925,7 +2925,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M5" s="1">
         <v>50</v>
@@ -2985,7 +2985,7 @@
         <v>3</v>
       </c>
       <c r="L6" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M6" s="1">
         <v>50</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
     <sheet name="#StatInfo" sheetId="7" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="256">
   <si>
     <t>!ID</t>
   </si>
@@ -344,315 +344,647 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>!ID</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!EnumTable</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseStat</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 데미지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 데미지</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!StatInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsRatio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 속도 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>명중치 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 파워 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 저항 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는 피해 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는 피해 감소</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는 피해 감소</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는 피해 증가</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는 피해 증가</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 스테미나</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스테미나 체력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스테미나 체력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 스테미나 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 스테미나 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초당 스테미너 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초당 스테미너 회복</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초당 스테미너 회복</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초당 스테미너 회복 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초당 스테미너 회복 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테미너 흡수 수치</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테미너 흡수 수치 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테미너 흡수 수치 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스테미너 흡수 수치</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스테미너 흡수 수치</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>Block_Base</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>Block_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>Block_Add</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>!ID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!EnumTable</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseStat</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!StatInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsRatio</t>
+    <t>MoveSpeed_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Add</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -660,322 +992,7 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>공격 속도 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>명중치 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evasion_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 파워 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는 피해 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는 피해 감소</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는 피해 감소</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는 피해 증가</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는 피해 증가</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Base</t>
-  </si>
-  <si>
-    <t>StaminaSteal_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 스테미나</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스테미나 체력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스테미나 체력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 스테미나 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 스테미나 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초당 스테미너 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초당 스테미너 회복</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초당 스테미너 회복</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초당 스테미너 회복 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초당 스테미너 회복 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테미너 흡수 수치</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테미너 흡수 수치 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테미너 흡수 수치 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스테미너 흡수 수치</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스테미너 흡수 수치</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Ratio</t>
+    <t>추가 이동 속도 (%)</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1450,7 +1467,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1458,7 +1475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M115"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
@@ -1479,17 +1496,17 @@
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>2</v>
@@ -1504,7 +1521,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="6"/>
@@ -1515,7 +1532,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
@@ -1541,7 +1558,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1565,7 +1582,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>48</v>
@@ -1590,7 +1607,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -1645,7 +1662,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="G14" s="1" t="b">
         <v>1</v>
@@ -1661,10 +1678,10 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -1678,7 +1695,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G17" s="1" t="b">
         <v>1</v>
@@ -1686,10 +1703,10 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>141</v>
+        <v>247</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G18" s="1" t="b">
         <v>1</v>
@@ -1697,10 +1714,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G19" s="1" t="b">
         <v>1</v>
@@ -1711,7 +1728,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G20" s="1" t="b">
         <v>1</v>
@@ -1719,10 +1736,10 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G21" s="1" t="b">
         <v>1</v>
@@ -1730,10 +1747,10 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F22" s="1">
         <v>100</v>
@@ -1744,10 +1761,10 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
@@ -1755,7 +1772,7 @@
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G24" s="1" t="b">
         <v>1</v>
@@ -1763,10 +1780,10 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G25" s="1" t="b">
         <v>1</v>
@@ -1774,10 +1791,10 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G26" s="1" t="b">
         <v>1</v>
@@ -1788,7 +1805,7 @@
         <v>22</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G27" s="1" t="b">
         <v>1</v>
@@ -1796,7 +1813,7 @@
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
         <v>56</v>
@@ -1804,7 +1821,7 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>57</v>
@@ -1812,7 +1829,7 @@
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C30" t="s">
         <v>58</v>
@@ -1820,7 +1837,7 @@
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
         <v>91</v>
@@ -1831,7 +1848,7 @@
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
         <v>59</v>
@@ -1842,7 +1859,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s">
         <v>60</v>
@@ -1864,7 +1881,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C35" t="s">
         <v>62</v>
@@ -1924,7 +1941,7 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C41" t="s">
         <v>68</v>
@@ -1932,7 +1949,7 @@
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
         <v>69</v>
@@ -1940,7 +1957,7 @@
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C43" t="s">
         <v>70</v>
@@ -1948,7 +1965,7 @@
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C44" t="s">
         <v>71</v>
@@ -1981,7 +1998,7 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C47" t="s">
         <v>74</v>
@@ -1992,10 +2009,10 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C48" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G48" s="1" t="b">
         <v>1</v>
@@ -2003,10 +2020,10 @@
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C49" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G49" s="1" t="b">
         <v>1</v>
@@ -2014,10 +2031,10 @@
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C50" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G50" s="1" t="b">
         <v>1</v>
@@ -2025,10 +2042,10 @@
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C51" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G51" s="1" t="b">
         <v>1</v>
@@ -2036,10 +2053,10 @@
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C52" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G52" s="1" t="b">
         <v>1</v>
@@ -2047,7 +2064,7 @@
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C53" t="s">
         <v>75</v>
@@ -2058,7 +2075,7 @@
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C54" t="s">
         <v>76</v>
@@ -2069,7 +2086,7 @@
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C55" t="s">
         <v>90</v>
@@ -2080,10 +2097,10 @@
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C56" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G56" s="1" t="b">
         <v>1</v>
@@ -2099,7 +2116,7 @@
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>32</v>
+        <v>252</v>
       </c>
       <c r="C58" t="s">
         <v>78</v>
@@ -2107,91 +2124,88 @@
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>144</v>
+        <v>253</v>
       </c>
       <c r="C59" t="s">
-        <v>171</v>
-      </c>
-      <c r="G59" s="1" t="b">
-        <v>1</v>
+        <v>255</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>254</v>
+      </c>
+      <c r="G60" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="C62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C63" t="s">
-        <v>175</v>
-      </c>
-      <c r="G63" s="1" t="b">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="C64" t="s">
-        <v>117</v>
+        <v>171</v>
+      </c>
+      <c r="G64" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="C65" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C66" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C67" t="s">
-        <v>120</v>
-      </c>
-      <c r="G67" s="1" t="b">
-        <v>1</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C68" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G68" s="1" t="b">
         <v>1</v>
@@ -2199,45 +2213,45 @@
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="C69" t="s">
-        <v>122</v>
+        <v>119</v>
+      </c>
+      <c r="G69" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="C70" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C71" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
-      </c>
-      <c r="G72" s="1" t="b">
-        <v>1</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G73" s="1" t="b">
         <v>1</v>
@@ -2245,45 +2259,45 @@
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>217</v>
+        <v>110</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>124</v>
+      </c>
+      <c r="G74" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>113</v>
+        <v>211</v>
       </c>
       <c r="C75" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C76" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C77" t="s">
-        <v>130</v>
-      </c>
-      <c r="G77" s="1" t="b">
-        <v>1</v>
+        <v>127</v>
       </c>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C78" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="G78" s="1" t="b">
         <v>1</v>
@@ -2291,45 +2305,48 @@
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>195</v>
+        <v>114</v>
       </c>
       <c r="C79" t="s">
-        <v>186</v>
+        <v>173</v>
+      </c>
+      <c r="G79" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C80" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="C81" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>185</v>
+        <v>246</v>
       </c>
       <c r="C82" t="s">
-        <v>189</v>
-      </c>
-      <c r="G82" s="1" t="b">
-        <v>1</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="C83" t="s">
-        <v>193</v>
+        <v>185</v>
+      </c>
+      <c r="G83" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
@@ -2337,69 +2354,66 @@
         <v>198</v>
       </c>
       <c r="C84" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="C85" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C86" t="s">
-        <v>192</v>
-      </c>
-      <c r="G86" s="1" t="b">
-        <v>1</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="C87" t="s">
-        <v>228</v>
+        <v>188</v>
+      </c>
+      <c r="G87" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>233</v>
+        <v>222</v>
+      </c>
+      <c r="C88" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C89" t="s">
-        <v>234</v>
+        <v>223</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="C90" t="s">
-        <v>235</v>
-      </c>
-      <c r="G90" s="1" t="b">
-        <v>1</v>
+        <v>227</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="C91" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G91" s="1" t="b">
         <v>1</v>
@@ -2407,45 +2421,45 @@
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C92" t="s">
-        <v>239</v>
+        <v>229</v>
+      </c>
+      <c r="G92" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C93" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C94" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="C95" t="s">
-        <v>242</v>
-      </c>
-      <c r="G95" s="1" t="b">
-        <v>1</v>
+        <v>234</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C96" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="G96" s="1" t="b">
         <v>1</v>
@@ -2453,45 +2467,45 @@
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C97" t="s">
-        <v>244</v>
+        <v>236</v>
+      </c>
+      <c r="G97" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C98" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C99" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C100" t="s">
-        <v>246</v>
-      </c>
-      <c r="G100" s="1" t="b">
-        <v>1</v>
+        <v>241</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C101" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="G101" s="1" t="b">
         <v>1</v>
@@ -2499,10 +2513,10 @@
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
-        <v>35</v>
+        <v>220</v>
       </c>
       <c r="C102" t="s">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="G102" s="1" t="b">
         <v>1</v>
@@ -2510,10 +2524,10 @@
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C103" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G103" s="1" t="b">
         <v>1</v>
@@ -2521,10 +2535,10 @@
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
-        <v>176</v>
+        <v>36</v>
       </c>
       <c r="C104" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G104" s="1" t="b">
         <v>1</v>
@@ -2532,10 +2546,10 @@
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="C105" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G105" s="1" t="b">
         <v>1</v>
@@ -2543,10 +2557,10 @@
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C106" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G106" s="1" t="b">
         <v>1</v>
@@ -2554,10 +2568,10 @@
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
-        <v>94</v>
+        <v>250</v>
       </c>
       <c r="C107" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G107" s="1" t="b">
         <v>1</v>
@@ -2565,10 +2579,10 @@
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
-        <v>37</v>
+        <v>251</v>
       </c>
       <c r="C108" t="s">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="G108" s="1" t="b">
         <v>1</v>
@@ -2576,10 +2590,10 @@
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C109" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G109" s="1" t="b">
         <v>1</v>
@@ -2587,10 +2601,10 @@
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C110" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G110" s="1" t="b">
         <v>1</v>
@@ -2598,10 +2612,10 @@
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C111" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G111" s="1" t="b">
         <v>1</v>
@@ -2609,10 +2623,10 @@
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C112" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G112" s="1" t="b">
         <v>1</v>
@@ -2620,10 +2634,10 @@
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C113" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G113" s="1" t="b">
         <v>1</v>
@@ -2631,10 +2645,10 @@
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C114" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G114" s="1" t="b">
         <v>1</v>
@@ -2642,12 +2656,23 @@
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C115" t="s">
+        <v>88</v>
+      </c>
+      <c r="G115" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B116" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C116" t="s">
         <v>89</v>
       </c>
-      <c r="G115" s="1" t="b">
+      <c r="G116" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2660,7 +2685,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W40"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
@@ -2676,34 +2701,34 @@
     <col min="11" max="11" width="14.75" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.75" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="19.25" style="1" customWidth="1"/>
-    <col min="22" max="22" width="12.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="1"/>
+    <col min="17" max="20" width="19.25" style="1" customWidth="1"/>
+    <col min="21" max="21" width="12.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>103</v>
-      </c>
       <c r="C1" s="7"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>19</v>
@@ -2712,7 +2737,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>23</v>
@@ -2721,7 +2746,7 @@
         <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>31</v>
@@ -2733,106 +2758,100 @@
         <v>34</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>197</v>
+        <v>245</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="D3" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>249</v>
+        <v>102</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="2">
         <v>101</v>
@@ -2871,10 +2890,10 @@
         <v>50</v>
       </c>
       <c r="N4" s="1">
+        <v>20</v>
+      </c>
+      <c r="O4" s="1">
         <v>100</v>
-      </c>
-      <c r="O4" s="1">
-        <v>20</v>
       </c>
       <c r="P4" s="1">
         <v>10</v>
@@ -2892,7 +2911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="2">
         <v>102</v>
@@ -2931,10 +2950,10 @@
         <v>50</v>
       </c>
       <c r="N5" s="1">
+        <v>20</v>
+      </c>
+      <c r="O5" s="1">
         <v>100</v>
-      </c>
-      <c r="O5" s="1">
-        <v>20</v>
       </c>
       <c r="P5" s="1">
         <v>10</v>
@@ -2952,7 +2971,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="2">
         <v>103</v>
@@ -2991,10 +3010,10 @@
         <v>50</v>
       </c>
       <c r="N6" s="1">
+        <v>20</v>
+      </c>
+      <c r="O6" s="1">
         <v>100</v>
-      </c>
-      <c r="O6" s="1">
-        <v>20</v>
       </c>
       <c r="P6" s="1">
         <v>10</v>
@@ -3012,7 +3031,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7">
         <v>10001</v>
@@ -3050,14 +3069,14 @@
       <c r="M7" s="1">
         <v>50</v>
       </c>
-      <c r="O7" s="1">
+      <c r="N7" s="1">
         <v>5</v>
       </c>
       <c r="Q7" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8">
         <v>10002</v>
@@ -3095,11 +3114,11 @@
       <c r="M8" s="1">
         <v>50</v>
       </c>
-      <c r="O8" s="1">
+      <c r="N8" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9">
         <v>10003</v>
@@ -3137,11 +3156,11 @@
       <c r="M9" s="1">
         <v>50</v>
       </c>
-      <c r="O9" s="1">
+      <c r="N9" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10">
         <v>20001</v>
@@ -3180,10 +3199,10 @@
         <v>50</v>
       </c>
       <c r="N10" s="1">
+        <v>5</v>
+      </c>
+      <c r="O10" s="1">
         <v>80</v>
-      </c>
-      <c r="O10" s="1">
-        <v>5</v>
       </c>
       <c r="P10" s="1">
         <v>10</v>
@@ -3195,7 +3214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>30001</v>
       </c>
@@ -3233,10 +3252,10 @@
         <v>50</v>
       </c>
       <c r="N11" s="1">
+        <v>5</v>
+      </c>
+      <c r="O11" s="1">
         <v>200</v>
-      </c>
-      <c r="O11" s="1">
-        <v>5</v>
       </c>
       <c r="P11" s="1">
         <v>25</v>
@@ -3248,7 +3267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>100001</v>
       </c>
@@ -3286,10 +3305,10 @@
         <v>50</v>
       </c>
       <c r="N12" s="1">
+        <v>20</v>
+      </c>
+      <c r="O12" s="1">
         <v>200</v>
-      </c>
-      <c r="O12" s="1">
-        <v>20</v>
       </c>
       <c r="P12" s="1">
         <v>25</v>
@@ -3301,7 +3320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B14"/>
     </row>
     <row r="20" spans="4:4" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="257">
   <si>
     <t>!ID</t>
   </si>
@@ -556,443 +556,447 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>ATK</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초치명타 확률 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초 치명타 피해량 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsRatio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 속도 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>명중치 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 회피 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 방어 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백 파워</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 파워 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 저항 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 저항</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는 피해 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는 피해 감소</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는 피해 감소</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는 피해 증가</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는 피해 증가</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 스테미나</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Amp</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스테미나 체력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스테미나 체력</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 스테미나 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 스테미나 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초당 스테미너 회복량</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초당 스테미너 회복</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초당 스테미너 회복</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초당 스테미너 회복 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>초당 스테미너 회복 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테미너 흡수 수치</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테미너 흡수 수치 증폭 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테미너 흡수 수치 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스테미너 흡수 수치</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스테미너 흡수 수치</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Ratio</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동 속도 증가 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 이동 속도 (%)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>HpRecovery_Add</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>ATK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsRatio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 속도 증가 (%)</t>
+    <t>MaxStamina_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Add</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Accuracy_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>명중치 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evasion_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 파워 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는 피해 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는 피해 감소</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는 피해 감소</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는 피해 증가</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는 피해 증가</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 스테미나</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스테미나 체력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스테미나 체력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 스테미나 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 스테미나 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초당 스테미너 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초당 스테미너 회복</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초당 스테미너 회복</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초당 스테미너 회복 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초당 스테미너 회복 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테미너 흡수 수치</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테미너 흡수 수치 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테미너 흡수 수치 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스테미너 흡수 수치</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스테미너 흡수 수치</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evasion_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동 속도 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 이동 속도 (%)</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1499,7 +1503,7 @@
         <v>94</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C1" s="7"/>
     </row>
@@ -1521,7 +1525,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="6"/>
@@ -1558,7 +1562,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1607,7 +1611,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -1662,7 +1666,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G14" s="1" t="b">
         <v>1</v>
@@ -1678,10 +1682,10 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -1695,7 +1699,7 @@
         <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G17" s="1" t="b">
         <v>1</v>
@@ -1703,10 +1707,10 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G18" s="1" t="b">
         <v>1</v>
@@ -1714,10 +1718,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G19" s="1" t="b">
         <v>1</v>
@@ -1728,7 +1732,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G20" s="1" t="b">
         <v>1</v>
@@ -1739,7 +1743,7 @@
         <v>142</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G21" s="1" t="b">
         <v>1</v>
@@ -1747,10 +1751,10 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F22" s="1">
         <v>100</v>
@@ -1761,10 +1765,10 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
@@ -1772,7 +1776,7 @@
         <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G24" s="1" t="b">
         <v>1</v>
@@ -1780,10 +1784,10 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G25" s="1" t="b">
         <v>1</v>
@@ -1791,10 +1795,10 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="G26" s="1" t="b">
         <v>1</v>
@@ -1805,7 +1809,7 @@
         <v>22</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G27" s="1" t="b">
         <v>1</v>
@@ -1859,7 +1863,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C33" t="s">
         <v>60</v>
@@ -1957,7 +1961,7 @@
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>146</v>
+        <v>252</v>
       </c>
       <c r="C43" t="s">
         <v>70</v>
@@ -1998,7 +2002,7 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C47" t="s">
         <v>74</v>
@@ -2009,10 +2013,10 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C48" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G48" s="1" t="b">
         <v>1</v>
@@ -2020,10 +2024,10 @@
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G49" s="1" t="b">
         <v>1</v>
@@ -2031,10 +2035,10 @@
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C50" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G50" s="1" t="b">
         <v>1</v>
@@ -2042,10 +2046,10 @@
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C51" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G51" s="1" t="b">
         <v>1</v>
@@ -2053,10 +2057,10 @@
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C52" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G52" s="1" t="b">
         <v>1</v>
@@ -2064,7 +2068,7 @@
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C53" t="s">
         <v>75</v>
@@ -2100,7 +2104,7 @@
         <v>144</v>
       </c>
       <c r="C56" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G56" s="1" t="b">
         <v>1</v>
@@ -2116,7 +2120,7 @@
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C58" t="s">
         <v>78</v>
@@ -2124,10 +2128,10 @@
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C59" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
@@ -2135,7 +2139,7 @@
         <v>141</v>
       </c>
       <c r="C60" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G60" s="1" t="b">
         <v>1</v>
@@ -2159,7 +2163,7 @@
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="C63" t="s">
         <v>81</v>
@@ -2167,10 +2171,10 @@
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C64" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G64" s="1" t="b">
         <v>1</v>
@@ -2270,7 +2274,7 @@
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C75" t="s">
         <v>125</v>
@@ -2308,7 +2312,7 @@
         <v>114</v>
       </c>
       <c r="C79" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G79" s="1" t="b">
         <v>1</v>
@@ -2316,34 +2320,34 @@
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C80" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C81" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C82" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C83" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G83" s="1" t="b">
         <v>1</v>
@@ -2351,34 +2355,34 @@
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C84" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C85" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C86" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C87" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G87" s="1" t="b">
         <v>1</v>
@@ -2386,34 +2390,34 @@
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C88" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="C90" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C91" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G91" s="1" t="b">
         <v>1</v>
@@ -2421,10 +2425,10 @@
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C92" t="s">
         <v>225</v>
-      </c>
-      <c r="C92" t="s">
-        <v>229</v>
       </c>
       <c r="G92" s="1" t="b">
         <v>1</v>
@@ -2432,34 +2436,34 @@
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C93" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>214</v>
+        <v>254</v>
       </c>
       <c r="C94" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="C95" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C96" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G96" s="1" t="b">
         <v>1</v>
@@ -2467,10 +2471,10 @@
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C97" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G97" s="1" t="b">
         <v>1</v>
@@ -2478,34 +2482,34 @@
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C98" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C99" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C100" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C101" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G101" s="1" t="b">
         <v>1</v>
@@ -2513,10 +2517,10 @@
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C102" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G102" s="1" t="b">
         <v>1</v>
@@ -2527,7 +2531,7 @@
         <v>35</v>
       </c>
       <c r="C103" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G103" s="1" t="b">
         <v>1</v>
@@ -2538,7 +2542,7 @@
         <v>36</v>
       </c>
       <c r="C104" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G104" s="1" t="b">
         <v>1</v>
@@ -2546,10 +2550,10 @@
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C105" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G105" s="1" t="b">
         <v>1</v>
@@ -2560,7 +2564,7 @@
         <v>92</v>
       </c>
       <c r="C106" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G106" s="1" t="b">
         <v>1</v>
@@ -2568,10 +2572,10 @@
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C107" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G107" s="1" t="b">
         <v>1</v>
@@ -2579,10 +2583,10 @@
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C108" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G108" s="1" t="b">
         <v>1</v>
@@ -2764,25 +2768,25 @@
         <v>103</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -2833,16 +2837,16 @@
         <v>102</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="U3" s="6" t="s">
         <v>102</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#StatInfo" sheetId="7" r:id="rId1"/>
     <sheet name="#BaseStat" sheetId="11" r:id="rId2"/>
+    <sheet name="#LevelupStat" sheetId="12" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="278">
   <si>
     <t>!ID</t>
   </si>
@@ -40,976 +41,1065 @@
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>물리 공격력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MinValue</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MaxValue</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!bool</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MATK_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MATK_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MATK_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Pen_Physical</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Pen_Magic</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ATK_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ATK_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate_Add</t>
+  </si>
+  <si>
+    <t>SuperCritDam_Add</t>
+  </si>
+  <si>
+    <t>DEF_Base</t>
+  </si>
+  <si>
+    <t>DEF_Ratio</t>
+  </si>
+  <si>
+    <t>MDEF</t>
+  </si>
+  <si>
+    <t>MDEF_Base</t>
+  </si>
+  <si>
+    <t>MDEF_Add</t>
+  </si>
+  <si>
+    <t>MDEF_Ratio</t>
+  </si>
+  <si>
+    <t>LifeSteal_Ratio</t>
+  </si>
+  <si>
+    <t>SpellVamp_Ratio</t>
+  </si>
+  <si>
+    <t>AtkSpeed_Base</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Base</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Accuracy_Base</t>
+  </si>
+  <si>
+    <t>Evasion</t>
+  </si>
+  <si>
+    <t>Evasion_Base</t>
+  </si>
+  <si>
+    <t>DamBoss_Ratio</t>
+  </si>
+  <si>
+    <t>DamNormal_Ratio</t>
+  </si>
+  <si>
+    <t>SkillDam_Ratio</t>
+  </si>
+  <si>
+    <t>NormalDam_Ratio</t>
+  </si>
+  <si>
+    <t>Cooldown_Reduce</t>
+  </si>
+  <si>
+    <t>GoldBonus_Ratio</t>
+  </si>
+  <si>
+    <t>ExpBonus_Ratio</t>
+  </si>
+  <si>
+    <t>ItemDrop_Ratio</t>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 물리 공격력</t>
+  </si>
+  <si>
+    <t>추가 물리 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어구 관통 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 마법 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 마법 공격력</t>
+  </si>
+  <si>
+    <t>마법 공격력 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 저항 관통 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 체력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 최대 체력</t>
+  </si>
+  <si>
+    <t>추가 최대 체력</t>
+  </si>
+  <si>
+    <t>최대 체력 최종 증폭 (%)</t>
+  </si>
+  <si>
+    <t>물리 방어력</t>
+  </si>
+  <si>
+    <t>기본 물리 방어력</t>
+  </si>
+  <si>
+    <t>추가 물리 방어력</t>
+  </si>
+  <si>
+    <t>물리 방어력 증가 (%)</t>
+  </si>
+  <si>
+    <t>마법 방어력</t>
+  </si>
+  <si>
+    <t>기본 마법 방어력</t>
+  </si>
+  <si>
+    <t>추가 마법 방어력</t>
+  </si>
+  <si>
+    <t>마법 방어력 증가 (%)</t>
+  </si>
+  <si>
+    <t>초당 체력 회복량</t>
+  </si>
+  <si>
+    <t>기본 초당 체력 회복</t>
+  </si>
+  <si>
+    <t>추가 초당 체력 회복</t>
+  </si>
+  <si>
+    <t>초당 체력 회복 증가 (%)</t>
+  </si>
+  <si>
+    <t>물리 피해 흡혈률 (%)</t>
+  </si>
+  <si>
+    <t>마법 피해 흡혈률 (%)</t>
+  </si>
+  <si>
+    <t>받는 피해 감소 (%)</t>
+  </si>
+  <si>
+    <t>공격 속도</t>
+  </si>
+  <si>
+    <t>기본 공격 속도</t>
+  </si>
+  <si>
+    <t>이동 속도</t>
+  </si>
+  <si>
+    <t>기본 이동 속도</t>
+  </si>
+  <si>
+    <t>명중치</t>
+  </si>
+  <si>
+    <t>기본 명중치</t>
+  </si>
+  <si>
+    <t>추가 명중치</t>
+  </si>
+  <si>
+    <t>보스 몬스터 추가 피해 (%)</t>
+  </si>
+  <si>
+    <t>일반 몬스터 추가 피해 (%)</t>
+  </si>
+  <si>
+    <t>스킬 피해량 증가 (%)</t>
+  </si>
+  <si>
+    <t>일반 공격 피해량 증가 (%)</t>
+  </si>
+  <si>
+    <t>스킬 쿨타임 감소 (%)</t>
+  </si>
+  <si>
+    <t>골드 획득량 증가 (%)</t>
+  </si>
+  <si>
+    <t>경험치 획득량 증가 (%)</t>
+  </si>
+  <si>
+    <t>아이템 드랍률 증가 (%)</t>
+  </si>
+  <si>
+    <t>추가 공격 속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 체력 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ID</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!EnumTable</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseStat</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증폭 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증폭 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지 회복량</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지 회복량</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate_Add</t>
-  </si>
-  <si>
-    <t>SuperCritDam_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 확률 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 확률 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 확률 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 피해량 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 피해량 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 피해량 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>초치명타 확률 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초치명타 확률 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초치명타 확률 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>초치명타 피해량 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초치명타 피해량 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초 치명타 피해량 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsRatio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 속도 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>명중치 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 회복량 증폭 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>회피 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 회피 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 회피 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 방어 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 방어 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 파워</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백 파워</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백 파워</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 파워 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백 저항</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백 저항</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 저항 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백 저항</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는 피해 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는 피해 감소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는 피해 감소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는 피해 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는 피해 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 스테미나</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스테미나 체력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스테미나 체력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 스테미나 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 스테미나 증폭 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 증폭 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증폭 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>초당 스테미너 회복량</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 초당 스테미너 회복</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 초당 스테미너 회복</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>초당 스테미너 회복 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>초당 스테미너 회복 증폭 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테미너 흡수 수치</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테미너 흡수 수치 증폭 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테미너 흡수 수치 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스테미너 흡수 수치</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스테미너 흡수 수치</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동 속도 증가 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 이동 속도 (%)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!StatInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Base</t>
+  </si>
+  <si>
+    <t>MaxHP_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>DEF_Base</t>
-  </si>
-  <si>
-    <t>DEF_Ratio</t>
-  </si>
-  <si>
-    <t>MDEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MDEF_Base</t>
-  </si>
-  <si>
-    <t>MDEF_Add</t>
-  </si>
-  <si>
-    <t>MDEF_Ratio</t>
-  </si>
-  <si>
-    <t>LifeSteal_Ratio</t>
-  </si>
-  <si>
-    <t>SpellVamp_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>AtkSpeed_Base</t>
-  </si>
-  <si>
-    <t>MoveSpeed_Base</t>
-  </si>
-  <si>
-    <t>Accuracy</t>
-  </si>
-  <si>
-    <t>Accuracy_Base</t>
-  </si>
-  <si>
-    <t>Evasion</t>
-  </si>
-  <si>
-    <t>Evasion_Base</t>
-  </si>
-  <si>
-    <t>DamBoss_Ratio</t>
-  </si>
-  <si>
-    <t>DamNormal_Ratio</t>
-  </si>
-  <si>
-    <t>SkillDam_Ratio</t>
-  </si>
-  <si>
-    <t>NormalDam_Ratio</t>
-  </si>
-  <si>
-    <t>Cooldown_Reduce</t>
-  </si>
-  <si>
-    <t>GoldBonus_Ratio</t>
-  </si>
-  <si>
-    <t>ExpBonus_Ratio</t>
-  </si>
-  <si>
-    <t>ItemDrop_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+  </si>
+  <si>
+    <t>LevelupStat</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 물리 공격력</t>
-  </si>
-  <si>
-    <t>추가 물리 공격력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 방어구 관통 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 마법 공격력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 마법 공격력</t>
-  </si>
-  <si>
-    <t>마법 공격력 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 저항 관통 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 체력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 최대 체력</t>
-  </si>
-  <si>
-    <t>추가 최대 체력</t>
-  </si>
-  <si>
-    <t>최대 체력 최종 증폭 (%)</t>
-  </si>
-  <si>
-    <t>물리 방어력</t>
-  </si>
-  <si>
-    <t>기본 물리 방어력</t>
-  </si>
-  <si>
-    <t>추가 물리 방어력</t>
-  </si>
-  <si>
-    <t>물리 방어력 증가 (%)</t>
-  </si>
-  <si>
-    <t>마법 방어력</t>
-  </si>
-  <si>
-    <t>기본 마법 방어력</t>
-  </si>
-  <si>
-    <t>추가 마법 방어력</t>
-  </si>
-  <si>
-    <t>마법 방어력 증가 (%)</t>
-  </si>
-  <si>
-    <t>초당 체력 회복량</t>
-  </si>
-  <si>
-    <t>기본 초당 체력 회복</t>
-  </si>
-  <si>
-    <t>추가 초당 체력 회복</t>
-  </si>
-  <si>
-    <t>초당 체력 회복 증가 (%)</t>
-  </si>
-  <si>
-    <t>물리 피해 흡혈률 (%)</t>
-  </si>
-  <si>
-    <t>마법 피해 흡혈률 (%)</t>
-  </si>
-  <si>
-    <t>받는 피해 감소 (%)</t>
-  </si>
-  <si>
-    <t>공격 속도</t>
-  </si>
-  <si>
-    <t>기본 공격 속도</t>
-  </si>
-  <si>
-    <t>이동 속도</t>
-  </si>
-  <si>
-    <t>기본 이동 속도</t>
-  </si>
-  <si>
-    <t>명중치</t>
-  </si>
-  <si>
-    <t>기본 명중치</t>
-  </si>
-  <si>
-    <t>추가 명중치</t>
-  </si>
-  <si>
-    <t>보스 몬스터 추가 피해 (%)</t>
-  </si>
-  <si>
-    <t>일반 몬스터 추가 피해 (%)</t>
-  </si>
-  <si>
-    <t>스킬 피해량 증가 (%)</t>
-  </si>
-  <si>
-    <t>일반 공격 피해량 증가 (%)</t>
-  </si>
-  <si>
-    <t>스킬 쿨타임 감소 (%)</t>
-  </si>
-  <si>
-    <t>골드 획득량 증가 (%)</t>
-  </si>
-  <si>
-    <t>경험치 획득량 증가 (%)</t>
-  </si>
-  <si>
-    <t>아이템 드랍률 증가 (%)</t>
-  </si>
-  <si>
-    <t>추가 공격 속도</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 체력 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!ID</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!EnumTable</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseStat</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 데미지</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!StatInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 확률 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초 치명타 피해량 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsRatio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 속도 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>명중치 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evasion_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 회피 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 방어 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 파워</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 파워 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는 피해 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는 피해 감소</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는 피해 감소</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는 피해 증가</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는 피해 증가</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 스테미나</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Amp</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스테미나 체력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스테미나 체력</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 스테미나 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 스테미나 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초당 스테미너 회복량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초당 스테미너 회복</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초당 스테미너 회복</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초당 스테미너 회복 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>초당 스테미너 회복 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테미너 흡수 수치</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테미너 흡수 수치 증폭 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테미너 흡수 수치 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스테미너 흡수 수치</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스테미너 흡수 수치</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Ratio</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evasion_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동 속도 증가 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 이동 속도 (%)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_4</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_4</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_5</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_5</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1146,54 +1236,57 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1471,7 +1564,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1500,17 +1593,17 @@
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>2</v>
@@ -1525,7 +1618,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="6"/>
@@ -1536,7 +1629,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
@@ -1545,10 +1638,10 @@
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>7</v>
@@ -1562,7 +1655,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1576,20 +1669,20 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>256</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="2"/>
@@ -1599,7 +1692,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -1611,7 +1704,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -1622,15 +1715,15 @@
         <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1638,7 +1731,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1647,7 +1740,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1655,7 +1748,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G13" s="1" t="b">
         <v>1</v>
@@ -1666,7 +1759,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G14" s="1" t="b">
         <v>1</v>
@@ -1677,15 +1770,15 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -1696,10 +1789,10 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G17" s="1" t="b">
         <v>1</v>
@@ -1707,10 +1800,10 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G18" s="1" t="b">
         <v>1</v>
@@ -1718,10 +1811,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G19" s="1" t="b">
         <v>1</v>
@@ -1729,10 +1822,10 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G20" s="1" t="b">
         <v>1</v>
@@ -1740,10 +1833,10 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G21" s="1" t="b">
         <v>1</v>
@@ -1751,10 +1844,10 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F22" s="1">
         <v>100</v>
@@ -1765,18 +1858,18 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G24" s="1" t="b">
         <v>1</v>
@@ -1784,10 +1877,10 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G25" s="1" t="b">
         <v>1</v>
@@ -1795,10 +1888,10 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G26" s="1" t="b">
         <v>1</v>
@@ -1806,10 +1899,10 @@
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G27" s="1" t="b">
         <v>1</v>
@@ -1817,34 +1910,34 @@
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>96</v>
+        <v>258</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G31" s="1" t="b">
         <v>1</v>
@@ -1852,10 +1945,10 @@
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G32" s="1" t="b">
         <v>1</v>
@@ -1863,10 +1956,10 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F33" s="1">
         <v>95</v>
@@ -1877,26 +1970,26 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>23</v>
+        <v>259</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G36" s="1" t="b">
         <v>1</v>
@@ -1904,10 +1997,10 @@
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F37" s="1">
         <v>95</v>
@@ -1918,26 +2011,26 @@
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>26</v>
+        <v>260</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G40" s="1" t="b">
         <v>1</v>
@@ -1945,34 +2038,34 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G44" s="1" t="b">
         <v>1</v>
@@ -1980,10 +2073,10 @@
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G45" s="1" t="b">
         <v>1</v>
@@ -1991,10 +2084,10 @@
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G46" s="1" t="b">
         <v>1</v>
@@ -2002,10 +2095,10 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G47" s="1" t="b">
         <v>1</v>
@@ -2013,10 +2106,10 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C48" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G48" s="1" t="b">
         <v>1</v>
@@ -2024,10 +2117,10 @@
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C49" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G49" s="1" t="b">
         <v>1</v>
@@ -2035,10 +2128,10 @@
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C50" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G50" s="1" t="b">
         <v>1</v>
@@ -2046,10 +2139,10 @@
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C51" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G51" s="1" t="b">
         <v>1</v>
@@ -2057,10 +2150,10 @@
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C52" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G52" s="1" t="b">
         <v>1</v>
@@ -2068,10 +2161,10 @@
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C53" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G53" s="1" t="b">
         <v>1</v>
@@ -2079,10 +2172,10 @@
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>140</v>
+        <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G54" s="1" t="b">
         <v>1</v>
@@ -2090,10 +2183,10 @@
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C55" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G55" s="1" t="b">
         <v>1</v>
@@ -2101,10 +2194,10 @@
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C56" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G56" s="1" t="b">
         <v>1</v>
@@ -2115,31 +2208,31 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C59" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C60" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G60" s="1" t="b">
         <v>1</v>
@@ -2147,34 +2240,34 @@
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C62" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C63" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C64" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G64" s="1" t="b">
         <v>1</v>
@@ -2182,34 +2275,34 @@
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>103</v>
+        <v>262</v>
       </c>
       <c r="C66" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C67" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G68" s="1" t="b">
         <v>1</v>
@@ -2217,10 +2310,10 @@
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C69" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G69" s="1" t="b">
         <v>1</v>
@@ -2228,34 +2321,34 @@
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C70" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C72" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C73" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G73" s="1" t="b">
         <v>1</v>
@@ -2263,10 +2356,10 @@
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C74" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G74" s="1" t="b">
         <v>1</v>
@@ -2274,34 +2367,34 @@
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C75" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C76" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C78" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G78" s="1" t="b">
         <v>1</v>
@@ -2309,10 +2402,10 @@
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C79" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G79" s="1" t="b">
         <v>1</v>
@@ -2320,34 +2413,34 @@
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C80" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C81" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C82" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C83" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G83" s="1" t="b">
         <v>1</v>
@@ -2355,34 +2448,34 @@
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C84" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C85" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C86" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C87" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G87" s="1" t="b">
         <v>1</v>
@@ -2390,34 +2483,34 @@
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C88" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C90" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C91" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G91" s="1" t="b">
         <v>1</v>
@@ -2425,10 +2518,10 @@
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C92" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G92" s="1" t="b">
         <v>1</v>
@@ -2436,34 +2529,34 @@
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C93" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C94" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C95" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C96" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G96" s="1" t="b">
         <v>1</v>
@@ -2471,10 +2564,10 @@
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C97" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G97" s="1" t="b">
         <v>1</v>
@@ -2482,34 +2575,34 @@
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C98" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C99" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C100" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C101" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G101" s="1" t="b">
         <v>1</v>
@@ -2517,10 +2610,10 @@
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C102" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G102" s="1" t="b">
         <v>1</v>
@@ -2528,10 +2621,10 @@
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C103" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G103" s="1" t="b">
         <v>1</v>
@@ -2539,10 +2632,10 @@
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C104" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G104" s="1" t="b">
         <v>1</v>
@@ -2550,10 +2643,10 @@
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C105" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G105" s="1" t="b">
         <v>1</v>
@@ -2561,10 +2654,10 @@
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C106" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G106" s="1" t="b">
         <v>1</v>
@@ -2572,10 +2665,10 @@
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C107" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G107" s="1" t="b">
         <v>1</v>
@@ -2583,10 +2676,10 @@
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C108" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G108" s="1" t="b">
         <v>1</v>
@@ -2594,10 +2687,10 @@
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C109" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G109" s="1" t="b">
         <v>1</v>
@@ -2605,10 +2698,10 @@
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C110" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G110" s="1" t="b">
         <v>1</v>
@@ -2616,10 +2709,10 @@
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C111" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G111" s="1" t="b">
         <v>1</v>
@@ -2627,10 +2720,10 @@
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C112" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G112" s="1" t="b">
         <v>1</v>
@@ -2638,10 +2731,10 @@
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C113" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G113" s="1" t="b">
         <v>1</v>
@@ -2649,10 +2742,10 @@
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C114" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G114" s="1" t="b">
         <v>1</v>
@@ -2660,10 +2753,10 @@
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C115" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G115" s="1" t="b">
         <v>1</v>
@@ -2671,17 +2764,17 @@
     </row>
     <row r="116" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C116" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G116" s="1" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2716,10 +2809,10 @@
   <sheetData>
     <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C1" s="7"/>
     </row>
@@ -2729,130 +2822,130 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="M2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="V2" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -3391,7 +3484,205 @@
       <c r="D40"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="1">
+        <v>101</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F4" s="2">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="J4" s="2">
+        <v>2E-3</v>
+      </c>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>102</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="1">
+        <v>103</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
     <sheet name="#StatInfo" sheetId="7" r:id="rId1"/>
@@ -48,10 +48,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>물리 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>MinValue</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -192,151 +188,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>기본 물리 공격력</t>
-  </si>
-  <si>
-    <t>추가 물리 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 방어구 관통 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 마법 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 마법 공격력</t>
-  </si>
-  <si>
-    <t>마법 공격력 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 저항 관통 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 체력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 최대 체력</t>
-  </si>
-  <si>
-    <t>추가 최대 체력</t>
-  </si>
-  <si>
-    <t>최대 체력 최종 증폭 (%)</t>
-  </si>
-  <si>
-    <t>물리 방어력</t>
-  </si>
-  <si>
-    <t>기본 물리 방어력</t>
-  </si>
-  <si>
-    <t>추가 물리 방어력</t>
-  </si>
-  <si>
-    <t>물리 방어력 증가 (%)</t>
-  </si>
-  <si>
-    <t>마법 방어력</t>
-  </si>
-  <si>
-    <t>기본 마법 방어력</t>
-  </si>
-  <si>
-    <t>추가 마법 방어력</t>
-  </si>
-  <si>
-    <t>마법 방어력 증가 (%)</t>
-  </si>
-  <si>
-    <t>초당 체력 회복량</t>
-  </si>
-  <si>
-    <t>기본 초당 체력 회복</t>
-  </si>
-  <si>
-    <t>추가 초당 체력 회복</t>
-  </si>
-  <si>
-    <t>초당 체력 회복 증가 (%)</t>
-  </si>
-  <si>
-    <t>물리 피해 흡혈률 (%)</t>
-  </si>
-  <si>
-    <t>마법 피해 흡혈률 (%)</t>
-  </si>
-  <si>
-    <t>받는 피해 감소 (%)</t>
-  </si>
-  <si>
-    <t>공격 속도</t>
-  </si>
-  <si>
-    <t>기본 공격 속도</t>
-  </si>
-  <si>
-    <t>이동 속도</t>
-  </si>
-  <si>
-    <t>기본 이동 속도</t>
-  </si>
-  <si>
-    <t>명중치</t>
-  </si>
-  <si>
-    <t>기본 명중치</t>
-  </si>
-  <si>
-    <t>추가 명중치</t>
-  </si>
-  <si>
-    <t>보스 몬스터 추가 피해 (%)</t>
-  </si>
-  <si>
-    <t>일반 몬스터 추가 피해 (%)</t>
-  </si>
-  <si>
-    <t>스킬 피해량 증가 (%)</t>
-  </si>
-  <si>
-    <t>일반 공격 피해량 증가 (%)</t>
-  </si>
-  <si>
-    <t>스킬 쿨타임 감소 (%)</t>
-  </si>
-  <si>
-    <t>골드 획득량 증가 (%)</t>
-  </si>
-  <si>
-    <t>경험치 획득량 증가 (%)</t>
-  </si>
-  <si>
-    <t>아이템 드랍률 증가 (%)</t>
-  </si>
-  <si>
-    <t>추가 공격 속도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 체력 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>Block</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -429,62 +280,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>브레이크 게이지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증폭 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증폭 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지 회복량</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지 회복량</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 회복량 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>HpRecovery</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -573,106 +368,22 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>치명타 확률 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 확률 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 확률 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 피해량 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 피해량 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 피해량 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 확률 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초치명타 확률 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 확률 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>초치명타 피해량 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초치명타 피해량 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>SuperCritDam_Base</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>기본 초 치명타 피해량 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>IsRatio</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>공격 속도 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>Accuracy_Ratio</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>명중치 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>Evasion_Add</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>브레이크 게이지 회복량 증폭 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>회피 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 회피 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 회피 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>방어 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 방어 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 방어 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>BreakRecovery_Base</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -681,38 +392,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>넉백 파워</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 파워</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 파워</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 파워 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백 저항</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백 저항</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백 저항</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>StatInfo</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -737,10 +416,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>받는 피해 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>KnockBackResist_Ratio</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -769,22 +444,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>기본 받는 피해 감소</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는 피해 감소</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는 피해 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는 피해 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>DamageTakenAmp</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -833,10 +492,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>최대 스테미나</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>MaxStamina</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -849,70 +504,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>기본 스테미나 체력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스테미나 체력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 스테미나 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대 스테미나 증폭 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력 증폭 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 증폭 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>초당 스테미너 회복량</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 초당 스테미너 회복</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 초당 스테미너 회복</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>초당 스테미너 회복 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>초당 스테미너 회복 증폭 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테미너 흡수 수치</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테미너 흡수 수치 증폭 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스테미너 흡수 수치 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스테미너 흡수 수치</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스테미너 흡수 수치</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>!int</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -961,14 +552,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>이동 속도 증가 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 이동 속도 (%)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>HpRecovery_Add</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -1079,6 +662,458 @@
   </si>
   <si>
     <t>StatID_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Phys. ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Phys. ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. ATK Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. ATK Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. DEF Penetration</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Mag. ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Mag. ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. ATK Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. ATK Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. RES Penetration</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Critical Rate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Crit Rate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Crit Rate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Critical Damage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Crit DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Crit DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Super Crit Rate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Super Crit Rate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Super Crit Rate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Super Crit DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Super Crit DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Super Crit DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max HP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Max HP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Max HP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max HP Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max HP Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Phys. DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Phys. DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. DEF Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Mag. DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Mag. DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. DEF Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP Regen per Sec</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base HP Regen/Sec</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus HP Regen/Sec</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP Regen Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. Lifesteal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. Lifesteal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage Reduction</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base DMG Reduction</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus DMG Reduction</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMG Taken Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base DMG Taken Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus DMG Taken Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack Speed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Atk Speed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Atk Speed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atk Speed Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Movement Speed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Move Speed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Move Speed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Move Speed Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Accuracy</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Accuracy</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Gauge</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Break Gauge</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Break Gauge</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Gauge Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Gauge Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Damage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Break DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Break DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break DMG Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break DMG Amp.</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Gauge Recovery</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Break Gauge Recovery</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Break Gauge Recovery</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Gauge Recovery Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Gauge Recovery Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knockback Power</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Knockback Power</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Knockback Power</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knockback Power Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knockback Resistance</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Knockback RES</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Knockback RES</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knockback RES Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max Stamina</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Max Stamina</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Max Stamina</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max Stamina Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max Stamina Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina Regen/Sec</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Stamina Regen/Sec</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Stamina Regen/Sec</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina Regen Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina Regen Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina Steal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Stamina Steal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Stamina Steal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina Steal Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina Steal Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Evasion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Evasion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Block</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Block</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus DMG to Bosses</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus DMG to Normal Monsters</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill DMG Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Attack DMG Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Cooldown Reduction</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold Gain Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXP Gain Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item Drop Rate Increase</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1564,7 +1599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1593,32 +1628,32 @@
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>185</v>
+        <v>96</v>
       </c>
       <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="6" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>6</v>
-      </c>
       <c r="G2" s="6" t="s">
-        <v>163</v>
+        <v>91</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="6"/>
@@ -1629,7 +1664,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>254</v>
+        <v>141</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
@@ -1638,13 +1673,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>45</v>
-      </c>
       <c r="G3" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -1655,10 +1690,10 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>4</v>
+        <v>165</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
@@ -1669,30 +1704,30 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>256</v>
+        <v>143</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>166</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>167</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>48</v>
+        <v>168</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -1701,10 +1736,10 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>224</v>
+        <v>169</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -1712,43 +1747,46 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>49</v>
+        <v>170</v>
+      </c>
+      <c r="G9" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>50</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>51</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>53</v>
+        <v>174</v>
       </c>
       <c r="G13" s="1" t="b">
         <v>1</v>
@@ -1756,10 +1794,10 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>223</v>
+        <v>175</v>
       </c>
       <c r="G14" s="1" t="b">
         <v>1</v>
@@ -1767,18 +1805,18 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>54</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="F16" s="1">
         <v>100</v>
@@ -1789,10 +1827,10 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="G17" s="1" t="b">
         <v>1</v>
@@ -1800,10 +1838,10 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="G18" s="1" t="b">
         <v>1</v>
@@ -1811,10 +1849,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="G19" s="1" t="b">
         <v>1</v>
@@ -1822,10 +1860,10 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="G20" s="1" t="b">
         <v>1</v>
@@ -1833,10 +1871,10 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="G21" s="1" t="b">
         <v>1</v>
@@ -1844,10 +1882,10 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="F22" s="1">
         <v>100</v>
@@ -1858,18 +1896,18 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="G24" s="1" t="b">
         <v>1</v>
@@ -1877,10 +1915,10 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="G25" s="1" t="b">
         <v>1</v>
@@ -1888,10 +1926,10 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="G26" s="1" t="b">
         <v>1</v>
@@ -1899,10 +1937,10 @@
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="G27" s="1" t="b">
         <v>1</v>
@@ -1910,34 +1948,34 @@
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>258</v>
+        <v>145</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>56</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>192</v>
       </c>
       <c r="G31" s="1" t="b">
         <v>1</v>
@@ -1945,10 +1983,10 @@
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>193</v>
       </c>
       <c r="G32" s="1" t="b">
         <v>1</v>
@@ -1956,10 +1994,10 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>194</v>
       </c>
       <c r="F33" s="1">
         <v>95</v>
@@ -1970,26 +2008,26 @@
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>259</v>
+        <v>146</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>61</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>197</v>
       </c>
       <c r="G36" s="1" t="b">
         <v>1</v>
@@ -1997,10 +2035,10 @@
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>63</v>
+        <v>198</v>
       </c>
       <c r="F37" s="1">
         <v>95</v>
@@ -2011,26 +2049,26 @@
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>260</v>
+        <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>66</v>
+        <v>201</v>
       </c>
       <c r="G40" s="1" t="b">
         <v>1</v>
@@ -2038,34 +2076,34 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>67</v>
+        <v>202</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="C42" t="s">
-        <v>68</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>249</v>
+        <v>136</v>
       </c>
       <c r="C43" t="s">
-        <v>69</v>
+        <v>204</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>205</v>
       </c>
       <c r="G44" s="1" t="b">
         <v>1</v>
@@ -2073,10 +2111,10 @@
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>71</v>
+        <v>206</v>
       </c>
       <c r="G45" s="1" t="b">
         <v>1</v>
@@ -2084,10 +2122,10 @@
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>72</v>
+        <v>207</v>
       </c>
       <c r="G46" s="1" t="b">
         <v>1</v>
@@ -2095,10 +2133,10 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="C47" t="s">
-        <v>73</v>
+        <v>208</v>
       </c>
       <c r="G47" s="1" t="b">
         <v>1</v>
@@ -2106,10 +2144,10 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>195</v>
+        <v>105</v>
       </c>
       <c r="C48" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="G48" s="1" t="b">
         <v>1</v>
@@ -2117,10 +2155,10 @@
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="C49" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G49" s="1" t="b">
         <v>1</v>
@@ -2128,10 +2166,10 @@
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>203</v>
+        <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="G50" s="1" t="b">
         <v>1</v>
@@ -2139,10 +2177,10 @@
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>197</v>
+        <v>107</v>
       </c>
       <c r="C51" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="G51" s="1" t="b">
         <v>1</v>
@@ -2150,10 +2188,10 @@
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>198</v>
+        <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="G52" s="1" t="b">
         <v>1</v>
@@ -2161,10 +2199,10 @@
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>205</v>
+        <v>111</v>
       </c>
       <c r="C53" t="s">
-        <v>74</v>
+        <v>214</v>
       </c>
       <c r="G53" s="1" t="b">
         <v>1</v>
@@ -2172,10 +2210,10 @@
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>261</v>
+        <v>148</v>
       </c>
       <c r="C54" t="s">
-        <v>75</v>
+        <v>215</v>
       </c>
       <c r="G54" s="1" t="b">
         <v>1</v>
@@ -2183,10 +2221,10 @@
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="C55" t="s">
-        <v>89</v>
+        <v>216</v>
       </c>
       <c r="G55" s="1" t="b">
         <v>1</v>
@@ -2194,10 +2232,10 @@
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="C56" t="s">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="G56" s="1" t="b">
         <v>1</v>
@@ -2208,31 +2246,31 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>76</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>245</v>
+        <v>134</v>
       </c>
       <c r="C58" t="s">
-        <v>77</v>
+        <v>219</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>246</v>
+        <v>135</v>
       </c>
       <c r="C59" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="G60" s="1" t="b">
         <v>1</v>
@@ -2240,34 +2278,34 @@
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C61" t="s">
-        <v>78</v>
+        <v>222</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C62" t="s">
-        <v>79</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>253</v>
+        <v>140</v>
       </c>
       <c r="C63" t="s">
-        <v>80</v>
+        <v>224</v>
       </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>165</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>166</v>
+        <v>225</v>
       </c>
       <c r="G64" s="1" t="b">
         <v>1</v>
@@ -2275,34 +2313,34 @@
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>114</v>
+        <v>226</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>262</v>
+        <v>149</v>
       </c>
       <c r="C66" t="s">
-        <v>115</v>
+        <v>227</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="C67" t="s">
-        <v>116</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="C68" t="s">
-        <v>117</v>
+        <v>229</v>
       </c>
       <c r="G68" s="1" t="b">
         <v>1</v>
@@ -2310,10 +2348,10 @@
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="C69" t="s">
-        <v>118</v>
+        <v>230</v>
       </c>
       <c r="G69" s="1" t="b">
         <v>1</v>
@@ -2321,34 +2359,34 @@
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>119</v>
+        <v>231</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="C71" t="s">
-        <v>120</v>
+        <v>232</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
       <c r="C72" t="s">
-        <v>121</v>
+        <v>233</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="C73" t="s">
-        <v>122</v>
+        <v>234</v>
       </c>
       <c r="G73" s="1" t="b">
         <v>1</v>
@@ -2356,10 +2394,10 @@
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>123</v>
+        <v>235</v>
       </c>
       <c r="G74" s="1" t="b">
         <v>1</v>
@@ -2367,34 +2405,34 @@
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>206</v>
+        <v>112</v>
       </c>
       <c r="C75" t="s">
-        <v>124</v>
+        <v>236</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="C76" t="s">
-        <v>125</v>
+        <v>237</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="C77" t="s">
-        <v>126</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>239</v>
       </c>
       <c r="G78" s="1" t="b">
         <v>1</v>
@@ -2402,10 +2440,10 @@
     </row>
     <row r="79" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="C79" t="s">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="G79" s="1" t="b">
         <v>1</v>
@@ -2413,34 +2451,34 @@
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="C80" t="s">
-        <v>177</v>
+        <v>241</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>187</v>
+        <v>98</v>
       </c>
       <c r="C81" t="s">
-        <v>178</v>
+        <v>242</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>239</v>
+        <v>128</v>
       </c>
       <c r="C82" t="s">
-        <v>179</v>
+        <v>243</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>176</v>
+        <v>95</v>
       </c>
       <c r="C83" t="s">
-        <v>180</v>
+        <v>244</v>
       </c>
       <c r="G83" s="1" t="b">
         <v>1</v>
@@ -2448,34 +2486,34 @@
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>193</v>
+        <v>103</v>
       </c>
       <c r="C84" t="s">
-        <v>184</v>
+        <v>245</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="C85" t="s">
-        <v>181</v>
+        <v>246</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="C86" t="s">
-        <v>182</v>
+        <v>247</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>192</v>
+        <v>102</v>
       </c>
       <c r="C87" t="s">
-        <v>183</v>
+        <v>248</v>
       </c>
       <c r="G87" s="1" t="b">
         <v>1</v>
@@ -2483,34 +2521,34 @@
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>216</v>
+        <v>121</v>
       </c>
       <c r="C88" t="s">
-        <v>215</v>
+        <v>249</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>217</v>
+        <v>122</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>250</v>
+        <v>137</v>
       </c>
       <c r="C90" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>236</v>
+        <v>125</v>
       </c>
       <c r="C91" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="G91" s="1" t="b">
         <v>1</v>
@@ -2518,10 +2556,10 @@
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>218</v>
+        <v>123</v>
       </c>
       <c r="C92" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="G92" s="1" t="b">
         <v>1</v>
@@ -2529,34 +2567,34 @@
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>207</v>
+        <v>113</v>
       </c>
       <c r="C93" t="s">
-        <v>225</v>
+        <v>254</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>251</v>
+        <v>138</v>
       </c>
       <c r="C94" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>252</v>
+        <v>139</v>
       </c>
       <c r="C95" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>237</v>
+        <v>126</v>
       </c>
       <c r="C96" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="G96" s="1" t="b">
         <v>1</v>
@@ -2564,10 +2602,10 @@
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>209</v>
+        <v>115</v>
       </c>
       <c r="C97" t="s">
-        <v>229</v>
+        <v>258</v>
       </c>
       <c r="G97" s="1" t="b">
         <v>1</v>
@@ -2575,34 +2613,34 @@
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>210</v>
+        <v>116</v>
       </c>
       <c r="C98" t="s">
-        <v>230</v>
+        <v>259</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>211</v>
+        <v>117</v>
       </c>
       <c r="C99" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>212</v>
+        <v>118</v>
       </c>
       <c r="C100" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>213</v>
+        <v>119</v>
       </c>
       <c r="C101" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="G101" s="1" t="b">
         <v>1</v>
@@ -2610,10 +2648,10 @@
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
-        <v>214</v>
+        <v>120</v>
       </c>
       <c r="C102" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="G102" s="1" t="b">
         <v>1</v>
@@ -2621,10 +2659,10 @@
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C103" t="s">
-        <v>169</v>
+        <v>264</v>
       </c>
       <c r="G103" s="1" t="b">
         <v>1</v>
@@ -2632,10 +2670,10 @@
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C104" t="s">
-        <v>170</v>
+        <v>265</v>
       </c>
       <c r="G104" s="1" t="b">
         <v>1</v>
@@ -2643,10 +2681,10 @@
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
-        <v>167</v>
+        <v>93</v>
       </c>
       <c r="C105" t="s">
-        <v>171</v>
+        <v>266</v>
       </c>
       <c r="G105" s="1" t="b">
         <v>1</v>
@@ -2654,10 +2692,10 @@
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="C106" t="s">
-        <v>172</v>
+        <v>267</v>
       </c>
       <c r="G106" s="1" t="b">
         <v>1</v>
@@ -2665,10 +2703,10 @@
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="C107" t="s">
-        <v>173</v>
+        <v>268</v>
       </c>
       <c r="G107" s="1" t="b">
         <v>1</v>
@@ -2676,10 +2714,10 @@
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
-        <v>244</v>
+        <v>133</v>
       </c>
       <c r="C108" t="s">
-        <v>174</v>
+        <v>269</v>
       </c>
       <c r="G108" s="1" t="b">
         <v>1</v>
@@ -2687,10 +2725,10 @@
     </row>
     <row r="109" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C109" t="s">
-        <v>81</v>
+        <v>270</v>
       </c>
       <c r="G109" s="1" t="b">
         <v>1</v>
@@ -2698,10 +2736,10 @@
     </row>
     <row r="110" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C110" t="s">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="G110" s="1" t="b">
         <v>1</v>
@@ -2709,10 +2747,10 @@
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C111" t="s">
-        <v>83</v>
+        <v>272</v>
       </c>
       <c r="G111" s="1" t="b">
         <v>1</v>
@@ -2720,10 +2758,10 @@
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C112" t="s">
-        <v>84</v>
+        <v>273</v>
       </c>
       <c r="G112" s="1" t="b">
         <v>1</v>
@@ -2731,10 +2769,10 @@
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C113" t="s">
-        <v>85</v>
+        <v>274</v>
       </c>
       <c r="G113" s="1" t="b">
         <v>1</v>
@@ -2742,10 +2780,10 @@
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C114" t="s">
-        <v>86</v>
+        <v>275</v>
       </c>
       <c r="G114" s="1" t="b">
         <v>1</v>
@@ -2753,10 +2791,10 @@
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C115" t="s">
-        <v>87</v>
+        <v>276</v>
       </c>
       <c r="G115" s="1" t="b">
         <v>1</v>
@@ -2764,10 +2802,10 @@
     </row>
     <row r="116" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C116" t="s">
-        <v>88</v>
+        <v>277</v>
       </c>
       <c r="G116" s="1" t="b">
         <v>1</v>
@@ -2809,10 +2847,10 @@
   <sheetData>
     <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="C1" s="7"/>
     </row>
@@ -2822,130 +2860,130 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q3" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="R3" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>190</v>
-      </c>
       <c r="S3" s="6" t="s">
-        <v>235</v>
+        <v>124</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>235</v>
+        <v>124</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>101</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -3511,10 +3549,10 @@
   <sheetData>
     <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>263</v>
+        <v>150</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>264</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -3523,70 +3561,70 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>277</v>
+        <v>164</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>265</v>
+        <v>152</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>269</v>
+        <v>156</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>270</v>
+        <v>157</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>271</v>
+        <v>158</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>272</v>
+        <v>159</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>273</v>
+        <v>160</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>274</v>
+        <v>161</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>275</v>
+        <v>162</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>276</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>266</v>
+        <v>153</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>267</v>
+        <v>154</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>268</v>
+        <v>155</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>267</v>
+        <v>154</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>268</v>
+        <v>155</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>267</v>
+        <v>154</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>268</v>
+        <v>155</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>267</v>
+        <v>154</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>268</v>
+        <v>155</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>267</v>
+        <v>154</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>268</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -3594,25 +3632,25 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>255</v>
+        <v>142</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>257</v>
+        <v>144</v>
       </c>
       <c r="F4" s="2">
         <v>3</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>259</v>
+        <v>146</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>261</v>
+        <v>148</v>
       </c>
       <c r="J4" s="2">
         <v>2E-3</v>
@@ -3624,25 +3662,25 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>256</v>
+        <v>143</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>257</v>
+        <v>144</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>259</v>
+        <v>146</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J5" s="2">
         <v>0.1</v>
@@ -3655,25 +3693,25 @@
         <v>103</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>257</v>
+        <v>144</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>259</v>
+        <v>146</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6" s="2">
         <v>0.1</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="278">
   <si>
     <t>!ID</t>
   </si>
@@ -653,14 +653,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>StatID_5</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue_5</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>StatID_1</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -1114,6 +1106,14 @@
   </si>
   <si>
     <t>Item Drop Rate Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1599,7 +1599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1607,26 +1607,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.75" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.75" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="6.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.25" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.75" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>47</v>
       </c>
@@ -1635,7 +1636,7 @@
       </c>
       <c r="C1" s="7"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="6" t="s">
         <v>46</v>
@@ -1647,21 +1648,24 @@
         <v>7</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="6"/>
-      <c r="K2" s="2"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="6"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
         <v>141</v>
@@ -1673,1141 +1677,1144 @@
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="6"/>
       <c r="I3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="J3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="H4" s="8"/>
+        <v>163</v>
+      </c>
       <c r="I4" s="8"/>
-      <c r="J4" s="2"/>
+      <c r="J4" s="8"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C5" t="s">
-        <v>166</v>
-      </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+      <c r="J5" s="8"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+      <c r="H7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+      <c r="H8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G9" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="H9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G13" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+      <c r="H13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G14" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+      <c r="H14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F16" s="1">
+        <v>175</v>
+      </c>
+      <c r="G16" s="1">
         <v>100</v>
       </c>
-      <c r="G16" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="H16" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G17" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+      <c r="H17" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G18" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+      <c r="H18" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="G19" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+      <c r="H19" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G20" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+      <c r="H20" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G21" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="H21" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F22" s="1">
+        <v>181</v>
+      </c>
+      <c r="G22" s="1">
         <v>100</v>
       </c>
-      <c r="G22" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="H22" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>185</v>
-      </c>
-      <c r="G24" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+      <c r="H24" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G25" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+      <c r="H25" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>90</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G26" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+      <c r="H26" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G27" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+      <c r="H27" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>145</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>192</v>
-      </c>
-      <c r="G31" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+      <c r="H31" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>193</v>
-      </c>
-      <c r="G32" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+      <c r="H32" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>194</v>
-      </c>
-      <c r="F33" s="1">
+        <v>192</v>
+      </c>
+      <c r="G33" s="1">
         <v>95</v>
       </c>
-      <c r="G33" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="H33" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C34" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>197</v>
-      </c>
-      <c r="G36" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+      <c r="H36" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>198</v>
-      </c>
-      <c r="F37" s="1">
+        <v>196</v>
+      </c>
+      <c r="G37" s="1">
         <v>95</v>
       </c>
-      <c r="G37" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="H37" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>201</v>
-      </c>
-      <c r="G40" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+      <c r="H40" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C42" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C43" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C44" t="s">
-        <v>205</v>
-      </c>
-      <c r="G44" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+      <c r="H44" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>206</v>
-      </c>
-      <c r="G45" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+      <c r="H45" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>207</v>
-      </c>
-      <c r="G46" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+      <c r="H46" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
         <v>104</v>
       </c>
       <c r="C47" t="s">
-        <v>208</v>
-      </c>
-      <c r="G47" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+      <c r="H47" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C48" t="s">
-        <v>209</v>
-      </c>
-      <c r="G48" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+        <v>207</v>
+      </c>
+      <c r="H48" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C49" t="s">
-        <v>210</v>
-      </c>
-      <c r="G49" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+      <c r="H49" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>211</v>
-      </c>
-      <c r="G50" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="H50" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C51" t="s">
-        <v>212</v>
-      </c>
-      <c r="G51" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+      <c r="H51" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>213</v>
-      </c>
-      <c r="G52" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+      <c r="H52" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C53" t="s">
-        <v>214</v>
-      </c>
-      <c r="G53" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+      <c r="H53" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
         <v>148</v>
       </c>
       <c r="C54" t="s">
-        <v>215</v>
-      </c>
-      <c r="G54" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+      <c r="H54" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C55" t="s">
-        <v>216</v>
-      </c>
-      <c r="G55" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+      <c r="H55" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C56" t="s">
-        <v>217</v>
-      </c>
-      <c r="G56" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+      <c r="H56" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C58" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C59" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>221</v>
-      </c>
-      <c r="G60" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+      <c r="H60" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C61" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C62" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C63" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>225</v>
-      </c>
-      <c r="G64" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+      <c r="H64" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C66" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C67" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C68" t="s">
-        <v>229</v>
-      </c>
-      <c r="G68" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+      <c r="H68" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C69" t="s">
-        <v>230</v>
-      </c>
-      <c r="G69" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+      <c r="H69" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C71" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C72" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C73" t="s">
-        <v>234</v>
-      </c>
-      <c r="G73" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+      <c r="H73" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>235</v>
-      </c>
-      <c r="G74" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+      <c r="H74" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C75" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C76" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C77" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C78" t="s">
-        <v>239</v>
-      </c>
-      <c r="G78" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.3">
+        <v>237</v>
+      </c>
+      <c r="H78" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C79" t="s">
-        <v>240</v>
-      </c>
-      <c r="G79" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.3">
+        <v>238</v>
+      </c>
+      <c r="H79" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C80" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C81" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
         <v>128</v>
       </c>
       <c r="C82" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C83" t="s">
-        <v>244</v>
-      </c>
-      <c r="G83" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.3">
+        <v>242</v>
+      </c>
+      <c r="H83" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C84" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.3">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
         <v>99</v>
       </c>
       <c r="C85" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
         <v>110</v>
       </c>
       <c r="C86" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C87" t="s">
-        <v>248</v>
-      </c>
-      <c r="G87" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+      <c r="H87" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
         <v>121</v>
       </c>
       <c r="C88" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
         <v>122</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C90" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C91" t="s">
-        <v>252</v>
-      </c>
-      <c r="G91" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+      <c r="H91" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
         <v>123</v>
       </c>
       <c r="C92" t="s">
-        <v>253</v>
-      </c>
-      <c r="G92" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+      <c r="H92" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
         <v>113</v>
       </c>
       <c r="C93" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C94" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C95" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
         <v>126</v>
       </c>
       <c r="C96" t="s">
-        <v>257</v>
-      </c>
-      <c r="G96" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
+        <v>255</v>
+      </c>
+      <c r="H96" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
         <v>115</v>
       </c>
       <c r="C97" t="s">
-        <v>258</v>
-      </c>
-      <c r="G97" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
+        <v>256</v>
+      </c>
+      <c r="H97" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
         <v>116</v>
       </c>
       <c r="C98" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
         <v>117</v>
       </c>
       <c r="C99" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
         <v>118</v>
       </c>
       <c r="C100" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
         <v>119</v>
       </c>
       <c r="C101" t="s">
-        <v>262</v>
-      </c>
-      <c r="G101" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.3">
+        <v>260</v>
+      </c>
+      <c r="H101" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C102" t="s">
-        <v>263</v>
-      </c>
-      <c r="G102" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+      <c r="H102" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C103" t="s">
-        <v>264</v>
-      </c>
-      <c r="G103" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
+        <v>262</v>
+      </c>
+      <c r="H103" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C104" t="s">
-        <v>265</v>
-      </c>
-      <c r="G104" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+      <c r="H104" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
         <v>93</v>
       </c>
       <c r="C105" t="s">
-        <v>266</v>
-      </c>
-      <c r="G105" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
+        <v>264</v>
+      </c>
+      <c r="H105" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C106" t="s">
-        <v>267</v>
-      </c>
-      <c r="G106" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+      <c r="H106" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B107" s="1" t="s">
         <v>132</v>
       </c>
       <c r="C107" t="s">
-        <v>268</v>
-      </c>
-      <c r="G107" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+      <c r="H107" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B108" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C108" t="s">
-        <v>269</v>
-      </c>
-      <c r="G108" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+      <c r="H108" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B109" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C109" t="s">
-        <v>270</v>
-      </c>
-      <c r="G109" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+      <c r="H109" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B110" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C110" t="s">
-        <v>271</v>
-      </c>
-      <c r="G110" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+      <c r="H110" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B111" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C111" t="s">
-        <v>272</v>
-      </c>
-      <c r="G111" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+      <c r="H111" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B112" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C112" t="s">
-        <v>273</v>
-      </c>
-      <c r="G112" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+      <c r="H112" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B113" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C113" t="s">
-        <v>274</v>
-      </c>
-      <c r="G113" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.3">
+        <v>272</v>
+      </c>
+      <c r="H113" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B114" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C114" t="s">
-        <v>275</v>
-      </c>
-      <c r="G114" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="2:7" x14ac:dyDescent="0.3">
+        <v>273</v>
+      </c>
+      <c r="H114" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B115" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C115" t="s">
-        <v>276</v>
-      </c>
-      <c r="G115" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+      <c r="H115" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B116" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C116" t="s">
-        <v>277</v>
-      </c>
-      <c r="G116" s="1" t="b">
+        <v>275</v>
+      </c>
+      <c r="H116" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3529,7 +3536,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -3542,12 +3549,10 @@
     <col min="8" max="8" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.75" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>150</v>
       </c>
@@ -3555,13 +3560,13 @@
         <v>151</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>152</v>
@@ -3584,14 +3589,8 @@
       <c r="J2" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
         <v>153</v>
@@ -3620,14 +3619,8 @@
       <c r="J3" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>101</v>
       </c>
@@ -3655,9 +3648,8 @@
       <c r="J4" s="2">
         <v>2E-3</v>
       </c>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>102</v>
       </c>
@@ -3685,10 +3677,8 @@
       <c r="J5" s="2">
         <v>0.1</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>103</v>
       </c>
@@ -3716,8 +3706,6 @@
       <c r="J6" s="2">
         <v>0.1</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="286">
   <si>
     <t>!ID</t>
   </si>
@@ -609,512 +609,536 @@
     <t>!Table</t>
   </si>
   <si>
+    <t>StatValue_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!StatInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_4</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_4</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Phys. ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Phys. ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. ATK Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. ATK Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Mag. ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Mag. ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. ATK Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. ATK Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Critical Rate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Crit Rate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Crit Rate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Critical Damage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Crit DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Crit DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Super Crit Rate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Super Crit Rate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Super Crit Rate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Super Crit DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Super Crit DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Super Crit DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max HP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Max HP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Max HP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max HP Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max HP Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Phys. DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Phys. DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. DEF Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Mag. DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Mag. DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. DEF Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP Regen per Sec</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base HP Regen/Sec</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus HP Regen/Sec</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP Regen Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. Lifesteal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. Lifesteal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage Reduction</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base DMG Reduction</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus DMG Reduction</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMG Taken Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base DMG Taken Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus DMG Taken Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack Speed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Atk Speed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Atk Speed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atk Speed Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Movement Speed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Move Speed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Move Speed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Move Speed Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Accuracy</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Accuracy</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Gauge</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Break Gauge</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Break Gauge</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Gauge Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Gauge Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Damage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Break DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Break DMG</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break DMG Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break DMG Amp.</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Gauge Recovery</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Break Gauge Recovery</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Break Gauge Recovery</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Gauge Recovery Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Break Gauge Recovery Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knockback Power</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Knockback Power</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Knockback Power</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knockback Power Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knockback Resistance</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Knockback RES</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Knockback RES</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knockback RES Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max Stamina</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Max Stamina</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Max Stamina</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max Stamina Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Max Stamina Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina Regen/Sec</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Stamina Regen/Sec</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Stamina Regen/Sec</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina Regen Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina Regen Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina Steal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Stamina Steal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Stamina Steal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina Steal Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina Steal Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Evasion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Evasion</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Block</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus Block</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus DMG to Bosses</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonus DMG to Normal Monsters</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill DMG Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Attack DMG Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill Cooldown Reduction</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold Gain Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXP Gain Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item Drop Rate Increase</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mag. RES Penetration</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Phys. DEF Penetration</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>LevelupStat</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>StatValue_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!StatInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue_3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_4</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue_4</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Phys. ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Phys. ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. ATK Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. ATK Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. DEF Penetration</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Mag. ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Mag. ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. ATK Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. ATK Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. RES Penetration</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Critical Rate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Crit Rate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Crit Rate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Critical Damage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Crit DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Crit DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Super Crit Rate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Super Crit Rate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Super Crit Rate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Super Crit DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Super Crit DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Super Crit DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max HP</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Max HP</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Max HP</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max HP Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max HP Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Phys. DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Phys. DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. DEF Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Mag. DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Mag. DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. DEF Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP Regen per Sec</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base HP Regen/Sec</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus HP Regen/Sec</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP Regen Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. Lifesteal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. Lifesteal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage Reduction</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base DMG Reduction</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus DMG Reduction</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DMG Taken Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base DMG Taken Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus DMG Taken Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack Speed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Atk Speed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Atk Speed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Atk Speed Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Movement Speed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Move Speed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Move Speed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Move Speed Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Accuracy</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Accuracy</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Gauge</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Break Gauge</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Break Gauge</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Gauge Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Gauge Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Damage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Break DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Break DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break DMG Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break DMG Amp.</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Gauge Recovery</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Break Gauge Recovery</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Break Gauge Recovery</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Gauge Recovery Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Gauge Recovery Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Knockback Power</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Knockback Power</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Knockback Power</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Knockback Power Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Knockback Resistance</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Knockback RES</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Knockback RES</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Knockback RES Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max Stamina</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Max Stamina</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Max Stamina</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max Stamina Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max Stamina Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stamina Regen/Sec</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Stamina Regen/Sec</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Stamina Regen/Sec</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stamina Regen Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stamina Regen Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stamina Steal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Stamina Steal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Stamina Steal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stamina Steal Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stamina Steal Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evasion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Evasion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Evasion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Block</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Block</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus DMG to Bosses</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus DMG to Normal Monsters</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill DMG Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic Attack DMG Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill Cooldown Reduction</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold Gain Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>EXP Gain Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item Drop Rate Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <t>ItemIcon_Skill_Attack</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Damage</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Critical</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Health</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Defense</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_DamageEnemy</t>
+  </si>
+  <si>
+    <t>ItemIcon_Energy_Blue</t>
+  </si>
+  <si>
+    <t>ItemIcon_Battle</t>
   </si>
 </sst>
 </file>
@@ -1599,7 +1623,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1614,7 +1638,7 @@
     <col min="2" max="2" width="23.75" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.75" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.125" style="1" bestFit="1" customWidth="1"/>
@@ -1648,7 +1672,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>4</v>
@@ -1677,7 +1701,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>43</v>
@@ -1700,7 +1724,10 @@
         <v>83</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -1714,7 +1741,10 @@
         <v>143</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>163</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="2"/>
@@ -1724,7 +1754,10 @@
         <v>75</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="2"/>
@@ -1734,7 +1767,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="H7" s="1" t="b">
         <v>1</v>
@@ -1746,7 +1782,10 @@
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="H8" s="1" t="b">
         <v>1</v>
@@ -1757,7 +1796,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>168</v>
+        <v>276</v>
       </c>
       <c r="H9" s="1" t="b">
         <v>1</v>
@@ -1768,7 +1807,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1776,7 +1815,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1785,7 +1824,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1793,7 +1832,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H13" s="1" t="b">
         <v>1</v>
@@ -1804,7 +1843,7 @@
         <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H14" s="1" t="b">
         <v>1</v>
@@ -1815,7 +1854,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>174</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1823,7 +1862,10 @@
         <v>85</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="G16" s="1">
         <v>100</v>
@@ -1837,7 +1879,10 @@
         <v>17</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="H17" s="1" t="b">
         <v>1</v>
@@ -1848,7 +1893,10 @@
         <v>129</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="H18" s="1" t="b">
         <v>1</v>
@@ -1859,7 +1907,10 @@
         <v>86</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="H19" s="1" t="b">
         <v>1</v>
@@ -1870,7 +1921,10 @@
         <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="H20" s="1" t="b">
         <v>1</v>
@@ -1881,7 +1935,10 @@
         <v>79</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="H21" s="1" t="b">
         <v>1</v>
@@ -1892,7 +1949,10 @@
         <v>87</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="G22" s="1">
         <v>100</v>
@@ -1906,7 +1966,10 @@
         <v>89</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
@@ -1914,7 +1977,10 @@
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>183</v>
+        <v>180</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="H24" s="1" t="b">
         <v>1</v>
@@ -1925,7 +1991,10 @@
         <v>88</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="H25" s="1" t="b">
         <v>1</v>
@@ -1936,7 +2005,10 @@
         <v>90</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="H26" s="1" t="b">
         <v>1</v>
@@ -1947,7 +2019,10 @@
         <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="H27" s="1" t="b">
         <v>1</v>
@@ -1958,7 +2033,10 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>187</v>
+        <v>184</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
@@ -1966,7 +2044,10 @@
         <v>145</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
@@ -1974,7 +2055,10 @@
         <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>189</v>
+        <v>186</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.3">
@@ -1982,7 +2066,10 @@
         <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>190</v>
+        <v>187</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="H31" s="1" t="b">
         <v>1</v>
@@ -1993,7 +2080,10 @@
         <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>191</v>
+        <v>188</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="H32" s="1" t="b">
         <v>1</v>
@@ -2004,7 +2094,10 @@
         <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>192</v>
+        <v>189</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="G33" s="1">
         <v>95</v>
@@ -2018,7 +2111,10 @@
         <v>146</v>
       </c>
       <c r="C34" t="s">
-        <v>193</v>
+        <v>190</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
@@ -2026,7 +2122,10 @@
         <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>194</v>
+        <v>191</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
@@ -2034,7 +2133,10 @@
         <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>195</v>
+        <v>192</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="H36" s="1" t="b">
         <v>1</v>
@@ -2045,7 +2147,10 @@
         <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>196</v>
+        <v>193</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="G37" s="1">
         <v>95</v>
@@ -2059,7 +2164,10 @@
         <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>197</v>
+        <v>194</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
@@ -2067,7 +2175,10 @@
         <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>198</v>
+        <v>195</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
@@ -2075,7 +2186,10 @@
         <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>199</v>
+        <v>196</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="H40" s="1" t="b">
         <v>1</v>
@@ -2086,7 +2200,10 @@
         <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>200</v>
+        <v>197</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
@@ -2094,7 +2211,10 @@
         <v>77</v>
       </c>
       <c r="C42" t="s">
-        <v>201</v>
+        <v>198</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
@@ -2102,7 +2222,10 @@
         <v>136</v>
       </c>
       <c r="C43" t="s">
-        <v>202</v>
+        <v>199</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.3">
@@ -2110,7 +2233,10 @@
         <v>69</v>
       </c>
       <c r="C44" t="s">
-        <v>203</v>
+        <v>200</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="H44" s="1" t="b">
         <v>1</v>
@@ -2121,7 +2247,10 @@
         <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>204</v>
+        <v>201</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>283</v>
       </c>
       <c r="H45" s="1" t="b">
         <v>1</v>
@@ -2132,7 +2261,10 @@
         <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>205</v>
+        <v>202</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>283</v>
       </c>
       <c r="H46" s="1" t="b">
         <v>1</v>
@@ -2143,7 +2275,7 @@
         <v>104</v>
       </c>
       <c r="C47" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H47" s="1" t="b">
         <v>1</v>
@@ -2154,7 +2286,7 @@
         <v>105</v>
       </c>
       <c r="C48" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H48" s="1" t="b">
         <v>1</v>
@@ -2165,7 +2297,7 @@
         <v>106</v>
       </c>
       <c r="C49" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H49" s="1" t="b">
         <v>1</v>
@@ -2176,7 +2308,7 @@
         <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H50" s="1" t="b">
         <v>1</v>
@@ -2187,7 +2319,7 @@
         <v>107</v>
       </c>
       <c r="C51" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H51" s="1" t="b">
         <v>1</v>
@@ -2198,7 +2330,7 @@
         <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H52" s="1" t="b">
         <v>1</v>
@@ -2209,7 +2341,10 @@
         <v>111</v>
       </c>
       <c r="C53" t="s">
-        <v>212</v>
+        <v>209</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="H53" s="1" t="b">
         <v>1</v>
@@ -2220,7 +2355,10 @@
         <v>148</v>
       </c>
       <c r="C54" t="s">
-        <v>213</v>
+        <v>210</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="H54" s="1" t="b">
         <v>1</v>
@@ -2231,7 +2369,10 @@
         <v>80</v>
       </c>
       <c r="C55" t="s">
-        <v>214</v>
+        <v>211</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="H55" s="1" t="b">
         <v>1</v>
@@ -2242,7 +2383,10 @@
         <v>81</v>
       </c>
       <c r="C56" t="s">
-        <v>215</v>
+        <v>212</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="H56" s="1" t="b">
         <v>1</v>
@@ -2253,7 +2397,10 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>216</v>
+        <v>213</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.3">
@@ -2261,7 +2408,10 @@
         <v>134</v>
       </c>
       <c r="C58" t="s">
-        <v>217</v>
+        <v>214</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
@@ -2269,7 +2419,10 @@
         <v>135</v>
       </c>
       <c r="C59" t="s">
-        <v>218</v>
+        <v>215</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
@@ -2277,7 +2430,10 @@
         <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>219</v>
+        <v>216</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="H60" s="1" t="b">
         <v>1</v>
@@ -2288,7 +2444,7 @@
         <v>31</v>
       </c>
       <c r="C61" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.3">
@@ -2296,7 +2452,7 @@
         <v>32</v>
       </c>
       <c r="C62" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.3">
@@ -2304,7 +2460,7 @@
         <v>140</v>
       </c>
       <c r="C63" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.3">
@@ -2312,7 +2468,7 @@
         <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H64" s="1" t="b">
         <v>1</v>
@@ -2323,7 +2479,7 @@
         <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.3">
@@ -2331,7 +2487,7 @@
         <v>149</v>
       </c>
       <c r="C66" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
@@ -2339,7 +2495,7 @@
         <v>57</v>
       </c>
       <c r="C67" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.3">
@@ -2347,7 +2503,7 @@
         <v>58</v>
       </c>
       <c r="C68" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H68" s="1" t="b">
         <v>1</v>
@@ -2358,7 +2514,7 @@
         <v>59</v>
       </c>
       <c r="C69" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H69" s="1" t="b">
         <v>1</v>
@@ -2369,7 +2525,7 @@
         <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.3">
@@ -2377,7 +2533,7 @@
         <v>60</v>
       </c>
       <c r="C71" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
@@ -2385,7 +2541,7 @@
         <v>61</v>
       </c>
       <c r="C72" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
@@ -2393,7 +2549,7 @@
         <v>62</v>
       </c>
       <c r="C73" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H73" s="1" t="b">
         <v>1</v>
@@ -2404,7 +2560,7 @@
         <v>63</v>
       </c>
       <c r="C74" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H74" s="1" t="b">
         <v>1</v>
@@ -2415,7 +2571,7 @@
         <v>112</v>
       </c>
       <c r="C75" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
@@ -2423,7 +2579,7 @@
         <v>64</v>
       </c>
       <c r="C76" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
@@ -2431,7 +2587,7 @@
         <v>65</v>
       </c>
       <c r="C77" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
@@ -2439,7 +2595,7 @@
         <v>66</v>
       </c>
       <c r="C78" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H78" s="1" t="b">
         <v>1</v>
@@ -2450,7 +2606,7 @@
         <v>67</v>
       </c>
       <c r="C79" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H79" s="1" t="b">
         <v>1</v>
@@ -2461,7 +2617,7 @@
         <v>97</v>
       </c>
       <c r="C80" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
@@ -2469,7 +2625,7 @@
         <v>98</v>
       </c>
       <c r="C81" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
@@ -2477,7 +2633,7 @@
         <v>128</v>
       </c>
       <c r="C82" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.3">
@@ -2485,7 +2641,7 @@
         <v>95</v>
       </c>
       <c r="C83" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H83" s="1" t="b">
         <v>1</v>
@@ -2496,7 +2652,7 @@
         <v>103</v>
       </c>
       <c r="C84" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
@@ -2504,7 +2660,7 @@
         <v>99</v>
       </c>
       <c r="C85" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.3">
@@ -2512,7 +2668,7 @@
         <v>110</v>
       </c>
       <c r="C86" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.3">
@@ -2520,7 +2676,7 @@
         <v>102</v>
       </c>
       <c r="C87" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H87" s="1" t="b">
         <v>1</v>
@@ -2531,7 +2687,7 @@
         <v>121</v>
       </c>
       <c r="C88" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
@@ -2539,7 +2695,7 @@
         <v>122</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.3">
@@ -2547,7 +2703,7 @@
         <v>137</v>
       </c>
       <c r="C90" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.3">
@@ -2555,7 +2711,7 @@
         <v>125</v>
       </c>
       <c r="C91" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H91" s="1" t="b">
         <v>1</v>
@@ -2566,7 +2722,7 @@
         <v>123</v>
       </c>
       <c r="C92" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H92" s="1" t="b">
         <v>1</v>
@@ -2577,7 +2733,7 @@
         <v>113</v>
       </c>
       <c r="C93" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.3">
@@ -2585,7 +2741,7 @@
         <v>138</v>
       </c>
       <c r="C94" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.3">
@@ -2593,7 +2749,7 @@
         <v>139</v>
       </c>
       <c r="C95" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.3">
@@ -2601,7 +2757,7 @@
         <v>126</v>
       </c>
       <c r="C96" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H96" s="1" t="b">
         <v>1</v>
@@ -2612,7 +2768,7 @@
         <v>115</v>
       </c>
       <c r="C97" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H97" s="1" t="b">
         <v>1</v>
@@ -2623,7 +2779,7 @@
         <v>116</v>
       </c>
       <c r="C98" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.3">
@@ -2631,7 +2787,7 @@
         <v>117</v>
       </c>
       <c r="C99" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.3">
@@ -2639,7 +2795,7 @@
         <v>118</v>
       </c>
       <c r="C100" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.3">
@@ -2647,7 +2803,7 @@
         <v>119</v>
       </c>
       <c r="C101" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H101" s="1" t="b">
         <v>1</v>
@@ -2658,7 +2814,7 @@
         <v>120</v>
       </c>
       <c r="C102" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H102" s="1" t="b">
         <v>1</v>
@@ -2669,7 +2825,7 @@
         <v>33</v>
       </c>
       <c r="C103" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H103" s="1" t="b">
         <v>1</v>
@@ -2680,7 +2836,7 @@
         <v>34</v>
       </c>
       <c r="C104" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H104" s="1" t="b">
         <v>1</v>
@@ -2691,7 +2847,7 @@
         <v>93</v>
       </c>
       <c r="C105" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H105" s="1" t="b">
         <v>1</v>
@@ -2702,7 +2858,7 @@
         <v>45</v>
       </c>
       <c r="C106" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H106" s="1" t="b">
         <v>1</v>
@@ -2713,7 +2869,7 @@
         <v>132</v>
       </c>
       <c r="C107" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H107" s="1" t="b">
         <v>1</v>
@@ -2724,7 +2880,7 @@
         <v>133</v>
       </c>
       <c r="C108" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H108" s="1" t="b">
         <v>1</v>
@@ -2735,7 +2891,7 @@
         <v>35</v>
       </c>
       <c r="C109" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H109" s="1" t="b">
         <v>1</v>
@@ -2746,7 +2902,7 @@
         <v>36</v>
       </c>
       <c r="C110" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H110" s="1" t="b">
         <v>1</v>
@@ -2757,7 +2913,7 @@
         <v>37</v>
       </c>
       <c r="C111" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H111" s="1" t="b">
         <v>1</v>
@@ -2768,7 +2924,7 @@
         <v>38</v>
       </c>
       <c r="C112" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="H112" s="1" t="b">
         <v>1</v>
@@ -2779,7 +2935,7 @@
         <v>39</v>
       </c>
       <c r="C113" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H113" s="1" t="b">
         <v>1</v>
@@ -2790,7 +2946,7 @@
         <v>40</v>
       </c>
       <c r="C114" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H114" s="1" t="b">
         <v>1</v>
@@ -2801,7 +2957,7 @@
         <v>41</v>
       </c>
       <c r="C115" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H115" s="1" t="b">
         <v>1</v>
@@ -2812,7 +2968,7 @@
         <v>42</v>
       </c>
       <c r="C116" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H116" s="1" t="b">
         <v>1</v>
@@ -3557,7 +3713,7 @@
         <v>150</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>151</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -3566,58 +3722,58 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="E3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="G3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="I3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="267">
   <si>
     <t>!ID</t>
   </si>
@@ -92,1053 +92,983 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>MATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate_Add</t>
+  </si>
+  <si>
+    <t>SuperCritDam_Add</t>
+  </si>
+  <si>
+    <t>DEF_Base</t>
+  </si>
+  <si>
+    <t>DEF_Ratio</t>
+  </si>
+  <si>
+    <t>MDEF</t>
+  </si>
+  <si>
+    <t>MDEF_Base</t>
+  </si>
+  <si>
+    <t>MDEF_Add</t>
+  </si>
+  <si>
+    <t>MDEF_Ratio</t>
+  </si>
+  <si>
+    <t>LifeSteal_Ratio</t>
+  </si>
+  <si>
+    <t>SpellVamp_Ratio</t>
+  </si>
+  <si>
+    <t>AtkSpeed_Base</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Base</t>
+  </si>
+  <si>
+    <t>Accuracy_Base</t>
+  </si>
+  <si>
+    <t>DamBoss_Ratio</t>
+  </si>
+  <si>
+    <t>DamNormal_Ratio</t>
+  </si>
+  <si>
+    <t>GoldBonus_Ratio</t>
+  </si>
+  <si>
+    <t>ExpBonus_Ratio</t>
+  </si>
+  <si>
+    <t>ItemDrop_Ratio</t>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ID</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!EnumTable</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseStat</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MATK_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakDamage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsRatio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!StatInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Base</t>
+  </si>
+  <si>
+    <t>MaxHP_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MDEF_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+  </si>
+  <si>
+    <t>StatValue_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!StatInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_4</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_4</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelupStat</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Attack</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Damage</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Critical</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Health</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Defense</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_DamageEnemy</t>
+  </si>
+  <si>
+    <t>ItemIcon_Energy_Blue</t>
+  </si>
+  <si>
+    <t>ItemIcon_Battle</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>ATK_Ratio</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>MATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate_Add</t>
-  </si>
-  <si>
-    <t>SuperCritDam_Add</t>
-  </si>
-  <si>
-    <t>DEF_Base</t>
-  </si>
-  <si>
-    <t>DEF_Ratio</t>
-  </si>
-  <si>
-    <t>MDEF</t>
-  </si>
-  <si>
-    <t>MDEF_Base</t>
-  </si>
-  <si>
-    <t>MDEF_Add</t>
-  </si>
-  <si>
-    <t>MDEF_Ratio</t>
-  </si>
-  <si>
-    <t>LifeSteal_Ratio</t>
-  </si>
-  <si>
-    <t>SpellVamp_Ratio</t>
-  </si>
-  <si>
-    <t>AtkSpeed_Base</t>
-  </si>
-  <si>
-    <t>MoveSpeed_Base</t>
-  </si>
-  <si>
-    <t>Accuracy</t>
-  </si>
-  <si>
-    <t>Accuracy_Base</t>
-  </si>
-  <si>
-    <t>Evasion</t>
-  </si>
-  <si>
-    <t>Evasion_Base</t>
-  </si>
-  <si>
-    <t>DamBoss_Ratio</t>
-  </si>
-  <si>
-    <t>DamNormal_Ratio</t>
-  </si>
-  <si>
-    <t>SkillDam_Ratio</t>
-  </si>
-  <si>
-    <t>NormalDam_Ratio</t>
-  </si>
-  <si>
-    <t>Cooldown_Reduce</t>
-  </si>
-  <si>
-    <t>GoldBonus_Ratio</t>
-  </si>
-  <si>
-    <t>ExpBonus_Ratio</t>
-  </si>
-  <si>
-    <t>ItemDrop_Ratio</t>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!ID</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!EnumTable</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseStat</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage_Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MATK_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakDamage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsRatio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evasion_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evasion_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!StatInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Base</t>
-  </si>
-  <si>
-    <t>ATK_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Base</t>
-  </si>
-  <si>
-    <t>MaxHP_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MDEF_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-  </si>
-  <si>
-    <t>StatValue_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!StatInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue_3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_4</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue_4</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Phys. ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Phys. ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. ATK Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. ATK Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Mag. ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Mag. ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. ATK Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. ATK Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Critical Rate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Crit Rate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Crit Rate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Critical Damage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Crit DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Crit DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Super Crit Rate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Super Crit Rate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Super Crit Rate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Super Crit DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Super Crit DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Super Crit DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max HP</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Max HP</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Max HP</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max HP Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max HP Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Phys. DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Phys. DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. DEF Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Mag. DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Mag. DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. DEF Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP Regen per Sec</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base HP Regen/Sec</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus HP Regen/Sec</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HP Regen Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. Lifesteal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. Lifesteal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage Reduction</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base DMG Reduction</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus DMG Reduction</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DMG Taken Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base DMG Taken Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus DMG Taken Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack Speed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Atk Speed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Atk Speed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Atk Speed Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Movement Speed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Move Speed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Move Speed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Move Speed Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Accuracy</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Accuracy</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Gauge</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Break Gauge</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Break Gauge</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Gauge Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Gauge Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Damage</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Break DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Break DMG</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break DMG Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break DMG Amp.</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Gauge Recovery</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Break Gauge Recovery</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Break Gauge Recovery</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Gauge Recovery Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Break Gauge Recovery Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Knockback Power</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Knockback Power</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Knockback Power</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Knockback Power Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Knockback Resistance</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Knockback RES</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Knockback RES</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Knockback RES Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max Stamina</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Max Stamina</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Max Stamina</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max Stamina Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Max Stamina Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stamina Regen/Sec</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Stamina Regen/Sec</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Stamina Regen/Sec</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stamina Regen Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stamina Regen Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stamina Steal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Stamina Steal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Stamina Steal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stamina Steal Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stamina Steal Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evasion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Evasion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Evasion</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Block</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus Block</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus DMG to Bosses</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bonus DMG to Normal Monsters</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill DMG Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic Attack DMG Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill Cooldown Reduction</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold Gain Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>EXP Gain Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item Drop Rate Increase</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mag. RES Penetration</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Phys. DEF Penetration</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelupStat</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Attack</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Damage</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Critical</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Health</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Defense</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_DamageEnemy</t>
-  </si>
-  <si>
-    <t>ItemIcon_Energy_Blue</t>
-  </si>
-  <si>
-    <t>ItemIcon_Battle</t>
+    <t>물리 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 물리 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 물리 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 마법 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 마법 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 방어력 관통</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어력 관통</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>극 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 극 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 극 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>극 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 극 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 극 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대체력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 최대체력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 최대체력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대체력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대체력 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 물리 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 물리 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 마법 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 마법 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 방어력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 체력 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 체력 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 재생 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는데미지 감소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는데미지 감소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는데미지 감소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 공격속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 공격속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격속도 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 이동속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 이동속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동속도 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 재생 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 재생 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백파워</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백파워</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백파워</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백파워 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백저항</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백저항</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백저항</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백저항 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스태미나</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스태미나</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스태미나 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스태미나 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 재생 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 재생 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 생명력흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 생명력흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스태미나 흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스태미나 흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 흡수 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 흡수 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 방어 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 방어 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스몬스터 데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반몬스터 데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드 획득량 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>경험치 획득량 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 드랍확률 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1623,7 +1553,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1631,7 +1561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N116"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
@@ -1653,17 +1583,17 @@
   <sheetData>
     <row r="1" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C1" s="7"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>2</v>
@@ -1672,7 +1602,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>273</v>
+        <v>150</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>4</v>
@@ -1681,7 +1611,7 @@
         <v>5</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="6"/>
@@ -1692,7 +1622,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
@@ -1701,13 +1631,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>274</v>
+        <v>151</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>6</v>
@@ -1721,13 +1651,13 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>278</v>
+        <v>153</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -1738,39 +1668,39 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>278</v>
+        <v>153</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>278</v>
+        <v>153</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>163</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>278</v>
+        <v>153</v>
       </c>
       <c r="H7" s="1" t="b">
         <v>1</v>
@@ -1782,10 +1712,10 @@
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>278</v>
+        <v>153</v>
       </c>
       <c r="H8" s="1" t="b">
         <v>1</v>
@@ -1796,7 +1726,10 @@
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>276</v>
+        <v>175</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="H9" s="1" t="b">
         <v>1</v>
@@ -1804,10 +1737,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1815,7 +1751,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1824,7 +1763,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>169</v>
+        <v>171</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1832,7 +1774,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="H13" s="1" t="b">
         <v>1</v>
@@ -1843,7 +1788,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="H14" s="1" t="b">
         <v>1</v>
@@ -1854,18 +1802,21 @@
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>275</v>
+        <v>174</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>280</v>
+        <v>155</v>
       </c>
       <c r="G16" s="1">
         <v>100</v>
@@ -1876,13 +1827,13 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>280</v>
+        <v>155</v>
       </c>
       <c r="H17" s="1" t="b">
         <v>1</v>
@@ -1890,13 +1841,13 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>280</v>
+        <v>155</v>
       </c>
       <c r="H18" s="1" t="b">
         <v>1</v>
@@ -1904,13 +1855,13 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>279</v>
+        <v>154</v>
       </c>
       <c r="H19" s="1" t="b">
         <v>1</v>
@@ -1918,13 +1869,13 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>279</v>
+        <v>154</v>
       </c>
       <c r="H20" s="1" t="b">
         <v>1</v>
@@ -1932,13 +1883,13 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>279</v>
+        <v>154</v>
       </c>
       <c r="H21" s="1" t="b">
         <v>1</v>
@@ -1946,13 +1897,13 @@
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>280</v>
+        <v>155</v>
       </c>
       <c r="G22" s="1">
         <v>100</v>
@@ -1963,24 +1914,24 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>280</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" t="s">
-        <v>180</v>
+        <v>18</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>280</v>
+        <v>155</v>
       </c>
       <c r="H24" s="1" t="b">
         <v>1</v>
@@ -1988,13 +1939,13 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>279</v>
+        <v>154</v>
       </c>
       <c r="H25" s="1" t="b">
         <v>1</v>
@@ -2002,13 +1953,13 @@
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>279</v>
+        <v>154</v>
       </c>
       <c r="H26" s="1" t="b">
         <v>1</v>
@@ -2016,13 +1967,13 @@
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>279</v>
+        <v>154</v>
       </c>
       <c r="H27" s="1" t="b">
         <v>1</v>
@@ -2030,46 +1981,46 @@
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>281</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>281</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>281</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>281</v>
+        <v>156</v>
       </c>
       <c r="H31" s="1" t="b">
         <v>1</v>
@@ -2077,13 +2028,13 @@
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>281</v>
+        <v>156</v>
       </c>
       <c r="H32" s="1" t="b">
         <v>1</v>
@@ -2091,13 +2042,13 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>282</v>
+        <v>157</v>
       </c>
       <c r="G33" s="1">
         <v>95</v>
@@ -2108,35 +2059,35 @@
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C34" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>282</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>282</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>282</v>
+        <v>157</v>
       </c>
       <c r="H36" s="1" t="b">
         <v>1</v>
@@ -2144,13 +2095,13 @@
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>282</v>
+        <v>157</v>
       </c>
       <c r="G37" s="1">
         <v>95</v>
@@ -2161,35 +2112,35 @@
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>282</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>282</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>282</v>
+        <v>157</v>
       </c>
       <c r="H40" s="1" t="b">
         <v>1</v>
@@ -2197,46 +2148,46 @@
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>281</v>
+        <v>156</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>281</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C43" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>281</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>281</v>
+        <v>156</v>
       </c>
       <c r="H44" s="1" t="b">
         <v>1</v>
@@ -2244,13 +2195,13 @@
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>283</v>
+        <v>158</v>
       </c>
       <c r="H45" s="1" t="b">
         <v>1</v>
@@ -2258,13 +2209,13 @@
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>202</v>
+        <v>253</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>283</v>
+        <v>158</v>
       </c>
       <c r="H46" s="1" t="b">
         <v>1</v>
@@ -2272,10 +2223,10 @@
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H47" s="1" t="b">
         <v>1</v>
@@ -2283,10 +2234,10 @@
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C48" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H48" s="1" t="b">
         <v>1</v>
@@ -2294,10 +2245,10 @@
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H49" s="1" t="b">
         <v>1</v>
@@ -2305,10 +2256,10 @@
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H50" s="1" t="b">
         <v>1</v>
@@ -2316,10 +2267,10 @@
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C51" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H51" s="1" t="b">
         <v>1</v>
@@ -2327,10 +2278,10 @@
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C52" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H52" s="1" t="b">
         <v>1</v>
@@ -2338,13 +2289,13 @@
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>285</v>
+        <v>160</v>
       </c>
       <c r="H53" s="1" t="b">
         <v>1</v>
@@ -2352,13 +2303,13 @@
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="C54" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>285</v>
+        <v>160</v>
       </c>
       <c r="H54" s="1" t="b">
         <v>1</v>
@@ -2366,13 +2317,13 @@
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="C55" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>285</v>
+        <v>160</v>
       </c>
       <c r="H55" s="1" t="b">
         <v>1</v>
@@ -2380,13 +2331,13 @@
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>285</v>
+        <v>160</v>
       </c>
       <c r="H56" s="1" t="b">
         <v>1</v>
@@ -2397,43 +2348,43 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C58" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="C59" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C60" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="H60" s="1" t="b">
         <v>1</v>
@@ -2441,34 +2392,34 @@
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B61" s="1" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="C61" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="C62" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="C63" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B64" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="C64" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H64" s="1" t="b">
         <v>1</v>
@@ -2476,45 +2427,45 @@
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B65" s="1" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="C65" t="s">
-        <v>221</v>
+        <v>223</v>
+      </c>
+      <c r="H65" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B66" s="1" t="s">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="C66" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B67" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B68" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C68" t="s">
-        <v>224</v>
-      </c>
-      <c r="H68" s="1" t="b">
-        <v>1</v>
+        <v>226</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B69" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C69" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H69" s="1" t="b">
         <v>1</v>
@@ -2522,45 +2473,45 @@
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B70" s="1" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C70" t="s">
-        <v>226</v>
+        <v>228</v>
+      </c>
+      <c r="H70" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="C71" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B72" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C72" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B73" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C73" t="s">
-        <v>229</v>
-      </c>
-      <c r="H73" s="1" t="b">
-        <v>1</v>
+        <v>231</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B74" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C74" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H74" s="1" t="b">
         <v>1</v>
@@ -2568,45 +2519,45 @@
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="C75" t="s">
-        <v>231</v>
+        <v>233</v>
+      </c>
+      <c r="H75" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="C76" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C77" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="C78" t="s">
-        <v>234</v>
-      </c>
-      <c r="H78" s="1" t="b">
-        <v>1</v>
+        <v>236</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C79" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H79" s="1" t="b">
         <v>1</v>
@@ -2614,34 +2565,34 @@
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C80" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C81" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="C82" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C83" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H83" s="1" t="b">
         <v>1</v>
@@ -2649,34 +2600,34 @@
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C84" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C85" t="s">
-        <v>241</v>
+        <v>112</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="C86" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C87" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H87" s="1" t="b">
         <v>1</v>
@@ -2684,45 +2635,45 @@
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C88" t="s">
-        <v>244</v>
+        <v>246</v>
+      </c>
+      <c r="H88" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>245</v>
+        <v>103</v>
+      </c>
+      <c r="C89" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C90" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C91" t="s">
-        <v>247</v>
-      </c>
-      <c r="H91" s="1" t="b">
-        <v>1</v>
+        <v>249</v>
       </c>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C92" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H92" s="1" t="b">
         <v>1</v>
@@ -2730,45 +2681,45 @@
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C93" t="s">
-        <v>249</v>
+        <v>251</v>
+      </c>
+      <c r="H93" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="C94" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="C95" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="C96" t="s">
-        <v>252</v>
-      </c>
-      <c r="H96" s="1" t="b">
-        <v>1</v>
+        <v>256</v>
       </c>
     </row>
     <row r="97" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C97" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H97" s="1" t="b">
         <v>1</v>
@@ -2776,34 +2727,52 @@
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C98" t="s">
-        <v>254</v>
+        <v>258</v>
+      </c>
+      <c r="H98" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B99" s="1" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="C99" t="s">
-        <v>255</v>
+        <v>259</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H99" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C100" t="s">
-        <v>256</v>
+        <v>260</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H100" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C101" t="s">
-        <v>257</v>
+        <v>261</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="H101" s="1" t="b">
         <v>1</v>
@@ -2811,10 +2780,13 @@
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B102" s="1" t="s">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="C102" t="s">
-        <v>258</v>
+        <v>262</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="H102" s="1" t="b">
         <v>1</v>
@@ -2822,10 +2794,13 @@
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B103" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C103" t="s">
-        <v>259</v>
+        <v>263</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="H103" s="1" t="b">
         <v>1</v>
@@ -2833,10 +2808,10 @@
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B104" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C104" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H104" s="1" t="b">
         <v>1</v>
@@ -2844,10 +2819,10 @@
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B105" s="1" t="s">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="C105" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H105" s="1" t="b">
         <v>1</v>
@@ -2855,122 +2830,12 @@
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B106" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C106" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="H106" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B107" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C107" t="s">
-        <v>263</v>
-      </c>
-      <c r="H107" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B108" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C108" t="s">
-        <v>264</v>
-      </c>
-      <c r="H108" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B109" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C109" t="s">
-        <v>265</v>
-      </c>
-      <c r="H109" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B110" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C110" t="s">
-        <v>266</v>
-      </c>
-      <c r="H110" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B111" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C111" t="s">
-        <v>267</v>
-      </c>
-      <c r="H111" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B112" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C112" t="s">
-        <v>268</v>
-      </c>
-      <c r="H112" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B113" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C113" t="s">
-        <v>269</v>
-      </c>
-      <c r="H113" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B114" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C114" t="s">
-        <v>270</v>
-      </c>
-      <c r="H114" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C115" t="s">
-        <v>271</v>
-      </c>
-      <c r="H115" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C116" t="s">
-        <v>272</v>
-      </c>
-      <c r="H116" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3010,10 +2875,10 @@
   <sheetData>
     <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C1" s="7"/>
     </row>
@@ -3023,130 +2888,130 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="G2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="P2" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -3710,10 +3575,10 @@
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>277</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -3722,58 +3587,58 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -3781,25 +3646,25 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="F4" s="2">
         <v>3</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="J4" s="2">
         <v>2E-3</v>
@@ -3810,25 +3675,25 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J5" s="2">
         <v>0.1</v>
@@ -3845,19 +3710,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J6" s="2">
         <v>0.1</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#StatInfo" sheetId="7" r:id="rId1"/>
@@ -346,728 +346,728 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!StatInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Base</t>
+  </si>
+  <si>
+    <t>MaxHP_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MDEF_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+  </si>
+  <si>
+    <t>StatValue_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!StatInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_4</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_4</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelupStat</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Attack</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Damage</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Critical</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Health</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Defense</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_DamageEnemy</t>
+  </si>
+  <si>
+    <t>ItemIcon_Energy_Blue</t>
+  </si>
+  <si>
+    <t>ItemIcon_Battle</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 물리 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 물리 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 마법 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 마법 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 방어력 관통</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어력 관통</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>극 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 극 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 극 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>극 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 극 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 극 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대체력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 최대체력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 최대체력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대체력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대체력 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 물리 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 물리 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 마법 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 마법 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 방어력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 체력 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 체력 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 재생 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는데미지 감소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는데미지 감소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는데미지 감소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 공격속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 공격속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격속도 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 이동속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 이동속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동속도 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 재생 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 재생 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백파워</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백파워</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백파워</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백파워 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백저항</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백저항</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백저항</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백저항 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스태미나</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스태미나</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스태미나 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스태미나 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 재생 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 재생 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 생명력흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 생명력흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스태미나 흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스태미나 흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 흡수 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 흡수 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 방어 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 방어 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스몬스터 데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반몬스터 데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드 획득량 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>경험치 획득량 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 드랍확률 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>IsRatio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evasion_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!StatInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Base</t>
-  </si>
-  <si>
-    <t>ATK_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Base</t>
-  </si>
-  <si>
-    <t>MaxHP_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MDEF_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-  </si>
-  <si>
-    <t>StatValue_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!StatInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue_3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_4</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue_4</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelupStat</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Attack</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Damage</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Critical</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Health</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Defense</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_DamageEnemy</t>
-  </si>
-  <si>
-    <t>ItemIcon_Energy_Blue</t>
-  </si>
-  <si>
-    <t>ItemIcon_Battle</t>
-  </si>
-  <si>
-    <t>MoveSpeed_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 물리 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 물리 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 마법 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 마법 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 방어력 관통</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 방어력 관통</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>극 치명타 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 극 치명타 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 극 치명타 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>극 치명타 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 극 치명타 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 극 치명타 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대체력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 최대체력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 최대체력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대체력 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대체력 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 방어력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 물리 방어력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 물리 방어력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 방어력 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 방어력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 마법 방어력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 마법 방어력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 방어력 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>체력 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 체력 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 체력 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>체력 재생 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는데미지 감소</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는데미지 감소</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는데미지 감소</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는데미지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는데미지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는데미지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격속도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 공격속도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 공격속도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격속도 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동속도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 이동속도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 이동속도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동속도 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 재생 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 재생 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백파워</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백파워</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백파워</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백파워 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백저항</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백저항</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백저항</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백저항 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스태미나</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스태미나</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스태미나 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스태미나 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 재생 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 재생 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 생명력흡수</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 생명력흡수</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 흡수</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스태미나 흡수</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스태미나 흡수</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 흡수 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 흡수 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>방어 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 방어 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 방어 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>보스몬스터 데미지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반몬스터 데미지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드 획득량 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치 획득량 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이템 드랍확률 증가</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1586,7 +1586,7 @@
         <v>40</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C1" s="7"/>
     </row>
@@ -1602,7 +1602,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>4</v>
@@ -1611,7 +1611,7 @@
         <v>5</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>83</v>
+        <v>266</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="6"/>
@@ -1622,7 +1622,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
@@ -1631,7 +1631,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>36</v>
@@ -1654,10 +1654,10 @@
         <v>75</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -1668,13 +1668,13 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="2"/>
@@ -1684,23 +1684,23 @@
         <v>68</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H7" s="1" t="b">
         <v>1</v>
@@ -1712,10 +1712,10 @@
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H8" s="1" t="b">
         <v>1</v>
@@ -1726,10 +1726,10 @@
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H9" s="1" t="b">
         <v>1</v>
@@ -1740,10 +1740,10 @@
         <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1751,10 +1751,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1763,10 +1763,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1774,10 +1774,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H13" s="1" t="b">
         <v>1</v>
@@ -1788,10 +1788,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H14" s="1" t="b">
         <v>1</v>
@@ -1802,10 +1802,10 @@
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1813,10 +1813,10 @@
         <v>77</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G16" s="1">
         <v>100</v>
@@ -1830,10 +1830,10 @@
         <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H17" s="1" t="b">
         <v>1</v>
@@ -1841,13 +1841,13 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H18" s="1" t="b">
         <v>1</v>
@@ -1858,10 +1858,10 @@
         <v>78</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H19" s="1" t="b">
         <v>1</v>
@@ -1872,10 +1872,10 @@
         <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H20" s="1" t="b">
         <v>1</v>
@@ -1886,10 +1886,10 @@
         <v>72</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H21" s="1" t="b">
         <v>1</v>
@@ -1900,10 +1900,10 @@
         <v>79</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G22" s="1">
         <v>100</v>
@@ -1917,10 +1917,10 @@
         <v>81</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
@@ -1928,10 +1928,10 @@
         <v>18</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H24" s="1" t="b">
         <v>1</v>
@@ -1942,10 +1942,10 @@
         <v>80</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H25" s="1" t="b">
         <v>1</v>
@@ -1956,10 +1956,10 @@
         <v>82</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H26" s="1" t="b">
         <v>1</v>
@@ -1970,10 +1970,10 @@
         <v>19</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H27" s="1" t="b">
         <v>1</v>
@@ -1984,21 +1984,21 @@
         <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
@@ -2006,10 +2006,10 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.3">
@@ -2017,10 +2017,10 @@
         <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H31" s="1" t="b">
         <v>1</v>
@@ -2031,10 +2031,10 @@
         <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H32" s="1" t="b">
         <v>1</v>
@@ -2045,10 +2045,10 @@
         <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G33" s="1">
         <v>95</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
@@ -2073,10 +2073,10 @@
         <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
@@ -2084,10 +2084,10 @@
         <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H36" s="1" t="b">
         <v>1</v>
@@ -2098,10 +2098,10 @@
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G37" s="1">
         <v>95</v>
@@ -2112,13 +2112,13 @@
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
@@ -2126,10 +2126,10 @@
         <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
@@ -2137,10 +2137,10 @@
         <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H40" s="1" t="b">
         <v>1</v>
@@ -2151,10 +2151,10 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
@@ -2162,21 +2162,21 @@
         <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.3">
@@ -2184,10 +2184,10 @@
         <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H44" s="1" t="b">
         <v>1</v>
@@ -2198,10 +2198,10 @@
         <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H45" s="1" t="b">
         <v>1</v>
@@ -2212,10 +2212,10 @@
         <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H46" s="1" t="b">
         <v>1</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H47" s="1" t="b">
         <v>1</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C48" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H48" s="1" t="b">
         <v>1</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C49" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H49" s="1" t="b">
         <v>1</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H50" s="1" t="b">
         <v>1</v>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C51" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H51" s="1" t="b">
         <v>1</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C52" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H52" s="1" t="b">
         <v>1</v>
@@ -2289,13 +2289,13 @@
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C53" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H53" s="1" t="b">
         <v>1</v>
@@ -2303,13 +2303,13 @@
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H54" s="1" t="b">
         <v>1</v>
@@ -2317,13 +2317,13 @@
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C55" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H55" s="1" t="b">
         <v>1</v>
@@ -2334,10 +2334,10 @@
         <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H56" s="1" t="b">
         <v>1</v>
@@ -2348,32 +2348,32 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C58" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C59" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
@@ -2381,10 +2381,10 @@
         <v>71</v>
       </c>
       <c r="C60" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H60" s="1" t="b">
         <v>1</v>
@@ -2395,15 +2395,15 @@
         <v>66</v>
       </c>
       <c r="C61" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C62" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.3">
@@ -2411,7 +2411,7 @@
         <v>50</v>
       </c>
       <c r="C63" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.3">
@@ -2419,7 +2419,7 @@
         <v>51</v>
       </c>
       <c r="C64" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H64" s="1" t="b">
         <v>1</v>
@@ -2430,7 +2430,7 @@
         <v>52</v>
       </c>
       <c r="C65" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H65" s="1" t="b">
         <v>1</v>
@@ -2441,7 +2441,7 @@
         <v>67</v>
       </c>
       <c r="C66" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
@@ -2449,7 +2449,7 @@
         <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.3">
@@ -2457,7 +2457,7 @@
         <v>54</v>
       </c>
       <c r="C68" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.3">
@@ -2465,7 +2465,7 @@
         <v>55</v>
       </c>
       <c r="C69" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H69" s="1" t="b">
         <v>1</v>
@@ -2476,7 +2476,7 @@
         <v>56</v>
       </c>
       <c r="C70" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H70" s="1" t="b">
         <v>1</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C71" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
@@ -2495,7 +2495,7 @@
         <v>57</v>
       </c>
       <c r="C72" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
@@ -2503,7 +2503,7 @@
         <v>58</v>
       </c>
       <c r="C73" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.3">
@@ -2511,7 +2511,7 @@
         <v>59</v>
       </c>
       <c r="C74" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H74" s="1" t="b">
         <v>1</v>
@@ -2522,7 +2522,7 @@
         <v>60</v>
       </c>
       <c r="C75" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H75" s="1" t="b">
         <v>1</v>
@@ -2530,34 +2530,34 @@
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C76" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C77" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C78" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H79" s="1" t="b">
         <v>1</v>
@@ -2565,34 +2565,34 @@
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C80" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C81" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C82" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C83" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H83" s="1" t="b">
         <v>1</v>
@@ -2600,34 +2600,34 @@
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C84" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C86" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C87" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H87" s="1" t="b">
         <v>1</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C88" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H88" s="1" t="b">
         <v>1</v>
@@ -2646,34 +2646,34 @@
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C89" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C90" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C91" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C92" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H92" s="1" t="b">
         <v>1</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C93" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H93" s="1" t="b">
         <v>1</v>
@@ -2692,34 +2692,34 @@
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C94" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C95" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C96" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="97" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C97" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H97" s="1" t="b">
         <v>1</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C98" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H98" s="1" t="b">
         <v>1</v>
@@ -2741,10 +2741,10 @@
         <v>38</v>
       </c>
       <c r="C99" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H99" s="1" t="b">
         <v>1</v>
@@ -2752,13 +2752,13 @@
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C100" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H100" s="1" t="b">
         <v>1</v>
@@ -2766,13 +2766,13 @@
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C101" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H101" s="1" t="b">
         <v>1</v>
@@ -2783,10 +2783,10 @@
         <v>31</v>
       </c>
       <c r="C102" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H102" s="1" t="b">
         <v>1</v>
@@ -2797,10 +2797,10 @@
         <v>32</v>
       </c>
       <c r="C103" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H103" s="1" t="b">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>33</v>
       </c>
       <c r="C104" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H104" s="1" t="b">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>34</v>
       </c>
       <c r="C105" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H105" s="1" t="b">
         <v>1</v>
@@ -2833,7 +2833,7 @@
         <v>35</v>
       </c>
       <c r="C106" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H106" s="1" t="b">
         <v>1</v>
@@ -2927,25 +2927,25 @@
         <v>49</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -2996,16 +2996,16 @@
         <v>48</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U3" s="6" t="s">
         <v>48</v>
@@ -3575,10 +3575,10 @@
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -3587,58 +3587,58 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="E3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="G3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="I3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -3646,25 +3646,25 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F4" s="2">
         <v>3</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J4" s="2">
         <v>2E-3</v>
@@ -3675,19 +3675,19 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
@@ -3710,13 +3710,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -1553,7 +1553,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3020,7 +3020,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -3044,7 +3044,7 @@
         <v>10</v>
       </c>
       <c r="K4" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L4" s="1">
         <v>15</v>
@@ -3062,7 +3062,7 @@
         <v>10</v>
       </c>
       <c r="Q4" s="1">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R4" s="1">
         <v>0</v>
@@ -3104,7 +3104,7 @@
         <v>10</v>
       </c>
       <c r="K5" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L5" s="1">
         <v>15</v>
@@ -3122,7 +3122,7 @@
         <v>10</v>
       </c>
       <c r="Q5" s="1">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="R5" s="1">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         <v>10</v>
       </c>
       <c r="K6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6" s="1">
         <v>15</v>
@@ -3182,7 +3182,7 @@
         <v>10</v>
       </c>
       <c r="Q6" s="1">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="R6" s="1">
         <v>0</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -286,788 +286,788 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>DEF_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDam</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritRate_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperCritDam_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageReduction_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageTakenAmp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBackResist_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakRecovery</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaSteal_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Amp</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockBack_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Block_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoveSpeed_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>HpRecovery_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxStamina_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StaminaRegen_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!StatInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+  </si>
+  <si>
+    <t>ATK_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHP_Base</t>
+  </si>
+  <si>
+    <t>MaxHP_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>MDEF_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BreakGage_Base</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+  </si>
+  <si>
+    <t>StatValue_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!StatInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!float</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_2</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_3</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_4</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatValue_4</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatID_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelupStat</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Attack</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Damage</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Critical</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Health</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_Defense</t>
+  </si>
+  <si>
+    <t>ItemIcon_Skill_DamageEnemy</t>
+  </si>
+  <si>
+    <t>ItemIcon_Energy_Blue</t>
+  </si>
+  <si>
+    <t>ItemIcon_Battle</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>AtkSpeed_Add</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK_Ratio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 물리 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 물리 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 공격력 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 마법 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 마법 공격력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공격력 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 방어력 관통</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어력 관통</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>극 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 극 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 극 치명타 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>극 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 극 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 극 치명타 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대체력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 최대체력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 최대체력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대체력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대체력 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 물리 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 물리 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 방어력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 마법 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 마법 방어력</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 방어력 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 체력 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 체력 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 재생 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는데미지 감소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는데미지 감소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는데미지 감소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 받는데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 받는데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 공격속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 공격속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격속도 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 이동속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 이동속도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동속도 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 데미지</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 데미지 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 브레이크 게이지 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 브레이크 게이지 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 재생 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>브레이크 게이지 재생 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백파워</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백파워</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백파워</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백파워 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백저항</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 넉백저항</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 넉백저항</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>넉백저항 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스태미나</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스태미나</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스태미나 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스태미나 재생</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 재생 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 재생 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>물리 생명력흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 생명력흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 스태미나 흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 스태미나 흡수</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 흡수 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>스태미나 흡수 증폭</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 방어 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가 방어 확률</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스몬스터 데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반몬스터 데미지 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드 획득량 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>경험치 획득량 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 드랍확률 증가</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsRatio</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>ATK_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritDam</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritRate_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperCritDam_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageReduction_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DamageTakenAmp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBackResist_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakRecovery</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaSteal_Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Amp</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>KnockBack_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>CritRate_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evasion_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Block_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MoveSpeed_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>HpRecovery_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxStamina_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StaminaRegen_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!StatInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Base</t>
-  </si>
-  <si>
-    <t>ATK_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxHP_Base</t>
-  </si>
-  <si>
-    <t>MaxHP_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DEF_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>MDEF_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BreakGage_Base</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Table</t>
-  </si>
-  <si>
-    <t>StatValue_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!StatInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue_2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue_3</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_4</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatValue_4</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatID_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>LevelupStat</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Attack</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Damage</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Critical</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Health</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_Defense</t>
-  </si>
-  <si>
-    <t>ItemIcon_Skill_DamageEnemy</t>
-  </si>
-  <si>
-    <t>ItemIcon_Energy_Blue</t>
-  </si>
-  <si>
-    <t>ItemIcon_Battle</t>
-  </si>
-  <si>
-    <t>MoveSpeed_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>AtkSpeed_Add</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ATK_Ratio</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 물리 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 물리 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 공격력 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 마법 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 마법 공격력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 공격력 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 방어력 관통</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 방어력 관통</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>치명타 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 치명타 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 치명타 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>극 치명타 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 극 치명타 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 극 치명타 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>극 치명타 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 극 치명타 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 극 치명타 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대체력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 최대체력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 최대체력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대체력 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>최대체력 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 방어력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 물리 방어력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 물리 방어력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 방어력 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 방어력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 마법 방어력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 마법 방어력</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 방어력 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>체력 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 체력 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 체력 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>체력 재생 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는데미지 감소</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는데미지 감소</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는데미지 감소</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는데미지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 받는데미지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 받는데미지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격속도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 공격속도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 공격속도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격속도 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동속도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 이동속도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 이동속도</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동속도 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 데미지</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 데미지 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 브레이크 게이지 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 브레이크 게이지 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 재생 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>브레이크 게이지 재생 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백파워</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백파워</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백파워</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백파워 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백저항</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 넉백저항</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 넉백저항</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>넉백저항 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스태미나</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스태미나</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스태미나 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스태미나 재생</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 재생 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 재생 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>물리 생명력흡수</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법 생명력흡수</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 흡수</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 스태미나 흡수</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 스태미나 흡수</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 흡수 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>스태미나 흡수 증폭</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>방어 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 방어 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가 방어 확률</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>보스몬스터 데미지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반몬스터 데미지 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드 획득량 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치 획득량 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이템 드랍확률 증가</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsRatio</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1553,7 +1553,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1586,7 +1586,7 @@
         <v>40</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C1" s="7"/>
     </row>
@@ -1602,7 +1602,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>4</v>
@@ -1611,7 +1611,7 @@
         <v>5</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="6"/>
@@ -1622,7 +1622,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>3</v>
@@ -1631,7 +1631,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>36</v>
@@ -1651,13 +1651,13 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -1668,39 +1668,39 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J5" s="8"/>
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>266</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H7" s="1" t="b">
         <v>1</v>
@@ -1712,10 +1712,10 @@
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H8" s="1" t="b">
         <v>1</v>
@@ -1726,10 +1726,10 @@
         <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H9" s="1" t="b">
         <v>1</v>
@@ -1740,10 +1740,10 @@
         <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1751,10 +1751,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1763,10 +1763,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1774,10 +1774,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H13" s="1" t="b">
         <v>1</v>
@@ -1788,10 +1788,10 @@
         <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H14" s="1" t="b">
         <v>1</v>
@@ -1802,21 +1802,21 @@
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G16" s="1">
         <v>100</v>
@@ -1830,10 +1830,10 @@
         <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H17" s="1" t="b">
         <v>1</v>
@@ -1841,13 +1841,13 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H18" s="1" t="b">
         <v>1</v>
@@ -1855,13 +1855,13 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H19" s="1" t="b">
         <v>1</v>
@@ -1872,10 +1872,10 @@
         <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H20" s="1" t="b">
         <v>1</v>
@@ -1883,13 +1883,13 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H21" s="1" t="b">
         <v>1</v>
@@ -1897,13 +1897,13 @@
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G22" s="1">
         <v>100</v>
@@ -1914,13 +1914,13 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
@@ -1928,10 +1928,10 @@
         <v>18</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H24" s="1" t="b">
         <v>1</v>
@@ -1939,13 +1939,13 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H25" s="1" t="b">
         <v>1</v>
@@ -1953,13 +1953,13 @@
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H26" s="1" t="b">
         <v>1</v>
@@ -1970,10 +1970,10 @@
         <v>19</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H27" s="1" t="b">
         <v>1</v>
@@ -1984,32 +1984,32 @@
         <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.3">
@@ -2017,10 +2017,10 @@
         <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H31" s="1" t="b">
         <v>1</v>
@@ -2031,10 +2031,10 @@
         <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H32" s="1" t="b">
         <v>1</v>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G33" s="1">
         <v>95</v>
@@ -2059,24 +2059,24 @@
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
@@ -2084,10 +2084,10 @@
         <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H36" s="1" t="b">
         <v>1</v>
@@ -2098,10 +2098,10 @@
         <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G37" s="1">
         <v>95</v>
@@ -2112,13 +2112,13 @@
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
@@ -2126,10 +2126,10 @@
         <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
@@ -2137,10 +2137,10 @@
         <v>25</v>
       </c>
       <c r="C40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H40" s="1" t="b">
         <v>1</v>
@@ -2151,32 +2151,32 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.3">
@@ -2184,10 +2184,10 @@
         <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H44" s="1" t="b">
         <v>1</v>
@@ -2198,10 +2198,10 @@
         <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H45" s="1" t="b">
         <v>1</v>
@@ -2212,10 +2212,10 @@
         <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H46" s="1" t="b">
         <v>1</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H47" s="1" t="b">
         <v>1</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H48" s="1" t="b">
         <v>1</v>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C49" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H49" s="1" t="b">
         <v>1</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H50" s="1" t="b">
         <v>1</v>
@@ -2267,10 +2267,10 @@
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C51" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H51" s="1" t="b">
         <v>1</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C52" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H52" s="1" t="b">
         <v>1</v>
@@ -2289,13 +2289,13 @@
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C53" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H53" s="1" t="b">
         <v>1</v>
@@ -2303,13 +2303,13 @@
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H54" s="1" t="b">
         <v>1</v>
@@ -2317,13 +2317,13 @@
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C55" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H55" s="1" t="b">
         <v>1</v>
@@ -2331,13 +2331,13 @@
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H56" s="1" t="b">
         <v>1</v>
@@ -2348,43 +2348,43 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B58" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C58" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C59" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B60" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C60" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H60" s="1" t="b">
         <v>1</v>
@@ -2395,15 +2395,15 @@
         <v>66</v>
       </c>
       <c r="C61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B62" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C62" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.3">
@@ -2411,7 +2411,7 @@
         <v>50</v>
       </c>
       <c r="C63" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.3">
@@ -2419,7 +2419,7 @@
         <v>51</v>
       </c>
       <c r="C64" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H64" s="1" t="b">
         <v>1</v>
@@ -2430,7 +2430,7 @@
         <v>52</v>
       </c>
       <c r="C65" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H65" s="1" t="b">
         <v>1</v>
@@ -2441,7 +2441,7 @@
         <v>67</v>
       </c>
       <c r="C66" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
@@ -2449,7 +2449,7 @@
         <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.3">
@@ -2457,7 +2457,7 @@
         <v>54</v>
       </c>
       <c r="C68" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.3">
@@ -2465,7 +2465,7 @@
         <v>55</v>
       </c>
       <c r="C69" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H69" s="1" t="b">
         <v>1</v>
@@ -2476,7 +2476,7 @@
         <v>56</v>
       </c>
       <c r="C70" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H70" s="1" t="b">
         <v>1</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B71" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C71" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
@@ -2495,7 +2495,7 @@
         <v>57</v>
       </c>
       <c r="C72" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
@@ -2503,7 +2503,7 @@
         <v>58</v>
       </c>
       <c r="C73" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.3">
@@ -2511,7 +2511,7 @@
         <v>59</v>
       </c>
       <c r="C74" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H74" s="1" t="b">
         <v>1</v>
@@ -2522,7 +2522,7 @@
         <v>60</v>
       </c>
       <c r="C75" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H75" s="1" t="b">
         <v>1</v>
@@ -2530,34 +2530,34 @@
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B76" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B77" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C77" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B78" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C78" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B79" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H79" s="1" t="b">
         <v>1</v>
@@ -2565,34 +2565,34 @@
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C80" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B81" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C81" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B82" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C82" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B83" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C83" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H83" s="1" t="b">
         <v>1</v>
@@ -2600,34 +2600,34 @@
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B84" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C84" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B86" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C86" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B87" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C87" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H87" s="1" t="b">
         <v>1</v>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B88" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H88" s="1" t="b">
         <v>1</v>
@@ -2646,34 +2646,34 @@
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B89" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C89" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B90" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C90" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B91" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C91" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B92" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C92" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H92" s="1" t="b">
         <v>1</v>
@@ -2681,10 +2681,10 @@
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B93" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C93" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H93" s="1" t="b">
         <v>1</v>
@@ -2692,34 +2692,34 @@
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B94" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C94" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B95" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C95" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B96" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C96" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="97" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B97" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C97" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H97" s="1" t="b">
         <v>1</v>
@@ -2727,10 +2727,10 @@
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B98" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C98" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H98" s="1" t="b">
         <v>1</v>
@@ -2741,10 +2741,10 @@
         <v>38</v>
       </c>
       <c r="C99" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H99" s="1" t="b">
         <v>1</v>
@@ -2752,13 +2752,13 @@
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B100" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C100" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H100" s="1" t="b">
         <v>1</v>
@@ -2766,13 +2766,13 @@
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B101" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C101" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H101" s="1" t="b">
         <v>1</v>
@@ -2783,10 +2783,10 @@
         <v>31</v>
       </c>
       <c r="C102" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H102" s="1" t="b">
         <v>1</v>
@@ -2797,10 +2797,10 @@
         <v>32</v>
       </c>
       <c r="C103" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H103" s="1" t="b">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>33</v>
       </c>
       <c r="C104" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H104" s="1" t="b">
         <v>1</v>
@@ -2822,7 +2822,7 @@
         <v>34</v>
       </c>
       <c r="C105" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H105" s="1" t="b">
         <v>1</v>
@@ -2833,7 +2833,7 @@
         <v>35</v>
       </c>
       <c r="C106" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H106" s="1" t="b">
         <v>1</v>
@@ -2927,25 +2927,25 @@
         <v>49</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -2996,16 +2996,16 @@
         <v>48</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U3" s="6" t="s">
         <v>48</v>
@@ -3035,7 +3035,7 @@
         <v>5000</v>
       </c>
       <c r="H4" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>5000</v>
       </c>
       <c r="H5" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>103</v>
       </c>
       <c r="C6" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -3155,7 +3155,7 @@
         <v>5000</v>
       </c>
       <c r="H6" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -3200,7 +3200,7 @@
         <v>10001</v>
       </c>
       <c r="C7" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -3215,7 +3215,7 @@
         <v>200</v>
       </c>
       <c r="H7" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
@@ -3245,7 +3245,7 @@
         <v>10002</v>
       </c>
       <c r="C8" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -3260,7 +3260,7 @@
         <v>500</v>
       </c>
       <c r="H8" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -3287,7 +3287,7 @@
         <v>10003</v>
       </c>
       <c r="C9" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -3302,7 +3302,7 @@
         <v>500</v>
       </c>
       <c r="H9" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>20001</v>
       </c>
       <c r="C10" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -3344,7 +3344,7 @@
         <v>500</v>
       </c>
       <c r="H10" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
@@ -3397,7 +3397,7 @@
         <v>1000</v>
       </c>
       <c r="H11" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -3450,7 +3450,7 @@
         <v>5000</v>
       </c>
       <c r="H12" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
@@ -3575,10 +3575,10 @@
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -3587,58 +3587,58 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="E3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="G3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="I3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -3646,25 +3646,25 @@
         <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F4" s="2">
         <v>3</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H4" s="2">
         <v>1</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J4" s="2">
         <v>2E-3</v>
@@ -3675,19 +3675,19 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
@@ -3710,13 +3710,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="13" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="183">
   <si>
     <t>Name</t>
     <phoneticPr fontId="7" type="noConversion"/>
@@ -663,6 +663,10 @@
   </si>
   <si>
     <t>StatDetail</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stat_MoveSpeedBonus</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1233,7 +1237,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1738,7 +1742,7 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>58</v>
+        <v>182</v>
       </c>
       <c r="C21" t="s">
         <v>70</v>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -253,10 +253,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Stat_MoveSpeedBonus</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>Stat_ExpBonus</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -436,9 +432,6 @@
     <t>막기 확률 +{0}%</t>
   </si>
   <si>
-    <t>이동 속도 +{0}%</t>
-  </si>
-  <si>
     <t>경험치 획득량 +{0}%</t>
   </si>
   <si>
@@ -602,12 +595,6 @@
   </si>
   <si>
     <t>StatDetail_BlockRate_Add</t>
-  </si>
-  <si>
-    <t>StatDetail_MoveSpeedBonus_Base</t>
-  </si>
-  <si>
-    <t>StatDetail_MoveSpeedBonus_Add</t>
   </si>
   <si>
     <t>StatDetail_ExpBonus_Base</t>
@@ -650,23 +637,39 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>Stat_Atk</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!StatDetail</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetail</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetail_MoveSpeed_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetail_MoveSpeed_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동 속도 +{0}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>ValueType</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Stat_Atk</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>!StatDetail</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatDetail</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stat_MoveSpeedBonus</t>
+    <t>이동 속도 증가+{0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stat_MoveSpeed</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1237,7 +1240,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1294,7 +1297,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D6" s="13"/>
     </row>
@@ -1319,7 +1322,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1327,7 +1330,7 @@
         <v>38</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -1338,7 +1341,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D12" s="13"/>
     </row>
@@ -1407,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>29</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>2</v>
@@ -1436,7 +1439,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>28</v>
@@ -1445,10 +1448,10 @@
         <v>13</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
@@ -1459,10 +1462,10 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>19</v>
@@ -1519,7 +1522,7 @@
         <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>19</v>
@@ -1536,7 +1539,7 @@
         <v>44</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
@@ -1549,10 +1552,10 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
@@ -1565,10 +1568,10 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
@@ -1584,7 +1587,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>19</v>
@@ -1598,7 +1601,7 @@
         <v>48</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>19</v>
@@ -1676,7 +1679,7 @@
         <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17"/>
       <c r="E17" t="s">
@@ -1694,7 +1697,7 @@
         <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18"/>
       <c r="E18" t="s">
@@ -1727,7 +1730,7 @@
         <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D20"/>
       <c r="E20" t="s">
@@ -1745,22 +1748,22 @@
         <v>182</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D21"/>
       <c r="E21" t="s">
         <v>23</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D22"/>
       <c r="E22" t="s">
@@ -1772,10 +1775,10 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>23</v>
@@ -1786,7 +1789,7 @@
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>33</v>
@@ -1800,10 +1803,10 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>23</v>
@@ -1843,7 +1846,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -1857,13 +1860,13 @@
         <v>42</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G2" s="6"/>
       <c r="I2" s="2"/>
@@ -1873,19 +1876,19 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>41</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G3" s="6"/>
       <c r="I3" s="6"/>
@@ -1895,7 +1898,7 @@
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>43</v>
@@ -1907,7 +1910,7 @@
         <v>7</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="2"/>
@@ -1918,7 +1921,7 @@
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>43</v>
@@ -1930,7 +1933,7 @@
         <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="2"/>
@@ -1941,7 +1944,7 @@
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>43</v>
@@ -1953,7 +1956,7 @@
         <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="2"/>
@@ -1964,7 +1967,7 @@
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>43</v>
@@ -1976,7 +1979,7 @@
         <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="2"/>
@@ -1986,7 +1989,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>45</v>
@@ -1998,12 +2001,12 @@
         <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>45</v>
@@ -2015,12 +2018,12 @@
         <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>46</v>
@@ -2032,12 +2035,12 @@
         <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>46</v>
@@ -2049,12 +2052,12 @@
         <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>47</v>
@@ -2066,12 +2069,12 @@
         <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>47</v>
@@ -2083,12 +2086,12 @@
         <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>44</v>
@@ -2100,14 +2103,14 @@
         <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>44</v>
@@ -2119,17 +2122,17 @@
         <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>35</v>
@@ -2138,17 +2141,17 @@
         <v>9</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>36</v>
@@ -2157,17 +2160,17 @@
         <v>9</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>35</v>
@@ -2176,17 +2179,17 @@
         <v>9</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>36</v>
@@ -2195,14 +2198,14 @@
         <v>9</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="2"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>49</v>
@@ -2214,12 +2217,12 @@
         <v>9</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>49</v>
@@ -2231,12 +2234,12 @@
         <v>9</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>48</v>
@@ -2248,12 +2251,12 @@
         <v>9</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>48</v>
@@ -2265,12 +2268,12 @@
         <v>9</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>50</v>
@@ -2282,12 +2285,12 @@
         <v>9</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>50</v>
@@ -2299,12 +2302,12 @@
         <v>9</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>51</v>
@@ -2316,12 +2319,12 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>51</v>
@@ -2333,12 +2336,12 @@
         <v>7</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>51</v>
@@ -2350,12 +2353,12 @@
         <v>9</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>51</v>
@@ -2367,12 +2370,12 @@
         <v>9</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>52</v>
@@ -2384,12 +2387,12 @@
         <v>7</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>52</v>
@@ -2401,12 +2404,12 @@
         <v>7</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>52</v>
@@ -2418,12 +2421,12 @@
         <v>9</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>52</v>
@@ -2435,12 +2438,12 @@
         <v>9</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>53</v>
@@ -2452,12 +2455,12 @@
         <v>7</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>53</v>
@@ -2469,12 +2472,12 @@
         <v>7</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>53</v>
@@ -2486,12 +2489,12 @@
         <v>9</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>53</v>
@@ -2503,12 +2506,12 @@
         <v>9</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>54</v>
@@ -2520,12 +2523,12 @@
         <v>9</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>54</v>
@@ -2537,12 +2540,12 @@
         <v>9</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>55</v>
@@ -2554,12 +2557,12 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>55</v>
@@ -2571,12 +2574,12 @@
         <v>7</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>55</v>
@@ -2588,12 +2591,12 @@
         <v>9</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>55</v>
@@ -2605,12 +2608,12 @@
         <v>9</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>56</v>
@@ -2622,12 +2625,12 @@
         <v>9</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>56</v>
@@ -2639,12 +2642,12 @@
         <v>9</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>57</v>
@@ -2656,12 +2659,12 @@
         <v>9</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>57</v>
@@ -2673,32 +2676,32 @@
         <v>9</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>58</v>
+        <v>182</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>58</v>
+        <v>182</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>36</v>
@@ -2707,15 +2710,15 @@
         <v>9</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>110</v>
+        <v>181</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>35</v>
@@ -2724,15 +2727,15 @@
         <v>9</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>36</v>
@@ -2741,15 +2744,15 @@
         <v>9</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>35</v>
@@ -2758,15 +2761,15 @@
         <v>9</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>36</v>
@@ -2775,15 +2778,15 @@
         <v>9</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>35</v>
@@ -2792,15 +2795,15 @@
         <v>9</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>36</v>
@@ -2809,15 +2812,15 @@
         <v>9</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>35</v>
@@ -2826,15 +2829,15 @@
         <v>9</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>36</v>
@@ -2843,7 +2846,7 @@
         <v>9</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="13" r:id="rId1"/>
@@ -665,11 +665,11 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>Stat_MoveSpeed</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>이동 속도 증가+{0}%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stat_MoveSpeed</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1240,7 +1240,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C21" t="s">
         <v>69</v>
@@ -2684,7 +2684,7 @@
         <v>177</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>35</v>
@@ -2701,7 +2701,7 @@
         <v>178</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>36</v>
@@ -2710,7 +2710,7 @@
         <v>9</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="190">
   <si>
     <t>Name</t>
     <phoneticPr fontId="7" type="noConversion"/>
@@ -353,97 +353,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>DisplayFormat</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 +{0}</t>
-  </si>
-  <si>
-    <t>공격력 +{0}%</t>
-  </si>
-  <si>
-    <t>공격력 +{0}% 증폭</t>
-  </si>
-  <si>
-    <t>피해량 +{0}%</t>
-  </si>
-  <si>
-    <t>공격 속도 +{0}%</t>
-  </si>
-  <si>
-    <t>치명타 확률 +{0}%</t>
-  </si>
-  <si>
-    <t>치명타 피해량 +{0}%</t>
-  </si>
-  <si>
-    <t>최종 피해량 +{0}% 증폭</t>
-  </si>
-  <si>
-    <t>보스 피해량 +{0}%</t>
-  </si>
-  <si>
-    <t>방어력 관통 +{0}%</t>
-  </si>
-  <si>
-    <t>최대 생명력 +{0}</t>
-  </si>
-  <si>
-    <t>최대 생명력 +{0}%</t>
-  </si>
-  <si>
-    <t>최대 생명력 +{0}% 증폭</t>
-  </si>
-  <si>
-    <t>생명력 재생 +{0}</t>
-  </si>
-  <si>
-    <t>생명력 재생 +{0}%</t>
-  </si>
-  <si>
-    <t>생명력 재생 +{0}% 증폭</t>
-  </si>
-  <si>
-    <t>방어력 +{0}</t>
-  </si>
-  <si>
-    <t>방어력 +{0}%</t>
-  </si>
-  <si>
-    <t>방어력 +{0}% 증폭</t>
-  </si>
-  <si>
-    <t>피해 감소 +{0}%</t>
-  </si>
-  <si>
-    <t>적중 시 체력 회복 +{0}</t>
-  </si>
-  <si>
-    <t>적중 시 체력 회복 +{0}%</t>
-  </si>
-  <si>
-    <t>적중 시 체력 회복 +{0}% 증폭</t>
-  </si>
-  <si>
-    <t>회피율 +{0}%</t>
-  </si>
-  <si>
-    <t>막기 확률 +{0}%</t>
-  </si>
-  <si>
-    <t>경험치 획득량 +{0}%</t>
-  </si>
-  <si>
-    <t>아이템 획득 범위 +{0}%</t>
-  </si>
-  <si>
-    <t>골드 획득량 +{0}%</t>
-  </si>
-  <si>
-    <t>받는 피해량 +{0}% 증폭</t>
-  </si>
-  <si>
     <t>Stat_MeleeDamageBonus</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -457,14 +366,6 @@
   </si>
   <si>
     <t>원거리 피해량</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>근접 피해량 +{0}%</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>원거리 피해량 +{0}%</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -645,31 +546,182 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>StatDetail_MoveSpeed_Base</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetail_MoveSpeed_Add</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ValueType</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stat_MoveSpeed</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatIcon_Attack</t>
+  </si>
+  <si>
+    <t>StatIcon_Critical</t>
+  </si>
+  <si>
+    <t>StatIcon_Health</t>
+  </si>
+  <si>
+    <t>StatIcon_Health</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatIcon_Defense</t>
+  </si>
+  <si>
+    <t>StatIcon_Utility</t>
+  </si>
+  <si>
+    <t>StatIcon_CritDamage</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
     <t>StatDetail</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>StatDetail_MoveSpeed_Base</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>StatDetail_MoveSpeed_Add</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동 속도 +{0}</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ValueType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stat_MoveSpeed</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동 속도 증가+{0}%</t>
+    <t>DisplayFormat</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 {0}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 속도 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 확률 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 증폭 {0}% </t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>치명타 피해량 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>피해량 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>근접 피해량 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>원거리 피해량 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>보스 피해량 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최종 피해량 증폭 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어력 관통 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 생명력 {0}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 생명력 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 생명력 증폭 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>생명력 재생 {0}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>생명력 재생 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>생명력 재생 증폭 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어력 {0}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어력 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어력 증폭 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>피해 감소 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>적중 시 체력 회복 {0}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>적중 시 체력 회복 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>적중 시 체력 회복 증폭 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>회피율 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>막기 확률 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동 속도 {0}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동 속도 증가 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>경험치 획득량 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 획득 범위 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드 획득량 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>받는 피해량 증폭 {0}%</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -907,7 +959,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -962,6 +1014,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1240,7 +1295,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1297,7 +1352,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="D6" s="13"/>
     </row>
@@ -1376,7 +1431,7 @@
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.75" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.25" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.75" style="1" bestFit="1" customWidth="1"/>
@@ -1416,7 +1471,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>2</v>
@@ -1462,10 +1517,13 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>73</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>19</v>
@@ -1487,6 +1545,9 @@
       <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="D5" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="E5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1507,6 +1568,9 @@
       <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="D6" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1524,6 +1588,9 @@
       <c r="C7" s="1" t="s">
         <v>66</v>
       </c>
+      <c r="D7" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
@@ -1541,6 +1608,9 @@
       <c r="C8" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="D8" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="E8" t="s">
         <v>19</v>
       </c>
@@ -1552,10 +1622,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>115</v>
+        <v>85</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
@@ -1568,10 +1641,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>116</v>
+        <v>86</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
@@ -1589,6 +1665,9 @@
       <c r="C11" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="E11" s="1" t="s">
         <v>19</v>
       </c>
@@ -1603,6 +1682,9 @@
       <c r="C12" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="D12" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="E12" s="1" t="s">
         <v>19</v>
       </c>
@@ -1617,6 +1699,9 @@
       <c r="C13" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="D13" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="E13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1634,7 +1719,9 @@
       <c r="C14" t="s">
         <v>15</v>
       </c>
-      <c r="D14"/>
+      <c r="D14" s="1" t="s">
+        <v>151</v>
+      </c>
       <c r="E14" t="s">
         <v>21</v>
       </c>
@@ -1652,6 +1739,9 @@
       <c r="C15" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="D15" s="1" t="s">
+        <v>150</v>
+      </c>
       <c r="E15" s="1" t="s">
         <v>21</v>
       </c>
@@ -1666,7 +1756,9 @@
       <c r="C16" t="s">
         <v>16</v>
       </c>
-      <c r="D16"/>
+      <c r="D16" t="s">
+        <v>152</v>
+      </c>
       <c r="E16" t="s">
         <v>21</v>
       </c>
@@ -1681,7 +1773,9 @@
       <c r="C17" t="s">
         <v>65</v>
       </c>
-      <c r="D17"/>
+      <c r="D17" t="s">
+        <v>152</v>
+      </c>
       <c r="E17" t="s">
         <v>21</v>
       </c>
@@ -1699,7 +1793,9 @@
       <c r="C18" t="s">
         <v>67</v>
       </c>
-      <c r="D18"/>
+      <c r="D18" t="s">
+        <v>153</v>
+      </c>
       <c r="E18" t="s">
         <v>21</v>
       </c>
@@ -1714,7 +1810,9 @@
       <c r="C19" t="s">
         <v>32</v>
       </c>
-      <c r="D19"/>
+      <c r="D19" t="s">
+        <v>152</v>
+      </c>
       <c r="E19" t="s">
         <v>21</v>
       </c>
@@ -1732,7 +1830,9 @@
       <c r="C20" t="s">
         <v>68</v>
       </c>
-      <c r="D20"/>
+      <c r="D20" t="s">
+        <v>152</v>
+      </c>
       <c r="E20" t="s">
         <v>21</v>
       </c>
@@ -1745,12 +1845,14 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="C21" t="s">
         <v>69</v>
       </c>
-      <c r="D21"/>
+      <c r="D21" t="s">
+        <v>153</v>
+      </c>
       <c r="E21" t="s">
         <v>23</v>
       </c>
@@ -1765,7 +1867,9 @@
       <c r="C22" t="s">
         <v>70</v>
       </c>
-      <c r="D22"/>
+      <c r="D22" t="s">
+        <v>153</v>
+      </c>
       <c r="E22" t="s">
         <v>23</v>
       </c>
@@ -1780,6 +1884,9 @@
       <c r="C23" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="D23" t="s">
+        <v>153</v>
+      </c>
       <c r="E23" s="1" t="s">
         <v>23</v>
       </c>
@@ -1794,6 +1901,9 @@
       <c r="C24" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="D24" t="s">
+        <v>153</v>
+      </c>
       <c r="E24" s="1" t="s">
         <v>23</v>
       </c>
@@ -1807,6 +1917,9 @@
       </c>
       <c r="C25" s="1" t="s">
         <v>72</v>
+      </c>
+      <c r="D25" t="s">
+        <v>152</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>23</v>
@@ -1846,7 +1959,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -1860,13 +1973,13 @@
         <v>42</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="E2" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="18" t="s">
-        <v>83</v>
+      <c r="F2" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="G2" s="6"/>
       <c r="I2" s="2"/>
@@ -1876,13 +1989,13 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>41</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>77</v>
@@ -1898,7 +2011,7 @@
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>43</v>
@@ -1910,7 +2023,7 @@
         <v>7</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="2"/>
@@ -1921,7 +2034,7 @@
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="1" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>43</v>
@@ -1933,7 +2046,7 @@
         <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="2"/>
@@ -1944,7 +2057,7 @@
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="1" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>43</v>
@@ -1956,7 +2069,7 @@
         <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="2"/>
@@ -1967,7 +2080,7 @@
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="1" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>43</v>
@@ -1979,7 +2092,7 @@
         <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>86</v>
+        <v>161</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="2"/>
@@ -1989,7 +2102,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>45</v>
@@ -2001,12 +2114,12 @@
         <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>45</v>
@@ -2018,12 +2131,12 @@
         <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>46</v>
@@ -2035,12 +2148,12 @@
         <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>89</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>46</v>
@@ -2052,12 +2165,12 @@
         <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>89</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>47</v>
@@ -2069,12 +2182,12 @@
         <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>47</v>
@@ -2086,12 +2199,12 @@
         <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>44</v>
@@ -2103,14 +2216,14 @@
         <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>44</v>
@@ -2122,17 +2235,17 @@
         <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>35</v>
@@ -2141,17 +2254,17 @@
         <v>9</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>36</v>
@@ -2160,17 +2273,17 @@
         <v>9</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>35</v>
@@ -2179,17 +2292,17 @@
         <v>9</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>36</v>
@@ -2198,14 +2311,14 @@
         <v>9</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="2"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>49</v>
@@ -2217,12 +2330,12 @@
         <v>9</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>49</v>
@@ -2234,12 +2347,12 @@
         <v>9</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>48</v>
@@ -2251,12 +2364,12 @@
         <v>9</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>91</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>48</v>
@@ -2268,12 +2381,12 @@
         <v>9</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>91</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>50</v>
@@ -2285,12 +2398,12 @@
         <v>9</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>50</v>
@@ -2302,12 +2415,12 @@
         <v>9</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>51</v>
@@ -2319,12 +2432,12 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>94</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>51</v>
@@ -2336,12 +2449,12 @@
         <v>7</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>94</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>51</v>
@@ -2353,12 +2466,12 @@
         <v>9</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>51</v>
@@ -2370,12 +2483,12 @@
         <v>9</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>96</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>52</v>
@@ -2387,12 +2500,12 @@
         <v>7</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>97</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>52</v>
@@ -2404,12 +2517,12 @@
         <v>7</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>97</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>52</v>
@@ -2421,12 +2534,12 @@
         <v>9</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>52</v>
@@ -2438,12 +2551,12 @@
         <v>9</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>99</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>53</v>
@@ -2455,12 +2568,12 @@
         <v>7</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="1" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>53</v>
@@ -2472,12 +2585,12 @@
         <v>7</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>100</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="1" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>53</v>
@@ -2489,12 +2602,12 @@
         <v>9</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="1" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>53</v>
@@ -2506,12 +2619,12 @@
         <v>9</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>102</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="1" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>54</v>
@@ -2523,12 +2636,12 @@
         <v>9</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>103</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="1" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>54</v>
@@ -2540,12 +2653,12 @@
         <v>9</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>103</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>55</v>
@@ -2557,12 +2670,12 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="1" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>55</v>
@@ -2574,12 +2687,12 @@
         <v>7</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="1" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>55</v>
@@ -2591,12 +2704,12 @@
         <v>9</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>105</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="1" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>55</v>
@@ -2608,12 +2721,12 @@
         <v>9</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>106</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>56</v>
@@ -2625,12 +2738,12 @@
         <v>9</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>107</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="1" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>56</v>
@@ -2642,12 +2755,12 @@
         <v>9</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>107</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="1" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>57</v>
@@ -2659,12 +2772,12 @@
         <v>9</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>108</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47" s="1" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>57</v>
@@ -2676,15 +2789,15 @@
         <v>9</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>108</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>35</v>
@@ -2693,15 +2806,15 @@
         <v>7</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>36</v>
@@ -2710,12 +2823,12 @@
         <v>9</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>58</v>
@@ -2727,12 +2840,12 @@
         <v>9</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>109</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" s="1" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>58</v>
@@ -2744,12 +2857,12 @@
         <v>9</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>109</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>59</v>
@@ -2761,12 +2874,12 @@
         <v>9</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>59</v>
@@ -2778,12 +2891,12 @@
         <v>9</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>60</v>
@@ -2795,12 +2908,12 @@
         <v>9</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>60</v>
@@ -2812,12 +2925,12 @@
         <v>9</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>61</v>
@@ -2829,12 +2942,12 @@
         <v>9</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>61</v>
@@ -2846,7 +2959,7 @@
         <v>9</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Stat.xlsx
+++ b/Shared/XLS/Stat.xlsx
@@ -504,9 +504,6 @@
     <t>StatDetail_ExpBonus_Add</t>
   </si>
   <si>
-    <t>StatDetail_PickupRange_Base</t>
-  </si>
-  <si>
     <t>StatDetail_PickupRange_Add</t>
   </si>
   <si>
@@ -722,6 +719,10 @@
   </si>
   <si>
     <t>받는 피해량 증폭 {0}%</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatDetail_PickupRange_Base</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1295,7 +1296,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1352,7 +1353,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D6" s="13"/>
     </row>
@@ -1471,7 +1472,7 @@
         <v>29</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>2</v>
@@ -1517,13 +1518,13 @@
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>19</v>
@@ -1546,7 +1547,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>19</v>
@@ -1569,7 +1570,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>19</v>
@@ -1589,7 +1590,7 @@
         <v>66</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>19</v>
@@ -1609,7 +1610,7 @@
         <v>62</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
@@ -1628,7 +1629,7 @@
         <v>85</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
@@ -1647,7 +1648,7 @@
         <v>86</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
@@ -1666,7 +1667,7 @@
         <v>64</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>19</v>
@@ -1683,7 +1684,7 @@
         <v>63</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>19</v>
@@ -1700,7 +1701,7 @@
         <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>19</v>
@@ -1720,7 +1721,7 @@
         <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
         <v>21</v>
@@ -1740,7 +1741,7 @@
         <v>31</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>21</v>
@@ -1757,7 +1758,7 @@
         <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
@@ -1774,7 +1775,7 @@
         <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E17" t="s">
         <v>21</v>
@@ -1794,7 +1795,7 @@
         <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E18" t="s">
         <v>21</v>
@@ -1811,7 +1812,7 @@
         <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E19" t="s">
         <v>21</v>
@@ -1831,7 +1832,7 @@
         <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E20" t="s">
         <v>21</v>
@@ -1845,13 +1846,13 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" t="s">
         <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E21" t="s">
         <v>23</v>
@@ -1868,7 +1869,7 @@
         <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E22" t="s">
         <v>23</v>
@@ -1885,7 +1886,7 @@
         <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>23</v>
@@ -1902,7 +1903,7 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>23</v>
@@ -1919,7 +1920,7 @@
         <v>72</v>
       </c>
       <c r="D25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>23</v>
@@ -1959,7 +1960,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -1973,13 +1974,13 @@
         <v>42</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E2" s="18" t="s">
         <v>78</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G2" s="6"/>
       <c r="I2" s="2"/>
@@ -1989,13 +1990,13 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>41</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>77</v>
@@ -2011,7 +2012,7 @@
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>43</v>
@@ -2023,7 +2024,7 @@
         <v>7</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="2"/>
@@ -2046,7 +2047,7 @@
         <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="2"/>
@@ -2069,7 +2070,7 @@
         <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="2"/>
@@ -2092,7 +2093,7 @@
         <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="2"/>
@@ -2114,7 +2115,7 @@
         <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -2131,7 +2132,7 @@
         <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -2148,7 +2149,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -2165,7 +2166,7 @@
         <v>9</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -2182,7 +2183,7 @@
         <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -2199,7 +2200,7 @@
         <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -2216,7 +2217,7 @@
         <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="2"/>
@@ -2235,7 +2236,7 @@
         <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="2"/>
@@ -2254,7 +2255,7 @@
         <v>9</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="2"/>
@@ -2273,7 +2274,7 @@
         <v>9</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="2"/>
@@ -2292,7 +2293,7 @@
         <v>9</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="2"/>
@@ -2311,7 +2312,7 @@
         <v>9</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="2"/>
@@ -2330,7 +2331,7 @@
         <v>9</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
@@ -2347,7 +2348,7 @@
         <v>9</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
@@ -2364,7 +2365,7 @@
         <v>9</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
@@ -2381,7 +2382,7 @@
         <v>9</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
@@ -2398,7 +2399,7 @@
         <v>9</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
@@ -2415,7 +2416,7 @@
         <v>9</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
@@ -2432,7 +2433,7 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
@@ -2449,7 +2450,7 @@
         <v>7</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
@@ -2466,7 +2467,7 @@
         <v>9</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
@@ -2483,7 +2484,7 @@
         <v>9</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
@@ -2500,7 +2501,7 @@
         <v>7</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.3">
@@ -2517,7 +2518,7 @@
         <v>7</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.3">
@@ -2534,7 +2535,7 @@
         <v>9</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
@@ -2551,7 +2552,7 @@
         <v>9</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
@@ -2568,7 +2569,7 @@
         <v>7</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
@@ -2585,7 +2586,7 @@
         <v>7</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
@@ -2602,7 +2603,7 @@
         <v>9</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
@@ -2619,7 +2620,7 @@
         <v>9</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
@@ -2636,7 +2637,7 @@
         <v>9</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
@@ -2653,7 +2654,7 @@
         <v>9</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
@@ -2670,7 +2671,7 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
@@ -2687,7 +2688,7 @@
         <v>7</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
@@ -2704,7 +2705,7 @@
         <v>9</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
@@ -2721,7 +2722,7 @@
         <v>9</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
@@ -2738,7 +2739,7 @@
         <v>9</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
@@ -2755,7 +2756,7 @@
         <v>9</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
@@ -2772,7 +2773,7 @@
         <v>9</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
@@ -2789,15 +2790,15 @@
         <v>9</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>35</v>
@@ -2806,15 +2807,15 @@
         <v>7</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>36</v>
@@ -2823,7 +2824,7 @@
         <v>9</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
@@ -2840,7 +2841,7 @@
         <v>9</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
@@ -2857,12 +2858,12 @@
         <v>9</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="1" t="s">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>59</v>
@@ -2874,12 +2875,12 @@
         <v>9</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>59</v>
@@ -2891,12 +2892,12 @@
         <v>9</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>60</v>
@@ -2908,12 +2909,12 @@
         <v>9</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>60</v>
@@ -2925,12 +2926,12 @@
         <v>9</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>61</v>
@@ -2942,12 +2943,12 @@
         <v>9</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>61</v>
@@ -2959,7 +2960,7 @@
         <v>9</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
